--- a/data/fix_values.xlsx
+++ b/data/fix_values.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3775" uniqueCount="1347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3777" uniqueCount="1347">
   <si>
     <t xml:space="preserve">lab_id</t>
   </si>
@@ -109,7 +109,7 @@
     <t xml:space="preserve">DASA</t>
   </si>
   <si>
-    <t xml:space="preserve">NAO DETECTADO</t>
+    <t xml:space="preserve">piratINING</t>
   </si>
   <si>
     <t xml:space="preserve">SABIN</t>
@@ -4141,11 +4141,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4162,16 +4162,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="10.5234375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D962"/>
+  <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.16"/>
   </cols>
   <sheetData>
@@ -4721,7 +4721,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
         <v>28</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
         <v>37</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
         <v>37</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
         <v>37</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
         <v>37</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
         <v>37</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
         <v>37</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
         <v>37</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
         <v>37</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
         <v>37</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
         <v>37</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
         <v>37</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
         <v>37</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
         <v>37</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
         <v>37</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
         <v>37</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
         <v>37</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
         <v>37</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
         <v>37</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
         <v>37</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
         <v>37</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
         <v>37</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
         <v>37</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
         <v>37</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
         <v>37</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
         <v>37</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
         <v>37</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
         <v>37</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
         <v>37</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
         <v>37</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
         <v>37</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
         <v>37</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
         <v>37</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
         <v>37</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
         <v>37</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
         <v>37</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
         <v>37</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
         <v>37</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
         <v>37</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
         <v>37</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
         <v>37</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
         <v>37</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
         <v>37</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
         <v>37</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
         <v>37</v>
       </c>
@@ -6378,7 +6378,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
         <v>37</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
         <v>37</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
         <v>37</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
         <v>37</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
         <v>37</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
         <v>37</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
         <v>37</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
         <v>37</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="s">
         <v>37</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
         <v>37</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
         <v>37</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
         <v>37</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
         <v>37</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
         <v>37</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
         <v>37</v>
       </c>
@@ -6588,7 +6588,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
         <v>37</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
         <v>37</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
         <v>37</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
         <v>37</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
         <v>37</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
         <v>37</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
         <v>37</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
         <v>37</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
         <v>37</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
         <v>37</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
         <v>37</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
         <v>37</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
         <v>37</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
         <v>37</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
         <v>37</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
         <v>37</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
         <v>37</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
         <v>37</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
         <v>37</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
         <v>37</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
         <v>37</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
         <v>37</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
         <v>37</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
         <v>37</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
         <v>37</v>
       </c>
@@ -6938,7 +6938,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
         <v>37</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
         <v>37</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
         <v>37</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
         <v>37</v>
       </c>
@@ -6994,7 +6994,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
         <v>37</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
         <v>37</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
         <v>37</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
         <v>37</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
         <v>37</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
         <v>37</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
         <v>37</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
         <v>37</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
         <v>37</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
         <v>37</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
         <v>37</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
         <v>37</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
         <v>37</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="0" t="s">
         <v>37</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
         <v>37</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
         <v>37</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
         <v>37</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
         <v>37</v>
       </c>
@@ -7246,7 +7246,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
         <v>37</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
         <v>37</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="0" t="s">
         <v>37</v>
       </c>
@@ -7288,7 +7288,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
         <v>37</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
         <v>37</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
         <v>37</v>
       </c>
@@ -7330,7 +7330,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
         <v>37</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
         <v>37</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
         <v>37</v>
       </c>
@@ -7372,7 +7372,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
         <v>37</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
         <v>37</v>
       </c>
@@ -7400,7 +7400,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
         <v>37</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
         <v>37</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
         <v>37</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
         <v>37</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
         <v>37</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
         <v>37</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
         <v>37</v>
       </c>
@@ -7498,7 +7498,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="0" t="s">
         <v>37</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
         <v>37</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
         <v>37</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
         <v>37</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
         <v>37</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
         <v>37</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
         <v>37</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="0" t="s">
         <v>37</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="0" t="s">
         <v>37</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="0" t="s">
         <v>37</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="0" t="s">
         <v>37</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="0" t="s">
         <v>37</v>
       </c>
@@ -7666,7 +7666,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="0" t="s">
         <v>37</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="0" t="s">
         <v>37</v>
       </c>
@@ -7694,7 +7694,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="0" t="s">
         <v>37</v>
       </c>
@@ -7708,7 +7708,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="0" t="s">
         <v>37</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="0" t="s">
         <v>37</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="0" t="s">
         <v>37</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="0" t="s">
         <v>37</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="0" t="s">
         <v>37</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="0" t="s">
         <v>37</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="s">
         <v>37</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="0" t="s">
         <v>37</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="0" t="s">
         <v>37</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="0" t="s">
         <v>37</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="0" t="s">
         <v>37</v>
       </c>
@@ -7862,7 +7862,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="0" t="s">
         <v>37</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="0" t="s">
         <v>37</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="0" t="s">
         <v>37</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="0" t="s">
         <v>37</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="0" t="s">
         <v>37</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="0" t="s">
         <v>37</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="0" t="s">
         <v>37</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="0" t="s">
         <v>37</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="0" t="s">
         <v>37</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="0" t="s">
         <v>37</v>
       </c>
@@ -8002,7 +8002,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="0" t="s">
         <v>37</v>
       </c>
@@ -8016,7 +8016,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="0" t="s">
         <v>37</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="0" t="s">
         <v>37</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="0" t="s">
         <v>37</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="0" t="s">
         <v>37</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="0" t="s">
         <v>37</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="0" t="s">
         <v>37</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="0" t="s">
         <v>37</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="0" t="s">
         <v>37</v>
       </c>
@@ -8128,7 +8128,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="0" t="s">
         <v>37</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="0" t="s">
         <v>37</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="0" t="s">
         <v>37</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="0" t="s">
         <v>37</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="0" t="s">
         <v>37</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="0" t="s">
         <v>37</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="0" t="s">
         <v>37</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="0" t="s">
         <v>37</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="0" t="s">
         <v>37</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="0" t="s">
         <v>37</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="0" t="s">
         <v>37</v>
       </c>
@@ -8282,7 +8282,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="0" t="s">
         <v>37</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="0" t="s">
         <v>37</v>
       </c>
@@ -8310,7 +8310,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="0" t="s">
         <v>37</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="0" t="s">
         <v>37</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="0" t="s">
         <v>37</v>
       </c>
@@ -8352,7 +8352,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="0" t="s">
         <v>37</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="0" t="s">
         <v>37</v>
       </c>
@@ -8380,7 +8380,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="0" t="s">
         <v>37</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="0" t="s">
         <v>37</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="0" t="s">
         <v>37</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="0" t="s">
         <v>37</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="0" t="s">
         <v>37</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="0" t="s">
         <v>37</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="0" t="s">
         <v>37</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="0" t="s">
         <v>37</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="0" t="s">
         <v>37</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="0" t="s">
         <v>37</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="0" t="s">
         <v>37</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="0" t="s">
         <v>37</v>
       </c>
@@ -8548,7 +8548,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="0" t="s">
         <v>37</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="0" t="s">
         <v>37</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="0" t="s">
         <v>37</v>
       </c>
@@ -8590,7 +8590,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="0" t="s">
         <v>37</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="0" t="s">
         <v>37</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="0" t="s">
         <v>37</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="0" t="s">
         <v>37</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="0" t="s">
         <v>37</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="0" t="s">
         <v>37</v>
       </c>
@@ -8674,7 +8674,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="0" t="s">
         <v>37</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="0" t="s">
         <v>37</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="0" t="s">
         <v>37</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="0" t="s">
         <v>37</v>
       </c>
@@ -8730,7 +8730,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="0" t="s">
         <v>37</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="0" t="s">
         <v>37</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="0" t="s">
         <v>37</v>
       </c>
@@ -8772,7 +8772,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="0" t="s">
         <v>37</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="0" t="s">
         <v>37</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="0" t="s">
         <v>37</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="0" t="s">
         <v>37</v>
       </c>
@@ -8828,7 +8828,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="0" t="s">
         <v>37</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="0" t="s">
         <v>37</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="0" t="s">
         <v>37</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="0" t="s">
         <v>37</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="0" t="s">
         <v>37</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="0" t="s">
         <v>37</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="0" t="s">
         <v>37</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="0" t="s">
         <v>37</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="0" t="s">
         <v>37</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="0" t="s">
         <v>37</v>
       </c>
@@ -8968,7 +8968,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="0" t="s">
         <v>37</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="0" t="s">
         <v>37</v>
       </c>
@@ -8996,7 +8996,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="0" t="s">
         <v>37</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="0" t="s">
         <v>37</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="0" t="s">
         <v>37</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="0" t="s">
         <v>37</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="0" t="s">
         <v>37</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="0" t="s">
         <v>37</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="0" t="s">
         <v>37</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="0" t="s">
         <v>37</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="0" t="s">
         <v>37</v>
       </c>
@@ -9122,7 +9122,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="0" t="s">
         <v>37</v>
       </c>
@@ -9136,7 +9136,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="0" t="s">
         <v>37</v>
       </c>
@@ -9150,7 +9150,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="0" t="s">
         <v>37</v>
       </c>
@@ -9164,7 +9164,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="0" t="s">
         <v>37</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="0" t="s">
         <v>37</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="0" t="s">
         <v>37</v>
       </c>
@@ -9206,7 +9206,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="0" t="s">
         <v>37</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="0" t="s">
         <v>37</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="0" t="s">
         <v>37</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="0" t="s">
         <v>37</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="0" t="s">
         <v>37</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="0" t="s">
         <v>37</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="0" t="s">
         <v>37</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="0" t="s">
         <v>37</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="0" t="s">
         <v>37</v>
       </c>
@@ -9332,7 +9332,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="0" t="s">
         <v>37</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="0" t="s">
         <v>37</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="0" t="s">
         <v>37</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="0" t="s">
         <v>37</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="0" t="s">
         <v>37</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="0" t="s">
         <v>37</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="0" t="s">
         <v>37</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="0" t="s">
         <v>37</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="0" t="s">
         <v>37</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="0" t="s">
         <v>37</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="0" t="s">
         <v>37</v>
       </c>
@@ -9486,7 +9486,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="0" t="s">
         <v>37</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="0" t="s">
         <v>37</v>
       </c>
@@ -9514,7 +9514,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="0" t="s">
         <v>37</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="0" t="s">
         <v>37</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="0" t="s">
         <v>37</v>
       </c>
@@ -9556,7 +9556,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="0" t="s">
         <v>37</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="0" t="s">
         <v>37</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="0" t="s">
         <v>37</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="0" t="s">
         <v>37</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="0" t="s">
         <v>37</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="0" t="s">
         <v>37</v>
       </c>
@@ -9640,7 +9640,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="0" t="s">
         <v>37</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="0" t="s">
         <v>37</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="0" t="s">
         <v>37</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="0" t="s">
         <v>37</v>
       </c>
@@ -9696,7 +9696,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="0" t="s">
         <v>37</v>
       </c>
@@ -9710,7 +9710,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="0" t="s">
         <v>37</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="0" t="s">
         <v>37</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="0" t="s">
         <v>37</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="0" t="s">
         <v>37</v>
       </c>
@@ -9766,7 +9766,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="0" t="s">
         <v>37</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="0" t="s">
         <v>37</v>
       </c>
@@ -9794,7 +9794,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="0" t="s">
         <v>37</v>
       </c>
@@ -9808,7 +9808,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="0" t="s">
         <v>37</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="0" t="s">
         <v>37</v>
       </c>
@@ -9836,7 +9836,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="0" t="s">
         <v>37</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="0" t="s">
         <v>37</v>
       </c>
@@ -9864,7 +9864,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="0" t="s">
         <v>37</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="0" t="s">
         <v>37</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="0" t="s">
         <v>37</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="0" t="s">
         <v>37</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="0" t="s">
         <v>37</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="0" t="s">
         <v>37</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="0" t="s">
         <v>37</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="0" t="s">
         <v>37</v>
       </c>
@@ -9976,7 +9976,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="0" t="s">
         <v>37</v>
       </c>
@@ -9990,7 +9990,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="0" t="s">
         <v>37</v>
       </c>
@@ -10004,7 +10004,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="0" t="s">
         <v>37</v>
       </c>
@@ -10018,7 +10018,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="0" t="s">
         <v>37</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="0" t="s">
         <v>37</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="0" t="s">
         <v>37</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="0" t="s">
         <v>37</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="0" t="s">
         <v>37</v>
       </c>
@@ -10088,7 +10088,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="0" t="s">
         <v>37</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="0" t="s">
         <v>37</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="0" t="s">
         <v>37</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="0" t="s">
         <v>37</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="0" t="s">
         <v>37</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="0" t="s">
         <v>37</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="0" t="s">
         <v>37</v>
       </c>
@@ -10186,7 +10186,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="0" t="s">
         <v>37</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="0" t="s">
         <v>37</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="0" t="s">
         <v>37</v>
       </c>
@@ -10228,7 +10228,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="0" t="s">
         <v>37</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="0" t="s">
         <v>37</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="0" t="s">
         <v>37</v>
       </c>
@@ -10270,7 +10270,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="0" t="s">
         <v>37</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="0" t="s">
         <v>37</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="0" t="s">
         <v>37</v>
       </c>
@@ -10312,7 +10312,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="0" t="s">
         <v>37</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="0" t="s">
         <v>37</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="0" t="s">
         <v>37</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="0" t="s">
         <v>37</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="0" t="s">
         <v>37</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="0" t="s">
         <v>37</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="0" t="s">
         <v>37</v>
       </c>
@@ -10410,7 +10410,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="0" t="s">
         <v>37</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="0" t="s">
         <v>37</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="0" t="s">
         <v>37</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="0" t="s">
         <v>37</v>
       </c>
@@ -10466,7 +10466,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="0" t="s">
         <v>37</v>
       </c>
@@ -10480,7 +10480,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="0" t="s">
         <v>37</v>
       </c>
@@ -10494,7 +10494,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="0" t="s">
         <v>37</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="0" t="s">
         <v>37</v>
       </c>
@@ -10522,7 +10522,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="0" t="s">
         <v>37</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="0" t="s">
         <v>37</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="0" t="s">
         <v>37</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="0" t="s">
         <v>37</v>
       </c>
@@ -10578,7 +10578,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="0" t="s">
         <v>37</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="0" t="s">
         <v>37</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="0" t="s">
         <v>37</v>
       </c>
@@ -10620,7 +10620,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="0" t="s">
         <v>37</v>
       </c>
@@ -10634,7 +10634,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="0" t="s">
         <v>37</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="0" t="s">
         <v>37</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="0" t="s">
         <v>37</v>
       </c>
@@ -10676,7 +10676,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="0" t="s">
         <v>37</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="0" t="s">
         <v>37</v>
       </c>
@@ -10704,7 +10704,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="0" t="s">
         <v>37</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="0" t="s">
         <v>37</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="0" t="s">
         <v>37</v>
       </c>
@@ -10746,7 +10746,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="0" t="s">
         <v>37</v>
       </c>
@@ -10760,7 +10760,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="0" t="s">
         <v>37</v>
       </c>
@@ -10774,7 +10774,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="0" t="s">
         <v>37</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="0" t="s">
         <v>37</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="0" t="s">
         <v>37</v>
       </c>
@@ -10816,7 +10816,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="0" t="s">
         <v>37</v>
       </c>
@@ -10830,7 +10830,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="0" t="s">
         <v>37</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="0" t="s">
         <v>37</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="0" t="s">
         <v>37</v>
       </c>
@@ -10872,7 +10872,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="0" t="s">
         <v>37</v>
       </c>
@@ -10886,7 +10886,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="0" t="s">
         <v>37</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="0" t="s">
         <v>37</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="0" t="s">
         <v>37</v>
       </c>
@@ -10928,7 +10928,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="0" t="s">
         <v>37</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="0" t="s">
         <v>37</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="0" t="s">
         <v>37</v>
       </c>
@@ -10970,7 +10970,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="0" t="s">
         <v>37</v>
       </c>
@@ -10984,7 +10984,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="0" t="s">
         <v>37</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="0" t="s">
         <v>37</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="0" t="s">
         <v>37</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="0" t="s">
         <v>37</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="0" t="s">
         <v>37</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="0" t="s">
         <v>37</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="0" t="s">
         <v>37</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="0" t="s">
         <v>37</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="0" t="s">
         <v>37</v>
       </c>
@@ -11110,7 +11110,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="0" t="s">
         <v>37</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="0" t="s">
         <v>37</v>
       </c>
@@ -11138,7 +11138,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="0" t="s">
         <v>37</v>
       </c>
@@ -11152,7 +11152,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="0" t="s">
         <v>37</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="0" t="s">
         <v>37</v>
       </c>
@@ -11180,7 +11180,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="0" t="s">
         <v>37</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="0" t="s">
         <v>37</v>
       </c>
@@ -11208,7 +11208,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="0" t="s">
         <v>37</v>
       </c>
@@ -11222,7 +11222,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="0" t="s">
         <v>37</v>
       </c>
@@ -11236,7 +11236,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="0" t="s">
         <v>37</v>
       </c>
@@ -11250,7 +11250,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="0" t="s">
         <v>37</v>
       </c>
@@ -11264,7 +11264,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="0" t="s">
         <v>37</v>
       </c>
@@ -11278,7 +11278,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="0" t="s">
         <v>37</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="0" t="s">
         <v>37</v>
       </c>
@@ -11306,7 +11306,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="0" t="s">
         <v>37</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="0" t="s">
         <v>37</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="0" t="s">
         <v>37</v>
       </c>
@@ -11348,7 +11348,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="0" t="s">
         <v>37</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="0" t="s">
         <v>37</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="0" t="s">
         <v>37</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="0" t="s">
         <v>37</v>
       </c>
@@ -11404,7 +11404,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="0" t="s">
         <v>37</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="0" t="s">
         <v>37</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="0" t="s">
         <v>37</v>
       </c>
@@ -11446,7 +11446,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="0" t="s">
         <v>37</v>
       </c>
@@ -11460,7 +11460,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="0" t="s">
         <v>37</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="0" t="s">
         <v>37</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="0" t="s">
         <v>37</v>
       </c>
@@ -11502,7 +11502,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="0" t="s">
         <v>37</v>
       </c>
@@ -11516,7 +11516,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="0" t="s">
         <v>37</v>
       </c>
@@ -11530,7 +11530,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="0" t="s">
         <v>37</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="0" t="s">
         <v>37</v>
       </c>
@@ -11558,7 +11558,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="0" t="s">
         <v>37</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="0" t="s">
         <v>37</v>
       </c>
@@ -11586,7 +11586,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="0" t="s">
         <v>37</v>
       </c>
@@ -11600,7 +11600,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="0" t="s">
         <v>37</v>
       </c>
@@ -11614,7 +11614,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="0" t="s">
         <v>37</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="0" t="s">
         <v>37</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="0" t="s">
         <v>37</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="0" t="s">
         <v>37</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="0" t="s">
         <v>37</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="0" t="s">
         <v>37</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="0" t="s">
         <v>37</v>
       </c>
@@ -11712,7 +11712,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="0" t="s">
         <v>37</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="0" t="s">
         <v>37</v>
       </c>
@@ -11740,7 +11740,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="0" t="s">
         <v>37</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="0" t="s">
         <v>37</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="0" t="s">
         <v>37</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="0" t="s">
         <v>37</v>
       </c>
@@ -11796,7 +11796,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="0" t="s">
         <v>37</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="0" t="s">
         <v>37</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="0" t="s">
         <v>37</v>
       </c>
@@ -11838,7 +11838,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="0" t="s">
         <v>37</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="0" t="s">
         <v>37</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="0" t="s">
         <v>37</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="0" t="s">
         <v>37</v>
       </c>
@@ -11894,7 +11894,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="0" t="s">
         <v>37</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="0" t="s">
         <v>37</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="0" t="s">
         <v>37</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="0" t="s">
         <v>37</v>
       </c>
@@ -11950,7 +11950,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="0" t="s">
         <v>37</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="0" t="s">
         <v>37</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="0" t="s">
         <v>37</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="0" t="s">
         <v>37</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="0" t="s">
         <v>37</v>
       </c>
@@ -12020,7 +12020,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="0" t="s">
         <v>37</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="0" t="s">
         <v>37</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="0" t="s">
         <v>37</v>
       </c>
@@ -12062,7 +12062,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="0" t="s">
         <v>37</v>
       </c>
@@ -12076,7 +12076,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="0" t="s">
         <v>37</v>
       </c>
@@ -12090,7 +12090,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="0" t="s">
         <v>37</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="0" t="s">
         <v>37</v>
       </c>
@@ -12118,7 +12118,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="0" t="s">
         <v>37</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="0" t="s">
         <v>37</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="0" t="s">
         <v>37</v>
       </c>
@@ -12160,7 +12160,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="0" t="s">
         <v>37</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="0" t="s">
         <v>37</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="0" t="s">
         <v>37</v>
       </c>
@@ -12202,7 +12202,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="0" t="s">
         <v>37</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="0" t="s">
         <v>37</v>
       </c>
@@ -12230,7 +12230,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="0" t="s">
         <v>37</v>
       </c>
@@ -12244,7 +12244,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="0" t="s">
         <v>37</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="0" t="s">
         <v>37</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="0" t="s">
         <v>37</v>
       </c>
@@ -12286,7 +12286,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="0" t="s">
         <v>37</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="0" t="s">
         <v>37</v>
       </c>
@@ -12314,7 +12314,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="0" t="s">
         <v>37</v>
       </c>
@@ -12328,7 +12328,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="0" t="s">
         <v>37</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="0" t="s">
         <v>37</v>
       </c>
@@ -12356,7 +12356,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="0" t="s">
         <v>37</v>
       </c>
@@ -12370,7 +12370,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="0" t="s">
         <v>37</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A588" s="0" t="s">
         <v>37</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="0" t="s">
         <v>37</v>
       </c>
@@ -12412,7 +12412,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="0" t="s">
         <v>37</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="0" t="s">
         <v>37</v>
       </c>
@@ -12440,7 +12440,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="0" t="s">
         <v>37</v>
       </c>
@@ -12454,7 +12454,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="0" t="s">
         <v>37</v>
       </c>
@@ -12468,7 +12468,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="0" t="s">
         <v>37</v>
       </c>
@@ -12482,7 +12482,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="0" t="s">
         <v>37</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="0" t="s">
         <v>37</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="0" t="s">
         <v>37</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="0" t="s">
         <v>37</v>
       </c>
@@ -12538,7 +12538,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="0" t="s">
         <v>37</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="0" t="s">
         <v>37</v>
       </c>
@@ -12566,7 +12566,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A601" s="0" t="s">
         <v>37</v>
       </c>
@@ -12580,7 +12580,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="0" t="s">
         <v>37</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="0" t="s">
         <v>37</v>
       </c>
@@ -12608,7 +12608,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A604" s="0" t="s">
         <v>37</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A605" s="0" t="s">
         <v>37</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A606" s="0" t="s">
         <v>37</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="0" t="s">
         <v>37</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="0" t="s">
         <v>37</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A609" s="0" t="s">
         <v>37</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A610" s="0" t="s">
         <v>37</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="0" t="s">
         <v>37</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A612" s="0" t="s">
         <v>37</v>
       </c>
@@ -12734,7 +12734,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A613" s="0" t="s">
         <v>37</v>
       </c>
@@ -12748,7 +12748,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A614" s="0" t="s">
         <v>37</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="0" t="s">
         <v>37</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="0" t="s">
         <v>37</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="0" t="s">
         <v>37</v>
       </c>
@@ -12804,7 +12804,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="0" t="s">
         <v>37</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="0" t="s">
         <v>37</v>
       </c>
@@ -12832,7 +12832,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="0" t="s">
         <v>37</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A621" s="0" t="s">
         <v>37</v>
       </c>
@@ -12860,7 +12860,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="0" t="s">
         <v>37</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A623" s="0" t="s">
         <v>37</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="0" t="s">
         <v>37</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A625" s="0" t="s">
         <v>37</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A626" s="0" t="s">
         <v>37</v>
       </c>
@@ -12930,7 +12930,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="0" t="s">
         <v>37</v>
       </c>
@@ -12944,7 +12944,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="0" t="s">
         <v>37</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A629" s="0" t="s">
         <v>37</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="0" t="s">
         <v>37</v>
       </c>
@@ -12986,7 +12986,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="0" t="s">
         <v>37</v>
       </c>
@@ -13000,7 +13000,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="0" t="s">
         <v>37</v>
       </c>
@@ -13014,7 +13014,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="0" t="s">
         <v>37</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A634" s="0" t="s">
         <v>37</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="0" t="s">
         <v>37</v>
       </c>
@@ -13056,7 +13056,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A636" s="0" t="s">
         <v>37</v>
       </c>
@@ -13070,7 +13070,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="0" t="s">
         <v>37</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="0" t="s">
         <v>37</v>
       </c>
@@ -13098,7 +13098,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A639" s="0" t="s">
         <v>37</v>
       </c>
@@ -13112,7 +13112,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="640" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A640" s="0" t="s">
         <v>37</v>
       </c>
@@ -13126,7 +13126,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="641" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="0" t="s">
         <v>37</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A642" s="0" t="s">
         <v>37</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A643" s="0" t="s">
         <v>37</v>
       </c>
@@ -13168,7 +13168,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A644" s="0" t="s">
         <v>37</v>
       </c>
@@ -13182,7 +13182,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="0" t="s">
         <v>37</v>
       </c>
@@ -13196,7 +13196,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A646" s="0" t="s">
         <v>37</v>
       </c>
@@ -13210,7 +13210,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A647" s="0" t="s">
         <v>37</v>
       </c>
@@ -13224,7 +13224,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A648" s="0" t="s">
         <v>37</v>
       </c>
@@ -13238,7 +13238,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="649" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A649" s="0" t="s">
         <v>37</v>
       </c>
@@ -13252,7 +13252,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="650" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A650" s="0" t="s">
         <v>37</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="651" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A651" s="0" t="s">
         <v>37</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="652" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A652" s="0" t="s">
         <v>37</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="653" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A653" s="0" t="s">
         <v>37</v>
       </c>
@@ -13308,7 +13308,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="654" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A654" s="0" t="s">
         <v>37</v>
       </c>
@@ -13322,7 +13322,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="655" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A655" s="0" t="s">
         <v>37</v>
       </c>
@@ -13336,7 +13336,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="656" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A656" s="0" t="s">
         <v>37</v>
       </c>
@@ -13350,7 +13350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="657" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A657" s="0" t="s">
         <v>37</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="658" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A658" s="0" t="s">
         <v>37</v>
       </c>
@@ -13378,7 +13378,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="659" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A659" s="0" t="s">
         <v>37</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="660" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A660" s="0" t="s">
         <v>37</v>
       </c>
@@ -13406,7 +13406,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="661" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A661" s="0" t="s">
         <v>37</v>
       </c>
@@ -13420,7 +13420,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="662" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A662" s="0" t="s">
         <v>37</v>
       </c>
@@ -13434,7 +13434,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="663" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A663" s="0" t="s">
         <v>37</v>
       </c>
@@ -13448,7 +13448,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="664" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A664" s="0" t="s">
         <v>37</v>
       </c>
@@ -13462,7 +13462,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="665" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A665" s="0" t="s">
         <v>37</v>
       </c>
@@ -13476,7 +13476,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="666" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A666" s="0" t="s">
         <v>37</v>
       </c>
@@ -13490,7 +13490,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="667" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A667" s="0" t="s">
         <v>37</v>
       </c>
@@ -13504,7 +13504,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="668" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A668" s="0" t="s">
         <v>37</v>
       </c>
@@ -13518,7 +13518,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="669" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A669" s="0" t="s">
         <v>37</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="670" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A670" s="0" t="s">
         <v>37</v>
       </c>
@@ -13546,7 +13546,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="671" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A671" s="0" t="s">
         <v>37</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="672" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A672" s="0" t="s">
         <v>37</v>
       </c>
@@ -13574,7 +13574,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="673" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A673" s="0" t="s">
         <v>37</v>
       </c>
@@ -13588,7 +13588,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="674" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A674" s="0" t="s">
         <v>37</v>
       </c>
@@ -13602,7 +13602,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A675" s="0" t="s">
         <v>37</v>
       </c>
@@ -13616,7 +13616,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A676" s="0" t="s">
         <v>37</v>
       </c>
@@ -13630,7 +13630,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A677" s="0" t="s">
         <v>37</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="678" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A678" s="0" t="s">
         <v>37</v>
       </c>
@@ -13658,7 +13658,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="679" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A679" s="0" t="s">
         <v>37</v>
       </c>
@@ -13672,7 +13672,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="680" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A680" s="0" t="s">
         <v>37</v>
       </c>
@@ -13686,7 +13686,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="681" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A681" s="0" t="s">
         <v>37</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="682" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A682" s="0" t="s">
         <v>37</v>
       </c>
@@ -13714,7 +13714,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="683" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A683" s="0" t="s">
         <v>37</v>
       </c>
@@ -13728,7 +13728,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="684" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A684" s="0" t="s">
         <v>37</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="685" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A685" s="0" t="s">
         <v>37</v>
       </c>
@@ -13756,7 +13756,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="686" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A686" s="0" t="s">
         <v>37</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A687" s="0" t="s">
         <v>37</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="688" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A688" s="0" t="s">
         <v>37</v>
       </c>
@@ -13798,7 +13798,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="689" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A689" s="0" t="s">
         <v>37</v>
       </c>
@@ -13812,7 +13812,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="690" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A690" s="0" t="s">
         <v>37</v>
       </c>
@@ -13826,7 +13826,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A691" s="0" t="s">
         <v>37</v>
       </c>
@@ -13840,7 +13840,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A692" s="0" t="s">
         <v>37</v>
       </c>
@@ -13854,7 +13854,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A693" s="0" t="s">
         <v>37</v>
       </c>
@@ -13868,7 +13868,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A694" s="0" t="s">
         <v>37</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A695" s="0" t="s">
         <v>37</v>
       </c>
@@ -13896,7 +13896,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="696" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A696" s="0" t="s">
         <v>37</v>
       </c>
@@ -13910,7 +13910,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="697" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A697" s="0" t="s">
         <v>37</v>
       </c>
@@ -13924,7 +13924,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A698" s="0" t="s">
         <v>37</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="699" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A699" s="0" t="s">
         <v>37</v>
       </c>
@@ -13952,7 +13952,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="700" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A700" s="0" t="s">
         <v>37</v>
       </c>
@@ -13966,7 +13966,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="701" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A701" s="0" t="s">
         <v>37</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="702" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A702" s="0" t="s">
         <v>37</v>
       </c>
@@ -13994,7 +13994,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="703" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A703" s="0" t="s">
         <v>37</v>
       </c>
@@ -14008,7 +14008,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="704" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A704" s="0" t="s">
         <v>37</v>
       </c>
@@ -14022,7 +14022,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="705" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A705" s="0" t="s">
         <v>37</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="706" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A706" s="0" t="s">
         <v>37</v>
       </c>
@@ -14050,7 +14050,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="707" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A707" s="0" t="s">
         <v>37</v>
       </c>
@@ -14064,7 +14064,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="708" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A708" s="0" t="s">
         <v>37</v>
       </c>
@@ -14078,7 +14078,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A709" s="0" t="s">
         <v>37</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="710" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A710" s="0" t="s">
         <v>37</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="711" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A711" s="0" t="s">
         <v>37</v>
       </c>
@@ -14120,7 +14120,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="712" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A712" s="0" t="s">
         <v>37</v>
       </c>
@@ -14134,7 +14134,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="713" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A713" s="0" t="s">
         <v>37</v>
       </c>
@@ -14148,7 +14148,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A714" s="0" t="s">
         <v>37</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A715" s="0" t="s">
         <v>37</v>
       </c>
@@ -14176,7 +14176,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="716" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A716" s="0" t="s">
         <v>37</v>
       </c>
@@ -14190,7 +14190,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A717" s="0" t="s">
         <v>37</v>
       </c>
@@ -14204,7 +14204,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="718" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A718" s="0" t="s">
         <v>37</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A719" s="0" t="s">
         <v>37</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="720" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A720" s="0" t="s">
         <v>37</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="721" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A721" s="0" t="s">
         <v>37</v>
       </c>
@@ -14260,7 +14260,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="722" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A722" s="0" t="s">
         <v>37</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A723" s="0" t="s">
         <v>37</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A724" s="0" t="s">
         <v>37</v>
       </c>
@@ -14302,7 +14302,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="725" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A725" s="0" t="s">
         <v>37</v>
       </c>
@@ -14316,7 +14316,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="726" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A726" s="0" t="s">
         <v>37</v>
       </c>
@@ -14330,7 +14330,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="727" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A727" s="0" t="s">
         <v>37</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="728" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A728" s="0" t="s">
         <v>37</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="729" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A729" s="0" t="s">
         <v>37</v>
       </c>
@@ -14372,7 +14372,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="730" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A730" s="0" t="s">
         <v>37</v>
       </c>
@@ -14386,7 +14386,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="731" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A731" s="0" t="s">
         <v>37</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A732" s="0" t="s">
         <v>37</v>
       </c>
@@ -14414,7 +14414,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A733" s="0" t="s">
         <v>37</v>
       </c>
@@ -14428,7 +14428,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="734" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A734" s="0" t="s">
         <v>37</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="735" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A735" s="0" t="s">
         <v>37</v>
       </c>
@@ -14456,7 +14456,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A736" s="0" t="s">
         <v>37</v>
       </c>
@@ -14470,7 +14470,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="737" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A737" s="0" t="s">
         <v>37</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="738" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A738" s="0" t="s">
         <v>37</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A739" s="0" t="s">
         <v>37</v>
       </c>
@@ -14512,7 +14512,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="740" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A740" s="0" t="s">
         <v>37</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A741" s="0" t="s">
         <v>37</v>
       </c>
@@ -14540,7 +14540,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="742" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A742" s="0" t="s">
         <v>37</v>
       </c>
@@ -14554,7 +14554,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="743" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A743" s="0" t="s">
         <v>37</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="744" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A744" s="0" t="s">
         <v>37</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="745" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A745" s="0" t="s">
         <v>37</v>
       </c>
@@ -14596,7 +14596,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="746" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A746" s="0" t="s">
         <v>37</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="747" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A747" s="0" t="s">
         <v>37</v>
       </c>
@@ -14624,7 +14624,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="748" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A748" s="0" t="s">
         <v>37</v>
       </c>
@@ -14638,7 +14638,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="749" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A749" s="0" t="s">
         <v>37</v>
       </c>
@@ -14652,7 +14652,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="750" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A750" s="0" t="s">
         <v>37</v>
       </c>
@@ -14666,7 +14666,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="751" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A751" s="0" t="s">
         <v>37</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="752" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A752" s="0" t="s">
         <v>37</v>
       </c>
@@ -14694,7 +14694,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="753" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A753" s="0" t="s">
         <v>37</v>
       </c>
@@ -14708,7 +14708,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="754" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A754" s="0" t="s">
         <v>37</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A755" s="0" t="s">
         <v>37</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="756" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A756" s="0" t="s">
         <v>37</v>
       </c>
@@ -14750,7 +14750,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="757" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A757" s="0" t="s">
         <v>37</v>
       </c>
@@ -14764,7 +14764,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="758" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A758" s="0" t="s">
         <v>37</v>
       </c>
@@ -14778,7 +14778,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A759" s="0" t="s">
         <v>37</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="760" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A760" s="0" t="s">
         <v>37</v>
       </c>
@@ -14806,7 +14806,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="761" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A761" s="0" t="s">
         <v>37</v>
       </c>
@@ -14820,7 +14820,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="762" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A762" s="0" t="s">
         <v>37</v>
       </c>
@@ -14834,7 +14834,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A763" s="0" t="s">
         <v>37</v>
       </c>
@@ -14848,7 +14848,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="764" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A764" s="0" t="s">
         <v>37</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="765" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A765" s="0" t="s">
         <v>37</v>
       </c>
@@ -14876,7 +14876,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="766" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A766" s="0" t="s">
         <v>37</v>
       </c>
@@ -14890,7 +14890,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="767" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A767" s="0" t="s">
         <v>37</v>
       </c>
@@ -14904,7 +14904,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="768" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A768" s="0" t="s">
         <v>37</v>
       </c>
@@ -14918,7 +14918,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="769" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A769" s="0" t="s">
         <v>37</v>
       </c>
@@ -14932,7 +14932,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="770" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A770" s="0" t="s">
         <v>37</v>
       </c>
@@ -14946,7 +14946,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="771" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A771" s="0" t="s">
         <v>37</v>
       </c>
@@ -14960,7 +14960,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="772" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A772" s="0" t="s">
         <v>37</v>
       </c>
@@ -14974,7 +14974,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="773" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A773" s="0" t="s">
         <v>37</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="774" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A774" s="0" t="s">
         <v>37</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="775" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A775" s="0" t="s">
         <v>37</v>
       </c>
@@ -15016,7 +15016,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="776" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A776" s="0" t="s">
         <v>37</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="777" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A777" s="0" t="s">
         <v>37</v>
       </c>
@@ -15044,7 +15044,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="778" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A778" s="0" t="s">
         <v>37</v>
       </c>
@@ -15058,7 +15058,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="779" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A779" s="0" t="s">
         <v>37</v>
       </c>
@@ -15072,7 +15072,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="780" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A780" s="0" t="s">
         <v>37</v>
       </c>
@@ -15086,7 +15086,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="781" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A781" s="0" t="s">
         <v>37</v>
       </c>
@@ -15100,7 +15100,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="782" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A782" s="0" t="s">
         <v>37</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="783" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A783" s="0" t="s">
         <v>37</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="784" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A784" s="0" t="s">
         <v>37</v>
       </c>
@@ -15142,7 +15142,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="785" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A785" s="0" t="s">
         <v>37</v>
       </c>
@@ -15156,7 +15156,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="786" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A786" s="0" t="s">
         <v>37</v>
       </c>
@@ -15170,7 +15170,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="787" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A787" s="0" t="s">
         <v>37</v>
       </c>
@@ -15184,7 +15184,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="788" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A788" s="0" t="s">
         <v>37</v>
       </c>
@@ -15198,7 +15198,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="789" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A789" s="0" t="s">
         <v>37</v>
       </c>
@@ -15212,7 +15212,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="790" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A790" s="0" t="s">
         <v>37</v>
       </c>
@@ -15226,7 +15226,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="791" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A791" s="0" t="s">
         <v>37</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="792" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A792" s="0" t="s">
         <v>37</v>
       </c>
@@ -15254,7 +15254,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="793" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A793" s="0" t="s">
         <v>37</v>
       </c>
@@ -15268,7 +15268,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="794" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A794" s="0" t="s">
         <v>37</v>
       </c>
@@ -15282,7 +15282,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="795" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A795" s="0" t="s">
         <v>37</v>
       </c>
@@ -15296,7 +15296,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="796" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A796" s="0" t="s">
         <v>37</v>
       </c>
@@ -15310,7 +15310,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="797" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A797" s="0" t="s">
         <v>37</v>
       </c>
@@ -15324,7 +15324,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="798" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A798" s="0" t="s">
         <v>37</v>
       </c>
@@ -15338,7 +15338,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="799" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A799" s="0" t="s">
         <v>37</v>
       </c>
@@ -15352,7 +15352,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="800" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A800" s="0" t="s">
         <v>37</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="801" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A801" s="0" t="s">
         <v>37</v>
       </c>
@@ -15380,7 +15380,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="802" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A802" s="0" t="s">
         <v>37</v>
       </c>
@@ -15394,7 +15394,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="803" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A803" s="0" t="s">
         <v>37</v>
       </c>
@@ -15408,7 +15408,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="804" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A804" s="0" t="s">
         <v>37</v>
       </c>
@@ -15422,7 +15422,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="805" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A805" s="0" t="s">
         <v>37</v>
       </c>
@@ -15436,7 +15436,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="806" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A806" s="0" t="s">
         <v>37</v>
       </c>
@@ -15450,7 +15450,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="807" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A807" s="0" t="s">
         <v>37</v>
       </c>
@@ -15464,7 +15464,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="808" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A808" s="0" t="s">
         <v>37</v>
       </c>
@@ -15478,7 +15478,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="809" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A809" s="0" t="s">
         <v>37</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="810" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A810" s="0" t="s">
         <v>37</v>
       </c>
@@ -15506,7 +15506,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="811" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A811" s="0" t="s">
         <v>37</v>
       </c>
@@ -15520,7 +15520,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="812" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A812" s="0" t="s">
         <v>37</v>
       </c>
@@ -15534,7 +15534,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="813" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A813" s="0" t="s">
         <v>37</v>
       </c>
@@ -15548,7 +15548,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="814" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A814" s="0" t="s">
         <v>37</v>
       </c>
@@ -15562,7 +15562,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="815" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A815" s="0" t="s">
         <v>37</v>
       </c>
@@ -15576,7 +15576,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="816" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A816" s="0" t="s">
         <v>37</v>
       </c>
@@ -15590,7 +15590,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="817" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A817" s="0" t="s">
         <v>37</v>
       </c>
@@ -15604,7 +15604,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="818" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A818" s="0" t="s">
         <v>37</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="819" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A819" s="0" t="s">
         <v>37</v>
       </c>
@@ -15632,7 +15632,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="820" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A820" s="0" t="s">
         <v>37</v>
       </c>
@@ -15646,7 +15646,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="821" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A821" s="0" t="s">
         <v>37</v>
       </c>
@@ -15660,7 +15660,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="822" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A822" s="0" t="s">
         <v>37</v>
       </c>
@@ -15674,7 +15674,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="823" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A823" s="0" t="s">
         <v>37</v>
       </c>
@@ -15688,7 +15688,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="824" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A824" s="0" t="s">
         <v>37</v>
       </c>
@@ -15702,7 +15702,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="825" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A825" s="0" t="s">
         <v>37</v>
       </c>
@@ -15716,7 +15716,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="826" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A826" s="0" t="s">
         <v>37</v>
       </c>
@@ -15730,7 +15730,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="827" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A827" s="0" t="s">
         <v>37</v>
       </c>
@@ -15744,7 +15744,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="828" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A828" s="0" t="s">
         <v>37</v>
       </c>
@@ -15758,7 +15758,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="829" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A829" s="0" t="s">
         <v>37</v>
       </c>
@@ -15772,7 +15772,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="830" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A830" s="0" t="s">
         <v>37</v>
       </c>
@@ -15786,7 +15786,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="831" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A831" s="0" t="s">
         <v>37</v>
       </c>
@@ -15800,7 +15800,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="832" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A832" s="0" t="s">
         <v>37</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="833" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A833" s="0" t="s">
         <v>37</v>
       </c>
@@ -15828,7 +15828,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="834" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A834" s="0" t="s">
         <v>37</v>
       </c>
@@ -15842,7 +15842,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="835" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A835" s="0" t="s">
         <v>37</v>
       </c>
@@ -15856,7 +15856,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="836" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A836" s="0" t="s">
         <v>37</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="837" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A837" s="0" t="s">
         <v>37</v>
       </c>
@@ -15884,7 +15884,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="838" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A838" s="0" t="s">
         <v>37</v>
       </c>
@@ -15898,7 +15898,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="839" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A839" s="0" t="s">
         <v>37</v>
       </c>
@@ -15912,7 +15912,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="840" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A840" s="0" t="s">
         <v>37</v>
       </c>
@@ -15926,7 +15926,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="841" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A841" s="0" t="s">
         <v>37</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="842" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A842" s="0" t="s">
         <v>37</v>
       </c>
@@ -15954,7 +15954,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="843" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A843" s="0" t="s">
         <v>37</v>
       </c>
@@ -15968,7 +15968,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="844" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A844" s="0" t="s">
         <v>37</v>
       </c>
@@ -15982,7 +15982,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="845" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A845" s="0" t="s">
         <v>37</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="846" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A846" s="0" t="s">
         <v>37</v>
       </c>
@@ -16010,7 +16010,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="847" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A847" s="0" t="s">
         <v>37</v>
       </c>
@@ -16024,7 +16024,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="848" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A848" s="0" t="s">
         <v>37</v>
       </c>
@@ -16038,7 +16038,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="849" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A849" s="0" t="s">
         <v>37</v>
       </c>
@@ -16052,7 +16052,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="850" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A850" s="0" t="s">
         <v>37</v>
       </c>
@@ -16066,7 +16066,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="851" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A851" s="0" t="s">
         <v>37</v>
       </c>
@@ -16080,7 +16080,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="852" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A852" s="0" t="s">
         <v>37</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="853" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A853" s="0" t="s">
         <v>37</v>
       </c>
@@ -16108,7 +16108,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="854" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A854" s="0" t="s">
         <v>37</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="855" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A855" s="0" t="s">
         <v>37</v>
       </c>
@@ -16136,7 +16136,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="856" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A856" s="0" t="s">
         <v>37</v>
       </c>
@@ -16150,7 +16150,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="857" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A857" s="0" t="s">
         <v>37</v>
       </c>
@@ -16164,7 +16164,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="858" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A858" s="0" t="s">
         <v>37</v>
       </c>
@@ -16178,7 +16178,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="859" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A859" s="0" t="s">
         <v>37</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="860" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A860" s="0" t="s">
         <v>37</v>
       </c>
@@ -16206,7 +16206,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="861" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A861" s="0" t="s">
         <v>37</v>
       </c>
@@ -16220,7 +16220,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="862" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A862" s="0" t="s">
         <v>37</v>
       </c>
@@ -16234,7 +16234,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="863" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A863" s="0" t="s">
         <v>37</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="864" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A864" s="0" t="s">
         <v>37</v>
       </c>
@@ -16262,7 +16262,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="865" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A865" s="0" t="s">
         <v>37</v>
       </c>
@@ -16276,7 +16276,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="866" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A866" s="0" t="s">
         <v>37</v>
       </c>
@@ -16290,7 +16290,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="867" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A867" s="0" t="s">
         <v>37</v>
       </c>
@@ -16304,7 +16304,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="868" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A868" s="0" t="s">
         <v>37</v>
       </c>
@@ -16318,7 +16318,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="869" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A869" s="0" t="s">
         <v>37</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="870" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A870" s="0" t="s">
         <v>37</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="871" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A871" s="0" t="s">
         <v>37</v>
       </c>
@@ -16360,7 +16360,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="872" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A872" s="0" t="s">
         <v>37</v>
       </c>
@@ -16374,7 +16374,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="873" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A873" s="0" t="s">
         <v>37</v>
       </c>
@@ -16388,7 +16388,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="874" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A874" s="0" t="s">
         <v>37</v>
       </c>
@@ -16402,7 +16402,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="875" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A875" s="0" t="s">
         <v>37</v>
       </c>
@@ -16416,7 +16416,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="876" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A876" s="0" t="s">
         <v>37</v>
       </c>
@@ -16430,7 +16430,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="877" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A877" s="0" t="s">
         <v>37</v>
       </c>
@@ -16444,7 +16444,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="878" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A878" s="0" t="s">
         <v>37</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="879" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A879" s="0" t="s">
         <v>37</v>
       </c>
@@ -16472,7 +16472,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="880" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A880" s="0" t="s">
         <v>37</v>
       </c>
@@ -16486,7 +16486,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="881" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A881" s="0" t="s">
         <v>37</v>
       </c>
@@ -16500,7 +16500,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="882" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A882" s="0" t="s">
         <v>37</v>
       </c>
@@ -16514,7 +16514,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="883" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A883" s="0" t="s">
         <v>37</v>
       </c>
@@ -16528,7 +16528,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="884" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A884" s="0" t="s">
         <v>37</v>
       </c>
@@ -16542,7 +16542,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="885" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A885" s="0" t="s">
         <v>37</v>
       </c>
@@ -16556,7 +16556,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="886" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A886" s="0" t="s">
         <v>37</v>
       </c>
@@ -16570,7 +16570,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="887" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A887" s="0" t="s">
         <v>37</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="888" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A888" s="0" t="s">
         <v>37</v>
       </c>
@@ -16598,7 +16598,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="889" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A889" s="0" t="s">
         <v>37</v>
       </c>
@@ -16612,7 +16612,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="890" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A890" s="0" t="s">
         <v>37</v>
       </c>
@@ -16626,7 +16626,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="891" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A891" s="0" t="s">
         <v>37</v>
       </c>
@@ -16640,7 +16640,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="892" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A892" s="0" t="s">
         <v>37</v>
       </c>
@@ -16654,7 +16654,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="893" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A893" s="0" t="s">
         <v>37</v>
       </c>
@@ -16668,7 +16668,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="894" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A894" s="0" t="s">
         <v>37</v>
       </c>
@@ -16682,7 +16682,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="895" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A895" s="0" t="s">
         <v>37</v>
       </c>
@@ -16696,7 +16696,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="896" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A896" s="0" t="s">
         <v>37</v>
       </c>
@@ -16707,7 +16707,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="897" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A897" s="0" t="s">
         <v>37</v>
       </c>
@@ -16718,7 +16718,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="898" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A898" s="0" t="s">
         <v>37</v>
       </c>
@@ -16729,7 +16729,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="899" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A899" s="0" t="s">
         <v>37</v>
       </c>
@@ -16740,7 +16740,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="900" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A900" s="0" t="s">
         <v>37</v>
       </c>
@@ -16751,7 +16751,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="901" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A901" s="0" t="s">
         <v>37</v>
       </c>
@@ -16762,7 +16762,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="902" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A902" s="0" t="s">
         <v>37</v>
       </c>
@@ -16773,7 +16773,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="903" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A903" s="0" t="s">
         <v>37</v>
       </c>
@@ -16784,7 +16784,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="904" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A904" s="0" t="s">
         <v>37</v>
       </c>
@@ -16795,7 +16795,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="905" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A905" s="0" t="s">
         <v>37</v>
       </c>
@@ -16806,7 +16806,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="906" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A906" s="0" t="s">
         <v>37</v>
       </c>
@@ -16817,7 +16817,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="907" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A907" s="0" t="s">
         <v>37</v>
       </c>
@@ -16828,7 +16828,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="908" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A908" s="0" t="s">
         <v>37</v>
       </c>
@@ -16839,7 +16839,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="909" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A909" s="0" t="s">
         <v>37</v>
       </c>
@@ -16850,7 +16850,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="910" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A910" s="0" t="s">
         <v>37</v>
       </c>
@@ -16861,7 +16861,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="911" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A911" s="0" t="s">
         <v>37</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="912" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A912" s="0" t="s">
         <v>37</v>
       </c>
@@ -16883,7 +16883,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="913" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A913" s="0" t="s">
         <v>37</v>
       </c>
@@ -16894,7 +16894,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="914" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A914" s="0" t="s">
         <v>37</v>
       </c>
@@ -16905,7 +16905,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="915" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A915" s="0" t="s">
         <v>37</v>
       </c>
@@ -16916,7 +16916,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="916" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A916" s="0" t="s">
         <v>37</v>
       </c>
@@ -16927,7 +16927,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="917" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A917" s="0" t="s">
         <v>37</v>
       </c>
@@ -16938,7 +16938,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="918" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A918" s="0" t="s">
         <v>37</v>
       </c>
@@ -16949,7 +16949,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="919" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A919" s="0" t="s">
         <v>37</v>
       </c>
@@ -16960,7 +16960,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="920" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A920" s="0" t="s">
         <v>37</v>
       </c>
@@ -16971,7 +16971,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="921" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A921" s="0" t="s">
         <v>37</v>
       </c>
@@ -16982,7 +16982,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="922" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A922" s="0" t="s">
         <v>37</v>
       </c>
@@ -16993,7 +16993,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="923" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A923" s="0" t="s">
         <v>37</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="924" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A924" s="0" t="s">
         <v>37</v>
       </c>
@@ -17015,7 +17015,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="925" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A925" s="0" t="s">
         <v>37</v>
       </c>
@@ -17026,7 +17026,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="926" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A926" s="0" t="s">
         <v>37</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="927" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A927" s="0" t="s">
         <v>37</v>
       </c>
@@ -17048,7 +17048,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="928" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A928" s="0" t="s">
         <v>37</v>
       </c>
@@ -17059,7 +17059,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="929" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A929" s="0" t="s">
         <v>37</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="930" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A930" s="0" t="s">
         <v>37</v>
       </c>
@@ -17081,7 +17081,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="931" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A931" s="0" t="s">
         <v>37</v>
       </c>
@@ -17092,7 +17092,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="932" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A932" s="0" t="s">
         <v>37</v>
       </c>
@@ -17103,7 +17103,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="933" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A933" s="0" t="s">
         <v>37</v>
       </c>
@@ -17114,7 +17114,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="934" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A934" s="0" t="s">
         <v>37</v>
       </c>
@@ -17125,7 +17125,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="935" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A935" s="0" t="s">
         <v>37</v>
       </c>
@@ -17136,7 +17136,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="936" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A936" s="0" t="s">
         <v>37</v>
       </c>
@@ -17147,7 +17147,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="937" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A937" s="0" t="s">
         <v>37</v>
       </c>
@@ -17158,7 +17158,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="938" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A938" s="0" t="s">
         <v>37</v>
       </c>
@@ -17169,7 +17169,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="939" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A939" s="0" t="s">
         <v>37</v>
       </c>
@@ -17180,7 +17180,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="940" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A940" s="0" t="s">
         <v>37</v>
       </c>
@@ -17191,7 +17191,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="941" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A941" s="0" t="s">
         <v>37</v>
       </c>
@@ -17202,7 +17202,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="942" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A942" s="0" t="s">
         <v>37</v>
       </c>
@@ -17213,7 +17213,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="943" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A943" s="0" t="s">
         <v>37</v>
       </c>
@@ -17224,7 +17224,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="944" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A944" s="0" t="s">
         <v>37</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="945" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A945" s="0" t="s">
         <v>37</v>
       </c>
@@ -17246,7 +17246,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="946" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A946" s="0" t="s">
         <v>37</v>
       </c>
@@ -17257,7 +17257,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="947" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A947" s="0" t="s">
         <v>37</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="948" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A948" s="0" t="s">
         <v>37</v>
       </c>
@@ -17279,7 +17279,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="949" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A949" s="0" t="s">
         <v>37</v>
       </c>
@@ -17290,7 +17290,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="950" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A950" s="0" t="s">
         <v>37</v>
       </c>
@@ -17301,7 +17301,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="951" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A951" s="0" t="s">
         <v>37</v>
       </c>
@@ -17312,7 +17312,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="952" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A952" s="0" t="s">
         <v>37</v>
       </c>
@@ -17323,7 +17323,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="953" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A953" s="0" t="s">
         <v>37</v>
       </c>
@@ -17334,7 +17334,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="954" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A954" s="0" t="s">
         <v>37</v>
       </c>
@@ -17345,7 +17345,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="955" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A955" s="0" t="s">
         <v>37</v>
       </c>
@@ -17356,7 +17356,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="956" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A956" s="0" t="s">
         <v>37</v>
       </c>
@@ -17367,7 +17367,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="957" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A957" s="0" t="s">
         <v>37</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="958" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A958" s="0" t="s">
         <v>37</v>
       </c>
@@ -17389,7 +17389,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="959" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A959" s="0" t="s">
         <v>37</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="960" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A960" s="0" t="s">
         <v>37</v>
       </c>
@@ -17411,7 +17411,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="961" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A961" s="0" t="s">
         <v>37</v>
       </c>
@@ -17422,962 +17422,14 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="1047621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047720" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047721" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047722" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047723" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047724" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047725" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047726" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047732" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047738" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047739" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047740" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047746" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047748" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047750" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047751" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047759" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047760" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047761" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047762" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047763" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047765" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047766" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047767" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047768" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047769" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047770" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047771" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047772" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047773" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047774" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047775" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047776" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047777" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047778" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047779" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047780" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047781" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047782" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047783" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047784" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047786" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047787" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047788" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047789" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047790" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047791" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047792" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047793" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047794" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047795" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047796" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047797" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047798" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047799" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047800" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047801" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047802" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047803" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047804" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047805" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047807" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047808" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047811" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047813" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047814" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047815" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047816" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047817" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047818" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047819" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047820" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047821" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047822" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047823" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047824" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047825" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047826" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047828" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047840" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047841" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047842" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047843" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047844" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047845" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047858" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047859" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047860" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047861" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047862" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047873" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047874" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047875" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047876" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047877" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047879" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047880" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047886" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047889" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047890" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047894" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047904" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047906" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048015" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048016" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048018" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048019" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048020" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048021" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048022" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048023" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048025" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048039" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048040" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048066" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048067" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048070" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048071" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048077" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048082" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048083" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048084" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048085" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048086" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048091" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048092" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048093" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048094" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048095" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048096" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048097" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048098" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048099" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A962" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B962" s="0" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/fix_values.xlsx
+++ b/data/fix_values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Anderson/Library/CloudStorage/GoogleDrive-anderson.brito@itps.org.br/Outros computadores/My Mac mini/google_drive/ITpS/projetos_itps/resp_pathogens/analyses/20230208_devsnake/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a033270622/Documents/GitHub/respat/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35611FF-8F21-ED47-BDFA-E23C0B3F8483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A99E60-49A4-034D-AEB2-88F74F472D03}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32880" yWindow="3180" windowWidth="15900" windowHeight="21720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32880" yWindow="-5520" windowWidth="15900" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18525,7 +18525,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1010" xr:uid="{DC9850CA-E5A9-DA4A-96CF-A9A3577752A5}"/>
+  <autoFilter ref="A1:D1010" xr:uid="{DC9850CA-E5A9-DA4A-96CF-A9A3577752A5}">
+    <sortState ref="A2:D1010">
+      <sortCondition descending="1" ref="A1:A1010"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/fix_values.xlsx
+++ b/data/fix_values.xlsx
@@ -10,14 +10,14 @@
     <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">=Sheet1!$A$1:$D$1022</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">=Sheet1!$A$1:$D$1023</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4088" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4092" uniqueCount="1397">
   <si>
     <t>lab_id</t>
   </si>
@@ -4058,6 +4058,9 @@
   </si>
   <si>
     <t>GO</t>
+  </si>
+  <si>
+    <t>GOIÁS</t>
   </si>
   <si>
     <t>GOIAS</t>
@@ -4260,7 +4263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4269,9 +4272,6 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -4582,17 +4582,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E1022"/>
+  <dimension ref="A1:E1023"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="18.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="51.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="18.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="51.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="28.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25" hidden="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25" hidden="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25" hidden="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25" hidden="1">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25" hidden="1">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25" hidden="1">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25" hidden="1">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25" hidden="1">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -4726,24 +4726,24 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25" hidden="1">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25" hidden="1">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -4760,14 +4760,14 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
-      <c r="A11" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25" hidden="1">
+      <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -4777,14 +4777,14 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
-      <c r="A12" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25" hidden="1">
+      <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -4794,7 +4794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25" hidden="1">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25" hidden="1">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25" hidden="1">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -4845,14 +4845,14 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
-      <c r="A16" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25" hidden="1">
+      <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -4862,14 +4862,14 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
-      <c r="A17" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25" hidden="1">
+      <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -4879,7 +4879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25" hidden="1">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25" hidden="1">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25" hidden="1">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -4930,41 +4930,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
-      <c r="A21" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25" hidden="1">
+      <c r="A21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
-      <c r="A22" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25" hidden="1">
+      <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25" hidden="1">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25" hidden="1">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25" hidden="1">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
@@ -5015,41 +5015,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
-      <c r="A26" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25" hidden="1">
+      <c r="A26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
-      <c r="A27" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25" hidden="1">
+      <c r="A27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25" hidden="1">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25" hidden="1">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25" hidden="1">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
@@ -5100,41 +5100,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
-      <c r="A31" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25" hidden="1">
+      <c r="A31" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
-      <c r="A32" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25" hidden="1">
+      <c r="A32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25" hidden="1">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25" hidden="1">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25" hidden="1">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
@@ -5185,41 +5185,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
-      <c r="A36" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25" hidden="1">
+      <c r="A36" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
-      <c r="A37" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25" hidden="1">
+      <c r="A37" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25" hidden="1">
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25" hidden="1">
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25" hidden="1">
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
@@ -5270,41 +5270,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
-      <c r="A41" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25" hidden="1">
+      <c r="A41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
-      <c r="A42" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25" hidden="1">
+      <c r="A42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25" hidden="1">
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25" hidden="1">
       <c r="A44" s="1" t="s">
         <v>4</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25" hidden="1">
       <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
@@ -5355,41 +5355,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
-      <c r="A46" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25" hidden="1">
+      <c r="A46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
-      <c r="A47" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25" hidden="1">
+      <c r="A47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25" hidden="1">
       <c r="A48" s="1" t="s">
         <v>4</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25" hidden="1">
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25" hidden="1">
       <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
@@ -5440,41 +5440,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
-      <c r="A51" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25" hidden="1">
+      <c r="A51" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
-      <c r="A52" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25" hidden="1">
+      <c r="A52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25" hidden="1">
       <c r="A53" s="1" t="s">
         <v>4</v>
       </c>
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25" hidden="1">
       <c r="A54" s="1" t="s">
         <v>4</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25" hidden="1">
       <c r="A55" s="1" t="s">
         <v>4</v>
       </c>
@@ -5525,41 +5525,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
-      <c r="A56" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25" hidden="1">
+      <c r="A56" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
-      <c r="A57" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25" hidden="1">
+      <c r="A57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25" hidden="1">
       <c r="A58" s="1" t="s">
         <v>4</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25" hidden="1">
       <c r="A59" s="1" t="s">
         <v>4</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25" hidden="1">
       <c r="A60" s="1" t="s">
         <v>4</v>
       </c>
@@ -5610,41 +5610,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
-      <c r="A61" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25" hidden="1">
+      <c r="A61" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
-      <c r="A62" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25" hidden="1">
+      <c r="A62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25" hidden="1">
       <c r="A63" s="1" t="s">
         <v>4</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25" hidden="1">
       <c r="A64" s="1" t="s">
         <v>4</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25" hidden="1">
       <c r="A65" s="1" t="s">
         <v>4</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25" hidden="1">
       <c r="A66" s="1" t="s">
         <v>32</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25" hidden="1">
       <c r="A67" s="1" t="s">
         <v>32</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25" hidden="1">
       <c r="A68" s="1" t="s">
         <v>32</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25" hidden="1">
       <c r="A69" s="1" t="s">
         <v>32</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25" hidden="1">
       <c r="A70" s="1" t="s">
         <v>32</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25" hidden="1">
       <c r="A71" s="1" t="s">
         <v>32</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25" hidden="1">
       <c r="A72" s="1" t="s">
         <v>32</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25" hidden="1">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25" hidden="1">
       <c r="A74" s="1" t="s">
         <v>32</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25" hidden="1">
       <c r="A75" s="1" t="s">
         <v>35</v>
       </c>
@@ -5858,10 +5858,10 @@
       <c r="C75" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D75" s="3"/>
+      <c r="D75" s="1"/>
       <c r="E75" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25" hidden="1">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E76" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25" hidden="1">
       <c r="A77" s="1" t="s">
         <v>35</v>
       </c>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25" hidden="1">
       <c r="A78" s="1" t="s">
         <v>35</v>
       </c>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25" hidden="1">
       <c r="A79" s="1" t="s">
         <v>35</v>
       </c>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25" hidden="1">
       <c r="A80" s="1" t="s">
         <v>35</v>
       </c>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25" hidden="1">
       <c r="A81" s="1" t="s">
         <v>35</v>
       </c>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25" hidden="1">
       <c r="A82" s="1" t="s">
         <v>35</v>
       </c>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25" hidden="1">
       <c r="A83" s="1" t="s">
         <v>35</v>
       </c>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25" hidden="1">
       <c r="A84" s="1" t="s">
         <v>35</v>
       </c>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25" hidden="1">
       <c r="A85" s="1" t="s">
         <v>35</v>
       </c>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="E85" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25" hidden="1">
       <c r="A86" s="1" t="s">
         <v>35</v>
       </c>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25" hidden="1">
       <c r="A87" s="1" t="s">
         <v>35</v>
       </c>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25" hidden="1">
       <c r="A88" s="1" t="s">
         <v>35</v>
       </c>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25" hidden="1">
       <c r="A89" s="1" t="s">
         <v>35</v>
       </c>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25" hidden="1">
       <c r="A90" s="1" t="s">
         <v>35</v>
       </c>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E90" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25" hidden="1">
       <c r="A91" s="1" t="s">
         <v>35</v>
       </c>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E91" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25" hidden="1">
       <c r="A92" s="1" t="s">
         <v>35</v>
       </c>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E92" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25" hidden="1">
       <c r="A93" s="1" t="s">
         <v>35</v>
       </c>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="E93" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25" hidden="1">
       <c r="A94" s="1" t="s">
         <v>35</v>
       </c>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25" hidden="1">
       <c r="A95" s="1" t="s">
         <v>35</v>
       </c>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25" hidden="1">
       <c r="A96" s="1" t="s">
         <v>35</v>
       </c>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25" hidden="1">
       <c r="A97" s="1" t="s">
         <v>35</v>
       </c>
@@ -6186,10 +6186,10 @@
       <c r="C97" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D97" s="3"/>
+      <c r="D97" s="1"/>
       <c r="E97" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25" hidden="1">
       <c r="A98" s="1" t="s">
         <v>35</v>
       </c>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="E98" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25" hidden="1">
       <c r="A99" s="1" t="s">
         <v>35</v>
       </c>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="E99" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25" hidden="1">
       <c r="A100" s="1" t="s">
         <v>35</v>
       </c>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25" hidden="1">
       <c r="A101" s="1" t="s">
         <v>35</v>
       </c>
@@ -6244,10 +6244,10 @@
       <c r="C101" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D101" s="3"/>
+      <c r="D101" s="1"/>
       <c r="E101" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25" hidden="1">
       <c r="A102" s="1" t="s">
         <v>35</v>
       </c>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25" hidden="1">
       <c r="A103" s="1" t="s">
         <v>35</v>
       </c>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25" hidden="1">
       <c r="A104" s="1" t="s">
         <v>35</v>
       </c>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25" hidden="1">
       <c r="A105" s="1" t="s">
         <v>35</v>
       </c>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25" hidden="1">
       <c r="A106" s="1" t="s">
         <v>35</v>
       </c>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E106" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25" hidden="1">
       <c r="A107" s="1" t="s">
         <v>35</v>
       </c>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="E107" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25" hidden="1">
       <c r="A108" s="1" t="s">
         <v>35</v>
       </c>
@@ -6347,10 +6347,10 @@
       <c r="C108" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D108" s="3"/>
+      <c r="D108" s="1"/>
       <c r="E108" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25" hidden="1">
       <c r="A109" s="1" t="s">
         <v>35</v>
       </c>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E109" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25" hidden="1">
       <c r="A110" s="1" t="s">
         <v>35</v>
       </c>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="E110" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25" hidden="1">
       <c r="A111" s="1" t="s">
         <v>35</v>
       </c>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="E111" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25" hidden="1">
       <c r="A112" s="1" t="s">
         <v>35</v>
       </c>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="E112" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25" hidden="1">
       <c r="A113" s="1" t="s">
         <v>35</v>
       </c>
@@ -6420,10 +6420,10 @@
       <c r="C113" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D113" s="3"/>
+      <c r="D113" s="1"/>
       <c r="E113" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25" hidden="1">
       <c r="A114" s="1" t="s">
         <v>35</v>
       </c>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E114" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25" hidden="1">
       <c r="A115" s="1" t="s">
         <v>35</v>
       </c>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="E115" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25" hidden="1">
       <c r="A116" s="1" t="s">
         <v>35</v>
       </c>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="E116" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25" hidden="1">
       <c r="A117" s="1" t="s">
         <v>35</v>
       </c>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="E117" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25" hidden="1">
       <c r="A118" s="1" t="s">
         <v>35</v>
       </c>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="E118" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25" hidden="1">
       <c r="A119" s="1" t="s">
         <v>35</v>
       </c>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E119" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25" hidden="1">
       <c r="A120" s="1" t="s">
         <v>35</v>
       </c>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="E120" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25" hidden="1">
       <c r="A121" s="1" t="s">
         <v>35</v>
       </c>
@@ -6538,10 +6538,10 @@
       <c r="C121" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D121" s="3"/>
+      <c r="D121" s="1"/>
       <c r="E121" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25" hidden="1">
       <c r="A122" s="1" t="s">
         <v>35</v>
       </c>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="E122" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25" hidden="1">
       <c r="A123" s="1" t="s">
         <v>35</v>
       </c>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E123" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25" hidden="1">
       <c r="A124" s="1" t="s">
         <v>35</v>
       </c>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="E124" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25" hidden="1">
       <c r="A125" s="1" t="s">
         <v>35</v>
       </c>
@@ -6596,10 +6596,10 @@
       <c r="C125" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D125" s="3"/>
+      <c r="D125" s="1"/>
       <c r="E125" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25" hidden="1">
       <c r="A126" s="1" t="s">
         <v>35</v>
       </c>
@@ -6609,10 +6609,10 @@
       <c r="C126" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D126" s="3"/>
+      <c r="D126" s="1"/>
       <c r="E126" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25" hidden="1">
       <c r="A127" s="1" t="s">
         <v>35</v>
       </c>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E127" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25" hidden="1">
       <c r="A128" s="1" t="s">
         <v>35</v>
       </c>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="E128" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25" hidden="1">
       <c r="A129" s="1" t="s">
         <v>35</v>
       </c>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="E129" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25" hidden="1">
       <c r="A130" s="1" t="s">
         <v>35</v>
       </c>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="E130" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25" hidden="1">
       <c r="A131" s="1" t="s">
         <v>35</v>
       </c>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E131" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25" hidden="1">
       <c r="A132" s="1" t="s">
         <v>35</v>
       </c>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="E132" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25" hidden="1">
       <c r="A133" s="1" t="s">
         <v>35</v>
       </c>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="E133" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25" hidden="1">
       <c r="A134" s="1" t="s">
         <v>35</v>
       </c>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E134" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25" hidden="1">
       <c r="A135" s="1" t="s">
         <v>35</v>
       </c>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="E135" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25" hidden="1">
       <c r="A136" s="1" t="s">
         <v>35</v>
       </c>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E136" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25" hidden="1">
       <c r="A137" s="1" t="s">
         <v>35</v>
       </c>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="E137" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25" hidden="1">
       <c r="A138" s="1" t="s">
         <v>35</v>
       </c>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="E138" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25" hidden="1">
       <c r="A139" s="1" t="s">
         <v>35</v>
       </c>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="E139" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25" hidden="1">
       <c r="A140" s="1" t="s">
         <v>35</v>
       </c>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="E140" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25" hidden="1">
       <c r="A141" s="1" t="s">
         <v>35</v>
       </c>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="E141" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25" hidden="1">
       <c r="A142" s="1" t="s">
         <v>35</v>
       </c>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="E142" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25" hidden="1">
       <c r="A143" s="1" t="s">
         <v>35</v>
       </c>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="E143" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25" hidden="1">
       <c r="A144" s="1" t="s">
         <v>35</v>
       </c>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E144" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25" hidden="1">
       <c r="A145" s="1" t="s">
         <v>35</v>
       </c>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="E145" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25" hidden="1">
       <c r="A146" s="1" t="s">
         <v>35</v>
       </c>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E146" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25" hidden="1">
       <c r="A147" s="1" t="s">
         <v>35</v>
       </c>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="E147" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25" hidden="1">
       <c r="A148" s="1" t="s">
         <v>35</v>
       </c>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="E148" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25" hidden="1">
       <c r="A149" s="1" t="s">
         <v>35</v>
       </c>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="E149" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25" hidden="1">
       <c r="A150" s="1" t="s">
         <v>35</v>
       </c>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="E150" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25" hidden="1">
       <c r="A151" s="1" t="s">
         <v>35</v>
       </c>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="E151" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25" hidden="1">
       <c r="A152" s="1" t="s">
         <v>35</v>
       </c>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="E152" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25" hidden="1">
       <c r="A153" s="1" t="s">
         <v>35</v>
       </c>
@@ -7012,10 +7012,10 @@
       <c r="C153" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D153" s="3"/>
+      <c r="D153" s="1"/>
       <c r="E153" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25" hidden="1">
       <c r="A154" s="1" t="s">
         <v>35</v>
       </c>
@@ -7025,10 +7025,10 @@
       <c r="C154" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D154" s="3"/>
+      <c r="D154" s="1"/>
       <c r="E154" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25" hidden="1">
       <c r="A155" s="1" t="s">
         <v>35</v>
       </c>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="E155" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25" hidden="1">
       <c r="A156" s="1" t="s">
         <v>35</v>
       </c>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="E156" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25" hidden="1">
       <c r="A157" s="1" t="s">
         <v>35</v>
       </c>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="E157" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25" hidden="1">
       <c r="A158" s="1" t="s">
         <v>35</v>
       </c>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="E158" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25" hidden="1">
       <c r="A159" s="1" t="s">
         <v>35</v>
       </c>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="E159" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25" hidden="1">
       <c r="A160" s="1" t="s">
         <v>35</v>
       </c>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="E160" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25" hidden="1">
       <c r="A161" s="1" t="s">
         <v>35</v>
       </c>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="E161" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25" hidden="1">
       <c r="A162" s="1" t="s">
         <v>35</v>
       </c>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="E162" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25" hidden="1">
       <c r="A163" s="1" t="s">
         <v>35</v>
       </c>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="E163" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25" hidden="1">
       <c r="A164" s="1" t="s">
         <v>35</v>
       </c>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="E164" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25" hidden="1">
       <c r="A165" s="1" t="s">
         <v>35</v>
       </c>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E165" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25" hidden="1">
       <c r="A166" s="1" t="s">
         <v>35</v>
       </c>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="E166" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25" hidden="1">
       <c r="A167" s="1" t="s">
         <v>35</v>
       </c>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="E167" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25" hidden="1">
       <c r="A168" s="1" t="s">
         <v>35</v>
       </c>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="E168" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25" hidden="1">
       <c r="A169" s="1" t="s">
         <v>35</v>
       </c>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="E169" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="17.25" hidden="1">
       <c r="A170" s="1" t="s">
         <v>35</v>
       </c>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="E170" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="17.25" hidden="1">
       <c r="A171" s="1" t="s">
         <v>35</v>
       </c>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="E171" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="17.25" hidden="1">
       <c r="A172" s="1" t="s">
         <v>35</v>
       </c>
@@ -7293,10 +7293,10 @@
       <c r="C172" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D172" s="3"/>
+      <c r="D172" s="1"/>
       <c r="E172" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="17.25" hidden="1">
       <c r="A173" s="1" t="s">
         <v>35</v>
       </c>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E173" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="17.25" hidden="1">
       <c r="A174" s="1" t="s">
         <v>35</v>
       </c>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="E174" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="17.25" hidden="1">
       <c r="A175" s="1" t="s">
         <v>35</v>
       </c>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="E175" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="17.25" hidden="1">
       <c r="A176" s="1" t="s">
         <v>35</v>
       </c>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="E176" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="17.25" hidden="1">
       <c r="A177" s="1" t="s">
         <v>35</v>
       </c>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E177" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="17.25" hidden="1">
       <c r="A178" s="1" t="s">
         <v>35</v>
       </c>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="E178" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="17.25" hidden="1">
       <c r="A179" s="1" t="s">
         <v>35</v>
       </c>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="E179" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="17.25" hidden="1">
       <c r="A180" s="1" t="s">
         <v>35</v>
       </c>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E180" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="17.25" hidden="1">
       <c r="A181" s="1" t="s">
         <v>35</v>
       </c>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="E181" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="17.25" hidden="1">
       <c r="A182" s="1" t="s">
         <v>35</v>
       </c>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="E182" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="17.25" hidden="1">
       <c r="A183" s="1" t="s">
         <v>35</v>
       </c>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="E183" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="17.25" hidden="1">
       <c r="A184" s="1" t="s">
         <v>35</v>
       </c>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="E184" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="17.25" hidden="1">
       <c r="A185" s="1" t="s">
         <v>35</v>
       </c>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E185" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="17.25" hidden="1">
       <c r="A186" s="1" t="s">
         <v>35</v>
       </c>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="E186" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="17.25" hidden="1">
       <c r="A187" s="1" t="s">
         <v>35</v>
       </c>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="E187" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="17.25" hidden="1">
       <c r="A188" s="1" t="s">
         <v>35</v>
       </c>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E188" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="17.25" hidden="1">
       <c r="A189" s="1" t="s">
         <v>35</v>
       </c>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="E189" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="17.25" hidden="1">
       <c r="A190" s="1" t="s">
         <v>35</v>
       </c>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="E190" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="17.25" hidden="1">
       <c r="A191" s="1" t="s">
         <v>35</v>
       </c>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="E191" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="17.25" hidden="1">
       <c r="A192" s="1" t="s">
         <v>35</v>
       </c>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="E192" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="17.25" hidden="1">
       <c r="A193" s="1" t="s">
         <v>35</v>
       </c>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="E193" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="17.25" hidden="1">
       <c r="A194" s="1" t="s">
         <v>35</v>
       </c>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E194" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="17.25" hidden="1">
       <c r="A195" s="1" t="s">
         <v>35</v>
       </c>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="E195" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="17.25" hidden="1">
       <c r="A196" s="1" t="s">
         <v>35</v>
       </c>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="E196" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="17.25" hidden="1">
       <c r="A197" s="1" t="s">
         <v>35</v>
       </c>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="E197" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="17.25" hidden="1">
       <c r="A198" s="1" t="s">
         <v>35</v>
       </c>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="E198" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="17.25" hidden="1">
       <c r="A199" s="1" t="s">
         <v>35</v>
       </c>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="E199" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="17.25" hidden="1">
       <c r="A200" s="1" t="s">
         <v>35</v>
       </c>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E200" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="17.25" hidden="1">
       <c r="A201" s="1" t="s">
         <v>35</v>
       </c>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E201" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25" hidden="1">
       <c r="A202" s="1" t="s">
         <v>35</v>
       </c>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="E202" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="17.25" hidden="1">
       <c r="A203" s="1" t="s">
         <v>35</v>
       </c>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="E203" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="17.25" hidden="1">
       <c r="A204" s="1" t="s">
         <v>35</v>
       </c>
@@ -7771,10 +7771,10 @@
       <c r="C204" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D204" s="3"/>
+      <c r="D204" s="1"/>
       <c r="E204" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25" hidden="1">
       <c r="A205" s="1" t="s">
         <v>35</v>
       </c>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="E205" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25" hidden="1">
       <c r="A206" s="1" t="s">
         <v>35</v>
       </c>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="E206" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25" hidden="1">
       <c r="A207" s="1" t="s">
         <v>35</v>
       </c>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="E207" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25" hidden="1">
       <c r="A208" s="1" t="s">
         <v>35</v>
       </c>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E208" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="17.25" hidden="1">
       <c r="A209" s="1" t="s">
         <v>35</v>
       </c>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="E209" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="17.25" hidden="1">
       <c r="A210" s="1" t="s">
         <v>35</v>
       </c>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="E210" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25" hidden="1">
       <c r="A211" s="1" t="s">
         <v>35</v>
       </c>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="E211" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25" hidden="1">
       <c r="A212" s="1" t="s">
         <v>35</v>
       </c>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="E212" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25" hidden="1">
       <c r="A213" s="1" t="s">
         <v>35</v>
       </c>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="E213" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25" hidden="1">
       <c r="A214" s="1" t="s">
         <v>35</v>
       </c>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="E214" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25" hidden="1">
       <c r="A215" s="1" t="s">
         <v>35</v>
       </c>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="E215" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25" hidden="1">
       <c r="A216" s="1" t="s">
         <v>35</v>
       </c>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="E216" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="17.25" hidden="1">
       <c r="A217" s="1" t="s">
         <v>35</v>
       </c>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="E217" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25" hidden="1">
       <c r="A218" s="1" t="s">
         <v>35</v>
       </c>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E218" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25" hidden="1">
       <c r="A219" s="1" t="s">
         <v>35</v>
       </c>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="E219" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="17.25" hidden="1">
       <c r="A220" s="1" t="s">
         <v>35</v>
       </c>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="E220" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25" hidden="1">
       <c r="A221" s="1" t="s">
         <v>35</v>
       </c>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="E221" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="17.25" hidden="1">
       <c r="A222" s="1" t="s">
         <v>35</v>
       </c>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E222" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="17.25" hidden="1">
       <c r="A223" s="1" t="s">
         <v>35</v>
       </c>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E223" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="17.25" hidden="1">
       <c r="A224" s="1" t="s">
         <v>35</v>
       </c>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="E224" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="17.25" hidden="1">
       <c r="A225" s="1" t="s">
         <v>35</v>
       </c>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="E225" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="17.25" hidden="1">
       <c r="A226" s="1" t="s">
         <v>35</v>
       </c>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="E226" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="17.25" hidden="1">
       <c r="A227" s="1" t="s">
         <v>35</v>
       </c>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="E227" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="17.25" hidden="1">
       <c r="A228" s="1" t="s">
         <v>35</v>
       </c>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="E228" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="17.25" hidden="1">
       <c r="A229" s="1" t="s">
         <v>35</v>
       </c>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="E229" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="17.25" hidden="1">
       <c r="A230" s="1" t="s">
         <v>35</v>
       </c>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="E230" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="17.25" hidden="1">
       <c r="A231" s="1" t="s">
         <v>35</v>
       </c>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="E231" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="17.25" hidden="1">
       <c r="A232" s="1" t="s">
         <v>35</v>
       </c>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E232" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="17.25" hidden="1">
       <c r="A233" s="1" t="s">
         <v>35</v>
       </c>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E233" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="17.25" hidden="1">
       <c r="A234" s="1" t="s">
         <v>35</v>
       </c>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="E234" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="17.25" hidden="1">
       <c r="A235" s="1" t="s">
         <v>35</v>
       </c>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="E235" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="17.25" hidden="1">
       <c r="A236" s="1" t="s">
         <v>35</v>
       </c>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="E236" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="17.25" hidden="1">
       <c r="A237" s="1" t="s">
         <v>35</v>
       </c>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="E237" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="17.25" hidden="1">
       <c r="A238" s="1" t="s">
         <v>35</v>
       </c>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="E238" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="17.25" hidden="1">
       <c r="A239" s="1" t="s">
         <v>35</v>
       </c>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="E239" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="17.25" hidden="1">
       <c r="A240" s="1" t="s">
         <v>35</v>
       </c>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="E240" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="17.25" hidden="1">
       <c r="A241" s="1" t="s">
         <v>35</v>
       </c>
@@ -8324,10 +8324,10 @@
       <c r="C241" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D241" s="3"/>
+      <c r="D241" s="1"/>
       <c r="E241" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="17.25" hidden="1">
       <c r="A242" s="1" t="s">
         <v>35</v>
       </c>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="E242" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="17.25" hidden="1">
       <c r="A243" s="1" t="s">
         <v>35</v>
       </c>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="E243" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="17.25" hidden="1">
       <c r="A244" s="1" t="s">
         <v>35</v>
       </c>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E244" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="17.25" hidden="1">
       <c r="A245" s="1" t="s">
         <v>35</v>
       </c>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="E245" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="17.25" hidden="1">
       <c r="A246" s="1" t="s">
         <v>35</v>
       </c>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="E246" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="17.25" hidden="1">
       <c r="A247" s="1" t="s">
         <v>35</v>
       </c>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="E247" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="17.25" hidden="1">
       <c r="A248" s="1" t="s">
         <v>35</v>
       </c>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="E248" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="17.25" hidden="1">
       <c r="A249" s="1" t="s">
         <v>35</v>
       </c>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="E249" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="17.25" hidden="1">
       <c r="A250" s="1" t="s">
         <v>35</v>
       </c>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="E250" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="17.25" hidden="1">
       <c r="A251" s="1" t="s">
         <v>35</v>
       </c>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="E251" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="17.25" hidden="1">
       <c r="A252" s="1" t="s">
         <v>35</v>
       </c>
@@ -8487,10 +8487,10 @@
       <c r="C252" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D252" s="3"/>
+      <c r="D252" s="1"/>
       <c r="E252" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="17.25" hidden="1">
       <c r="A253" s="1" t="s">
         <v>35</v>
       </c>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="E253" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="17.25" hidden="1">
       <c r="A254" s="1" t="s">
         <v>35</v>
       </c>
@@ -8515,10 +8515,10 @@
       <c r="C254" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D254" s="3"/>
+      <c r="D254" s="1"/>
       <c r="E254" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="17.25" hidden="1">
       <c r="A255" s="1" t="s">
         <v>35</v>
       </c>
@@ -8528,10 +8528,10 @@
       <c r="C255" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D255" s="3"/>
+      <c r="D255" s="1"/>
       <c r="E255" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="17.25" hidden="1">
       <c r="A256" s="1" t="s">
         <v>35</v>
       </c>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="E256" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="17.25" hidden="1">
       <c r="A257" s="1" t="s">
         <v>35</v>
       </c>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="E257" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="17.25" hidden="1">
       <c r="A258" s="1" t="s">
         <v>35</v>
       </c>
@@ -8571,10 +8571,10 @@
       <c r="C258" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D258" s="3"/>
+      <c r="D258" s="1"/>
       <c r="E258" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="17.25" hidden="1">
       <c r="A259" s="1" t="s">
         <v>35</v>
       </c>
@@ -8584,10 +8584,10 @@
       <c r="C259" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D259" s="3"/>
+      <c r="D259" s="1"/>
       <c r="E259" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="17.25" hidden="1">
       <c r="A260" s="1" t="s">
         <v>35</v>
       </c>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="E260" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="17.25" hidden="1">
       <c r="A261" s="1" t="s">
         <v>35</v>
       </c>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="E261" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="17.25" hidden="1">
       <c r="A262" s="1" t="s">
         <v>35</v>
       </c>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="E262" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="17.25" hidden="1">
       <c r="A263" s="1" t="s">
         <v>35</v>
       </c>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="E263" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="17.25" hidden="1">
       <c r="A264" s="1" t="s">
         <v>35</v>
       </c>
@@ -8657,10 +8657,10 @@
       <c r="C264" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D264" s="3"/>
+      <c r="D264" s="1"/>
       <c r="E264" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="17.25" hidden="1">
       <c r="A265" s="1" t="s">
         <v>35</v>
       </c>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="E265" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="17.25" hidden="1">
       <c r="A266" s="1" t="s">
         <v>35</v>
       </c>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="E266" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="17.25" hidden="1">
       <c r="A267" s="1" t="s">
         <v>35</v>
       </c>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E267" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="17.25" hidden="1">
       <c r="A268" s="1" t="s">
         <v>35</v>
       </c>
@@ -8715,10 +8715,10 @@
       <c r="C268" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D268" s="3"/>
+      <c r="D268" s="1"/>
       <c r="E268" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="17.25" hidden="1">
       <c r="A269" s="1" t="s">
         <v>35</v>
       </c>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="E269" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="17.25" hidden="1">
       <c r="A270" s="1" t="s">
         <v>35</v>
       </c>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="E270" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="17.25" hidden="1">
       <c r="A271" s="1" t="s">
         <v>35</v>
       </c>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="E271" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="17.25" hidden="1">
       <c r="A272" s="1" t="s">
         <v>35</v>
       </c>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E272" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="17.25" hidden="1">
       <c r="A273" s="1" t="s">
         <v>35</v>
       </c>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="E273" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="17.25" hidden="1">
       <c r="A274" s="1" t="s">
         <v>35</v>
       </c>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="E274" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="17.25" hidden="1">
       <c r="A275" s="1" t="s">
         <v>35</v>
       </c>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E275" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="17.25" hidden="1">
       <c r="A276" s="1" t="s">
         <v>35</v>
       </c>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="E276" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="17.25" hidden="1">
       <c r="A277" s="1" t="s">
         <v>35</v>
       </c>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="E277" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="17.25" hidden="1">
       <c r="A278" s="1" t="s">
         <v>35</v>
       </c>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="E278" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="17.25" hidden="1">
       <c r="A279" s="1" t="s">
         <v>35</v>
       </c>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="E279" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="17.25" hidden="1">
       <c r="A280" s="1" t="s">
         <v>35</v>
       </c>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="E280" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="17.25" hidden="1">
       <c r="A281" s="1" t="s">
         <v>35</v>
       </c>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="E281" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="17.25" hidden="1">
       <c r="A282" s="1" t="s">
         <v>35</v>
       </c>
@@ -8923,10 +8923,10 @@
       <c r="C282" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D282" s="3"/>
+      <c r="D282" s="1"/>
       <c r="E282" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="17.25" hidden="1">
       <c r="A283" s="1" t="s">
         <v>35</v>
       </c>
@@ -8936,10 +8936,10 @@
       <c r="C283" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D283" s="3"/>
+      <c r="D283" s="1"/>
       <c r="E283" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="17.25" hidden="1">
       <c r="A284" s="1" t="s">
         <v>35</v>
       </c>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="E284" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="17.25" hidden="1">
       <c r="A285" s="1" t="s">
         <v>35</v>
       </c>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="E285" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="17.25" hidden="1">
       <c r="A286" s="1" t="s">
         <v>35</v>
       </c>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="E286" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="17.25" hidden="1">
       <c r="A287" s="1" t="s">
         <v>35</v>
       </c>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="E287" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="17.25" hidden="1">
       <c r="A288" s="1" t="s">
         <v>35</v>
       </c>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="E288" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="17.25" hidden="1">
       <c r="A289" s="1" t="s">
         <v>35</v>
       </c>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="E289" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="17.25" hidden="1">
       <c r="A290" s="1" t="s">
         <v>35</v>
       </c>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="E290" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="17.25" hidden="1">
       <c r="A291" s="1" t="s">
         <v>35</v>
       </c>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="E291" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="17.25" hidden="1">
       <c r="A292" s="1" t="s">
         <v>35</v>
       </c>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="E292" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="17.25" hidden="1">
       <c r="A293" s="1" t="s">
         <v>35</v>
       </c>
@@ -9084,10 +9084,10 @@
       <c r="C293" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D293" s="3"/>
+      <c r="D293" s="1"/>
       <c r="E293" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="17.25" hidden="1">
       <c r="A294" s="1" t="s">
         <v>35</v>
       </c>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="E294" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="17.25" hidden="1">
       <c r="A295" s="1" t="s">
         <v>35</v>
       </c>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="E295" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="17.25" hidden="1">
       <c r="A296" s="1" t="s">
         <v>35</v>
       </c>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="E296" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="17.25" hidden="1">
       <c r="A297" s="1" t="s">
         <v>35</v>
       </c>
@@ -9142,10 +9142,10 @@
       <c r="C297" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D297" s="3"/>
+      <c r="D297" s="1"/>
       <c r="E297" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="17.25" hidden="1">
       <c r="A298" s="1" t="s">
         <v>35</v>
       </c>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="E298" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="17.25" hidden="1">
       <c r="A299" s="1" t="s">
         <v>35</v>
       </c>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E299" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="17.25" hidden="1">
       <c r="A300" s="1" t="s">
         <v>35</v>
       </c>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="E300" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="17.25" hidden="1">
       <c r="A301" s="1" t="s">
         <v>35</v>
       </c>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="E301" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="17.25" hidden="1">
       <c r="A302" s="1" t="s">
         <v>35</v>
       </c>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="E302" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="17.25" hidden="1">
       <c r="A303" s="1" t="s">
         <v>35</v>
       </c>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="E303" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="17.25" hidden="1">
       <c r="A304" s="1" t="s">
         <v>35</v>
       </c>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="E304" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="17.25" hidden="1">
       <c r="A305" s="1" t="s">
         <v>35</v>
       </c>
@@ -9260,10 +9260,10 @@
       <c r="C305" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D305" s="3"/>
+      <c r="D305" s="1"/>
       <c r="E305" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="17.25" hidden="1">
       <c r="A306" s="1" t="s">
         <v>35</v>
       </c>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="E306" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="17.25" hidden="1">
       <c r="A307" s="1" t="s">
         <v>35</v>
       </c>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="E307" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="17.25" hidden="1">
       <c r="A308" s="1" t="s">
         <v>35</v>
       </c>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="E308" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="17.25" hidden="1">
       <c r="A309" s="1" t="s">
         <v>35</v>
       </c>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="E309" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="17.25" hidden="1">
       <c r="A310" s="1" t="s">
         <v>35</v>
       </c>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="E310" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="17.25" hidden="1">
       <c r="A311" s="1" t="s">
         <v>35</v>
       </c>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="E311" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="17.25" hidden="1">
       <c r="A312" s="1" t="s">
         <v>35</v>
       </c>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="E312" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="17.25" hidden="1">
       <c r="A313" s="1" t="s">
         <v>35</v>
       </c>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E313" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="17.25" hidden="1">
       <c r="A314" s="1" t="s">
         <v>35</v>
       </c>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="E314" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="17.25" hidden="1">
       <c r="A315" s="1" t="s">
         <v>35</v>
       </c>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="E315" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="17.25" hidden="1">
       <c r="A316" s="1" t="s">
         <v>35</v>
       </c>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="E316" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="17.25" hidden="1">
       <c r="A317" s="1" t="s">
         <v>35</v>
       </c>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="E317" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="17.25" hidden="1">
       <c r="A318" s="1" t="s">
         <v>35</v>
       </c>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="E318" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="17.25" hidden="1">
       <c r="A319" s="1" t="s">
         <v>35</v>
       </c>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="E319" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="17.25" hidden="1">
       <c r="A320" s="1" t="s">
         <v>35</v>
       </c>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="E320" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="17.25" hidden="1">
       <c r="A321" s="1" t="s">
         <v>35</v>
       </c>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="E321" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="17.25" hidden="1">
       <c r="A322" s="1" t="s">
         <v>35</v>
       </c>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="E322" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="17.25" hidden="1">
       <c r="A323" s="1" t="s">
         <v>35</v>
       </c>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="E323" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="17.25" hidden="1">
       <c r="A324" s="1" t="s">
         <v>35</v>
       </c>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E324" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="17.25" hidden="1">
       <c r="A325" s="1" t="s">
         <v>35</v>
       </c>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="E325" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="17.25" hidden="1">
       <c r="A326" s="1" t="s">
         <v>35</v>
       </c>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="E326" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="17.25" hidden="1">
       <c r="A327" s="1" t="s">
         <v>35</v>
       </c>
@@ -9588,10 +9588,10 @@
       <c r="C327" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D327" s="3"/>
+      <c r="D327" s="1"/>
       <c r="E327" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="17.25" hidden="1">
       <c r="A328" s="1" t="s">
         <v>35</v>
       </c>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="E328" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="17.25" hidden="1">
       <c r="A329" s="1" t="s">
         <v>35</v>
       </c>
@@ -9616,10 +9616,10 @@
       <c r="C329" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D329" s="3"/>
+      <c r="D329" s="1"/>
       <c r="E329" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="17.25" hidden="1">
       <c r="A330" s="1" t="s">
         <v>35</v>
       </c>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="E330" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="17.25" hidden="1">
       <c r="A331" s="1" t="s">
         <v>35</v>
       </c>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="E331" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="17.25" hidden="1">
       <c r="A332" s="1" t="s">
         <v>35</v>
       </c>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="E332" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="17.25" hidden="1">
       <c r="A333" s="1" t="s">
         <v>35</v>
       </c>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="E333" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="17.25" hidden="1">
       <c r="A334" s="1" t="s">
         <v>35</v>
       </c>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="E334" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="17.25" hidden="1">
       <c r="A335" s="1" t="s">
         <v>35</v>
       </c>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E335" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="17.25" hidden="1">
       <c r="A336" s="1" t="s">
         <v>35</v>
       </c>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="E336" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="17.25" hidden="1">
       <c r="A337" s="1" t="s">
         <v>35</v>
       </c>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E337" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="17.25" hidden="1">
       <c r="A338" s="1" t="s">
         <v>35</v>
       </c>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="E338" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="17.25" hidden="1">
       <c r="A339" s="1" t="s">
         <v>35</v>
       </c>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="E339" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="17.25" hidden="1">
       <c r="A340" s="1" t="s">
         <v>35</v>
       </c>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="E340" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="17.25" hidden="1">
       <c r="A341" s="1" t="s">
         <v>35</v>
       </c>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="E341" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="17.25" hidden="1">
       <c r="A342" s="1" t="s">
         <v>35</v>
       </c>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="E342" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="17.25" hidden="1">
       <c r="A343" s="1" t="s">
         <v>35</v>
       </c>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="E343" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="17.25" hidden="1">
       <c r="A344" s="1" t="s">
         <v>35</v>
       </c>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="E344" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="17.25" hidden="1">
       <c r="A345" s="1" t="s">
         <v>35</v>
       </c>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="E345" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="17.25" hidden="1">
       <c r="A346" s="1" t="s">
         <v>35</v>
       </c>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="E346" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="17.25" hidden="1">
       <c r="A347" s="1" t="s">
         <v>35</v>
       </c>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E347" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="17.25" hidden="1">
       <c r="A348" s="1" t="s">
         <v>35</v>
       </c>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="E348" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="17.25" hidden="1">
       <c r="A349" s="1" t="s">
         <v>35</v>
       </c>
@@ -9914,10 +9914,10 @@
       <c r="C349" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D349" s="3"/>
+      <c r="D349" s="1"/>
       <c r="E349" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="17.25" hidden="1">
       <c r="A350" s="1" t="s">
         <v>35</v>
       </c>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="E350" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="17.25" hidden="1">
       <c r="A351" s="1" t="s">
         <v>35</v>
       </c>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="E351" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="17.25" hidden="1">
       <c r="A352" s="1" t="s">
         <v>35</v>
       </c>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="E352" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="17.25" hidden="1">
       <c r="A353" s="1" t="s">
         <v>35</v>
       </c>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="E353" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="17.25" hidden="1">
       <c r="A354" s="1" t="s">
         <v>35</v>
       </c>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="E354" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="17.25" hidden="1">
       <c r="A355" s="1" t="s">
         <v>35</v>
       </c>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="E355" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="17.25" hidden="1">
       <c r="A356" s="1" t="s">
         <v>35</v>
       </c>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="E356" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="17.25" hidden="1">
       <c r="A357" s="1" t="s">
         <v>35</v>
       </c>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="E357" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="17.25" hidden="1">
       <c r="A358" s="1" t="s">
         <v>35</v>
       </c>
@@ -10047,10 +10047,10 @@
       <c r="C358" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="D358" s="3"/>
+      <c r="D358" s="1"/>
       <c r="E358" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="17.25" hidden="1">
       <c r="A359" s="1" t="s">
         <v>35</v>
       </c>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="E359" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="17.25" hidden="1">
       <c r="A360" s="1" t="s">
         <v>35</v>
       </c>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="E360" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="17.25" hidden="1">
       <c r="A361" s="1" t="s">
         <v>35</v>
       </c>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E361" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="17.25" hidden="1">
       <c r="A362" s="1" t="s">
         <v>35</v>
       </c>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="E362" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="17.25" hidden="1">
       <c r="A363" s="1" t="s">
         <v>35</v>
       </c>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E363" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="17.25" hidden="1">
       <c r="A364" s="1" t="s">
         <v>35</v>
       </c>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="E364" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="17.25" hidden="1">
       <c r="A365" s="1" t="s">
         <v>35</v>
       </c>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="E365" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="17.25" hidden="1">
       <c r="A366" s="1" t="s">
         <v>35</v>
       </c>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="E366" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="17.25" hidden="1">
       <c r="A367" s="1" t="s">
         <v>35</v>
       </c>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="E367" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="17.25" hidden="1">
       <c r="A368" s="1" t="s">
         <v>35</v>
       </c>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="E368" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="17.25" hidden="1">
       <c r="A369" s="1" t="s">
         <v>35</v>
       </c>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="E369" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="17.25" hidden="1">
       <c r="A370" s="1" t="s">
         <v>35</v>
       </c>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="E370" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="17.25" hidden="1">
       <c r="A371" s="1" t="s">
         <v>35</v>
       </c>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="E371" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="17.25" hidden="1">
       <c r="A372" s="1" t="s">
         <v>35</v>
       </c>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E372" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="17.25" hidden="1">
       <c r="A373" s="1" t="s">
         <v>35</v>
       </c>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="E373" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="17.25" hidden="1">
       <c r="A374" s="1" t="s">
         <v>35</v>
       </c>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="E374" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="17.25" hidden="1">
       <c r="A375" s="1" t="s">
         <v>35</v>
       </c>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="E375" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="17.25" hidden="1">
       <c r="A376" s="1" t="s">
         <v>35</v>
       </c>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="E376" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="17.25" hidden="1">
       <c r="A377" s="1" t="s">
         <v>35</v>
       </c>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="E377" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="17.25" hidden="1">
       <c r="A378" s="1" t="s">
         <v>35</v>
       </c>
@@ -10345,10 +10345,10 @@
       <c r="C378" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D378" s="3"/>
+      <c r="D378" s="1"/>
       <c r="E378" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="17.25" hidden="1">
       <c r="A379" s="1" t="s">
         <v>35</v>
       </c>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="E379" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="17.25" hidden="1">
       <c r="A380" s="1" t="s">
         <v>35</v>
       </c>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="E380" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="17.25" hidden="1">
       <c r="A381" s="1" t="s">
         <v>35</v>
       </c>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="E381" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="17.25" hidden="1">
       <c r="A382" s="1" t="s">
         <v>35</v>
       </c>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="E382" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="17.25" hidden="1">
       <c r="A383" s="1" t="s">
         <v>35</v>
       </c>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E383" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="17.25" hidden="1">
       <c r="A384" s="1" t="s">
         <v>35</v>
       </c>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="E384" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="17.25" hidden="1">
       <c r="A385" s="1" t="s">
         <v>35</v>
       </c>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="E385" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="17.25" hidden="1">
       <c r="A386" s="1" t="s">
         <v>35</v>
       </c>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E386" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="17.25" hidden="1">
       <c r="A387" s="1" t="s">
         <v>35</v>
       </c>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="E387" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="17.25" hidden="1">
       <c r="A388" s="1" t="s">
         <v>35</v>
       </c>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="E388" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="17.25" hidden="1">
       <c r="A389" s="1" t="s">
         <v>35</v>
       </c>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="E389" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="17.25" hidden="1">
       <c r="A390" s="1" t="s">
         <v>35</v>
       </c>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="E390" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="17.25" hidden="1">
       <c r="A391" s="1" t="s">
         <v>35</v>
       </c>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="E391" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="17.25" hidden="1">
       <c r="A392" s="1" t="s">
         <v>35</v>
       </c>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="E392" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="17.25" hidden="1">
       <c r="A393" s="1" t="s">
         <v>35</v>
       </c>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="E393" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="17.25" hidden="1">
       <c r="A394" s="1" t="s">
         <v>35</v>
       </c>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="E394" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="17.25" hidden="1">
       <c r="A395" s="1" t="s">
         <v>35</v>
       </c>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="E395" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="17.25" hidden="1">
       <c r="A396" s="1" t="s">
         <v>35</v>
       </c>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="E396" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="17.25" hidden="1">
       <c r="A397" s="1" t="s">
         <v>35</v>
       </c>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="E397" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="17.25" hidden="1">
       <c r="A398" s="1" t="s">
         <v>35</v>
       </c>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="E398" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="17.25" hidden="1">
       <c r="A399" s="1" t="s">
         <v>35</v>
       </c>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="E399" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="17.25" hidden="1">
       <c r="A400" s="1" t="s">
         <v>35</v>
       </c>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="E400" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="17.25" hidden="1">
       <c r="A401" s="1" t="s">
         <v>35</v>
       </c>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="E401" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="17.25" hidden="1">
       <c r="A402" s="1" t="s">
         <v>35</v>
       </c>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="E402" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="17.25" hidden="1">
       <c r="A403" s="1" t="s">
         <v>35</v>
       </c>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="E403" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="17.25" hidden="1">
       <c r="A404" s="1" t="s">
         <v>35</v>
       </c>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="E404" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="17.25" hidden="1">
       <c r="A405" s="1" t="s">
         <v>35</v>
       </c>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="E405" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="17.25" hidden="1">
       <c r="A406" s="1" t="s">
         <v>35</v>
       </c>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="E406" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="17.25" hidden="1">
       <c r="A407" s="1" t="s">
         <v>35</v>
       </c>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="E407" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="17.25" hidden="1">
       <c r="A408" s="1" t="s">
         <v>35</v>
       </c>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="E408" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="17.25" hidden="1">
       <c r="A409" s="1" t="s">
         <v>35</v>
       </c>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="E409" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="17.25" hidden="1">
       <c r="A410" s="1" t="s">
         <v>35</v>
       </c>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="E410" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="17.25" hidden="1">
       <c r="A411" s="1" t="s">
         <v>35</v>
       </c>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="E411" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="17.25" hidden="1">
       <c r="A412" s="1" t="s">
         <v>35</v>
       </c>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="E412" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="17.25" hidden="1">
       <c r="A413" s="1" t="s">
         <v>35</v>
       </c>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E413" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="17.25" hidden="1">
       <c r="A414" s="1" t="s">
         <v>35</v>
       </c>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="E414" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="17.25" hidden="1">
       <c r="A415" s="1" t="s">
         <v>35</v>
       </c>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E415" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="17.25" hidden="1">
       <c r="A416" s="1" t="s">
         <v>35</v>
       </c>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="E416" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="17.25" hidden="1">
       <c r="A417" s="1" t="s">
         <v>35</v>
       </c>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="E417" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="17.25" hidden="1">
       <c r="A418" s="1" t="s">
         <v>35</v>
       </c>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="E418" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="17.25" hidden="1">
       <c r="A419" s="1" t="s">
         <v>35</v>
       </c>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="E419" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="17.25" hidden="1">
       <c r="A420" s="1" t="s">
         <v>35</v>
       </c>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="E420" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="17.25" hidden="1">
       <c r="A421" s="1" t="s">
         <v>35</v>
       </c>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="E421" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="17.25" hidden="1">
       <c r="A422" s="1" t="s">
         <v>35</v>
       </c>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="E422" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="17.25" hidden="1">
       <c r="A423" s="1" t="s">
         <v>35</v>
       </c>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E423" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="17.25" hidden="1">
       <c r="A424" s="1" t="s">
         <v>35</v>
       </c>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="E424" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="17.25" hidden="1">
       <c r="A425" s="1" t="s">
         <v>35</v>
       </c>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="E425" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="17.25" hidden="1">
       <c r="A426" s="1" t="s">
         <v>35</v>
       </c>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="E426" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="17.25" hidden="1">
       <c r="A427" s="1" t="s">
         <v>35</v>
       </c>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="E427" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="17.25" hidden="1">
       <c r="A428" s="1" t="s">
         <v>35</v>
       </c>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="E428" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="17.25" hidden="1">
       <c r="A429" s="1" t="s">
         <v>35</v>
       </c>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="E429" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="17.25" hidden="1">
       <c r="A430" s="1" t="s">
         <v>35</v>
       </c>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E430" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="17.25" hidden="1">
       <c r="A431" s="1" t="s">
         <v>35</v>
       </c>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="E431" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="17.25" hidden="1">
       <c r="A432" s="1" t="s">
         <v>35</v>
       </c>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E432" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="17.25" hidden="1">
       <c r="A433" s="1" t="s">
         <v>35</v>
       </c>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="E433" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="17.25" hidden="1">
       <c r="A434" s="1" t="s">
         <v>35</v>
       </c>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="E434" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="17.25" hidden="1">
       <c r="A435" s="1" t="s">
         <v>35</v>
       </c>
@@ -11203,7 +11203,7 @@
       </c>
       <c r="E435" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="17.25" hidden="1">
       <c r="A436" s="1" t="s">
         <v>35</v>
       </c>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="E436" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="17.25" hidden="1">
       <c r="A437" s="1" t="s">
         <v>35</v>
       </c>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="E437" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="17.25" hidden="1">
       <c r="A438" s="1" t="s">
         <v>35</v>
       </c>
@@ -11248,7 +11248,7 @@
       </c>
       <c r="E438" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="17.25" hidden="1">
       <c r="A439" s="1" t="s">
         <v>35</v>
       </c>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="E439" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="17.25" hidden="1">
       <c r="A440" s="1" t="s">
         <v>35</v>
       </c>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="E440" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="17.25" hidden="1">
       <c r="A441" s="1" t="s">
         <v>35</v>
       </c>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="E441" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="17.25" hidden="1">
       <c r="A442" s="1" t="s">
         <v>35</v>
       </c>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="E442" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="17.25" hidden="1">
       <c r="A443" s="1" t="s">
         <v>35</v>
       </c>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="E443" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="17.25" hidden="1">
       <c r="A444" s="1" t="s">
         <v>35</v>
       </c>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="E444" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="17.25" hidden="1">
       <c r="A445" s="1" t="s">
         <v>35</v>
       </c>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="E445" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="17.25" hidden="1">
       <c r="A446" s="1" t="s">
         <v>35</v>
       </c>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="E446" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="17.25" hidden="1">
       <c r="A447" s="1" t="s">
         <v>35</v>
       </c>
@@ -11378,10 +11378,10 @@
       <c r="C447" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="D447" s="3"/>
+      <c r="D447" s="1"/>
       <c r="E447" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="17.25" hidden="1">
       <c r="A448" s="1" t="s">
         <v>35</v>
       </c>
@@ -11391,10 +11391,10 @@
       <c r="C448" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="D448" s="3"/>
+      <c r="D448" s="1"/>
       <c r="E448" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="17.25" hidden="1">
       <c r="A449" s="1" t="s">
         <v>35</v>
       </c>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="E449" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="17.25" hidden="1">
       <c r="A450" s="1" t="s">
         <v>35</v>
       </c>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="E450" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="17.25" hidden="1">
       <c r="A451" s="1" t="s">
         <v>35</v>
       </c>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="E451" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="17.25" hidden="1">
       <c r="A452" s="1" t="s">
         <v>35</v>
       </c>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="E452" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="17.25" hidden="1">
       <c r="A453" s="1" t="s">
         <v>35</v>
       </c>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E453" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="17.25" hidden="1">
       <c r="A454" s="1" t="s">
         <v>35</v>
       </c>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="E454" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="17.25" hidden="1">
       <c r="A455" s="1" t="s">
         <v>35</v>
       </c>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="E455" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="17.25" hidden="1">
       <c r="A456" s="1" t="s">
         <v>35</v>
       </c>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E456" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="17.25" hidden="1">
       <c r="A457" s="1" t="s">
         <v>35</v>
       </c>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E457" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="17.25" hidden="1">
       <c r="A458" s="1" t="s">
         <v>35</v>
       </c>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="E458" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="17.25" hidden="1">
       <c r="A459" s="1" t="s">
         <v>35</v>
       </c>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="E459" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="17.25" hidden="1">
       <c r="A460" s="1" t="s">
         <v>35</v>
       </c>
@@ -11574,7 +11574,7 @@
       </c>
       <c r="E460" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="17.25" hidden="1">
       <c r="A461" s="1" t="s">
         <v>35</v>
       </c>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="E461" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="17.25" hidden="1">
       <c r="A462" s="1" t="s">
         <v>35</v>
       </c>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="E462" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="17.25" hidden="1">
       <c r="A463" s="1" t="s">
         <v>35</v>
       </c>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="E463" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="17.25" hidden="1">
       <c r="A464" s="1" t="s">
         <v>35</v>
       </c>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="E464" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="17.25" hidden="1">
       <c r="A465" s="1" t="s">
         <v>35</v>
       </c>
@@ -11644,10 +11644,10 @@
       <c r="C465" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="D465" s="3"/>
+      <c r="D465" s="1"/>
       <c r="E465" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="17.25" hidden="1">
       <c r="A466" s="1" t="s">
         <v>35</v>
       </c>
@@ -11657,10 +11657,10 @@
       <c r="C466" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="D466" s="3"/>
+      <c r="D466" s="1"/>
       <c r="E466" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="17.25" hidden="1">
       <c r="A467" s="1" t="s">
         <v>35</v>
       </c>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E467" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="17.25" hidden="1">
       <c r="A468" s="1" t="s">
         <v>35</v>
       </c>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="E468" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="17.25" hidden="1">
       <c r="A469" s="1" t="s">
         <v>35</v>
       </c>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="E469" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="17.25" hidden="1">
       <c r="A470" s="1" t="s">
         <v>35</v>
       </c>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E470" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="17.25" hidden="1">
       <c r="A471" s="1" t="s">
         <v>35</v>
       </c>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="E471" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="17.25" hidden="1">
       <c r="A472" s="1" t="s">
         <v>35</v>
       </c>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="E472" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="17.25" hidden="1">
       <c r="A473" s="1" t="s">
         <v>35</v>
       </c>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="E473" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="17.25" hidden="1">
       <c r="A474" s="1" t="s">
         <v>35</v>
       </c>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="E474" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="17.25" hidden="1">
       <c r="A475" s="1" t="s">
         <v>35</v>
       </c>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="E475" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="17.25" hidden="1">
       <c r="A476" s="1" t="s">
         <v>35</v>
       </c>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="E476" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="17.25" hidden="1">
       <c r="A477" s="1" t="s">
         <v>35</v>
       </c>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="E477" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="17.25" hidden="1">
       <c r="A478" s="1" t="s">
         <v>35</v>
       </c>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="E478" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="17.25" hidden="1">
       <c r="A479" s="1" t="s">
         <v>35</v>
       </c>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="E479" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="17.25" hidden="1">
       <c r="A480" s="1" t="s">
         <v>35</v>
       </c>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="E480" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="17.25" hidden="1">
       <c r="A481" s="1" t="s">
         <v>35</v>
       </c>
@@ -11880,10 +11880,10 @@
       <c r="C481" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="D481" s="3"/>
+      <c r="D481" s="1"/>
       <c r="E481" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="17.25" hidden="1">
       <c r="A482" s="1" t="s">
         <v>35</v>
       </c>
@@ -11893,10 +11893,10 @@
       <c r="C482" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="D482" s="3"/>
+      <c r="D482" s="1"/>
       <c r="E482" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="17.25" hidden="1">
       <c r="A483" s="1" t="s">
         <v>35</v>
       </c>
@@ -11906,10 +11906,10 @@
       <c r="C483" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="D483" s="3"/>
+      <c r="D483" s="1"/>
       <c r="E483" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="17.25" hidden="1">
       <c r="A484" s="1" t="s">
         <v>35</v>
       </c>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="E484" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="17.25" hidden="1">
       <c r="A485" s="1" t="s">
         <v>35</v>
       </c>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E485" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="17.25" hidden="1">
       <c r="A486" s="1" t="s">
         <v>35</v>
       </c>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="E486" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="17.25" hidden="1">
       <c r="A487" s="1" t="s">
         <v>35</v>
       </c>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="E487" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="17.25" hidden="1">
       <c r="A488" s="1" t="s">
         <v>35</v>
       </c>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="E488" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="17.25" hidden="1">
       <c r="A489" s="1" t="s">
         <v>35</v>
       </c>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="E489" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="17.25" hidden="1">
       <c r="A490" s="1" t="s">
         <v>35</v>
       </c>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="E490" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="17.25" hidden="1">
       <c r="A491" s="1" t="s">
         <v>35</v>
       </c>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="E491" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="17.25" hidden="1">
       <c r="A492" s="1" t="s">
         <v>35</v>
       </c>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="E492" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="17.25" hidden="1">
       <c r="A493" s="1" t="s">
         <v>35</v>
       </c>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="E493" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="17.25" hidden="1">
       <c r="A494" s="1" t="s">
         <v>35</v>
       </c>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="E494" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="17.25" hidden="1">
       <c r="A495" s="1" t="s">
         <v>35</v>
       </c>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E495" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="17.25" hidden="1">
       <c r="A496" s="1" t="s">
         <v>35</v>
       </c>
@@ -12099,10 +12099,10 @@
       <c r="C496" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="D496" s="3"/>
+      <c r="D496" s="1"/>
       <c r="E496" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="17.25" hidden="1">
       <c r="A497" s="1" t="s">
         <v>35</v>
       </c>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E497" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="17.25" hidden="1">
       <c r="A498" s="1" t="s">
         <v>35</v>
       </c>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="E498" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="17.25" hidden="1">
       <c r="A499" s="1" t="s">
         <v>35</v>
       </c>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="E499" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="17.25" hidden="1">
       <c r="A500" s="1" t="s">
         <v>35</v>
       </c>
@@ -12157,10 +12157,10 @@
       <c r="C500" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="D500" s="3"/>
+      <c r="D500" s="1"/>
       <c r="E500" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="17.25" hidden="1">
       <c r="A501" s="1" t="s">
         <v>35</v>
       </c>
@@ -12170,10 +12170,10 @@
       <c r="C501" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="D501" s="3"/>
+      <c r="D501" s="1"/>
       <c r="E501" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="17.25" hidden="1">
       <c r="A502" s="1" t="s">
         <v>35</v>
       </c>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="E502" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="17.25" hidden="1">
       <c r="A503" s="1" t="s">
         <v>35</v>
       </c>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="E503" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="17.25" hidden="1">
       <c r="A504" s="1" t="s">
         <v>35</v>
       </c>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="E504" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="17.25" hidden="1">
       <c r="A505" s="1" t="s">
         <v>35</v>
       </c>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="E505" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="17.25" hidden="1">
       <c r="A506" s="1" t="s">
         <v>35</v>
       </c>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E506" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="17.25" hidden="1">
       <c r="A507" s="1" t="s">
         <v>35</v>
       </c>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="E507" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="17.25" hidden="1">
       <c r="A508" s="1" t="s">
         <v>35</v>
       </c>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="E508" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="17.25" hidden="1">
       <c r="A509" s="1" t="s">
         <v>35</v>
       </c>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="E509" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="17.25" hidden="1">
       <c r="A510" s="1" t="s">
         <v>35</v>
       </c>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E510" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="17.25" hidden="1">
       <c r="A511" s="1" t="s">
         <v>35</v>
       </c>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="E511" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="17.25" hidden="1">
       <c r="A512" s="1" t="s">
         <v>35</v>
       </c>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="E512" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="17.25" hidden="1">
       <c r="A513" s="1" t="s">
         <v>35</v>
       </c>
@@ -12353,7 +12353,7 @@
       </c>
       <c r="E513" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="17.25" hidden="1">
       <c r="A514" s="1" t="s">
         <v>35</v>
       </c>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E514" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="17.25" hidden="1">
       <c r="A515" s="1" t="s">
         <v>35</v>
       </c>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="E515" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="17.25" hidden="1">
       <c r="A516" s="1" t="s">
         <v>35</v>
       </c>
@@ -12398,7 +12398,7 @@
       </c>
       <c r="E516" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="17.25" hidden="1">
       <c r="A517" s="1" t="s">
         <v>35</v>
       </c>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="E517" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="17.25" hidden="1">
       <c r="A518" s="1" t="s">
         <v>35</v>
       </c>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="E518" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="17.25" hidden="1">
       <c r="A519" s="1" t="s">
         <v>35</v>
       </c>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="E519" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="17.25" hidden="1">
       <c r="A520" s="1" t="s">
         <v>35</v>
       </c>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E520" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="17.25" hidden="1">
       <c r="A521" s="1" t="s">
         <v>35</v>
       </c>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="E521" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="17.25" hidden="1">
       <c r="A522" s="1" t="s">
         <v>35</v>
       </c>
@@ -12488,7 +12488,7 @@
       </c>
       <c r="E522" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="17.25" hidden="1">
       <c r="A523" s="1" t="s">
         <v>35</v>
       </c>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="E523" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="17.25" hidden="1">
       <c r="A524" s="1" t="s">
         <v>35</v>
       </c>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="E524" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="17.25" hidden="1">
       <c r="A525" s="1" t="s">
         <v>35</v>
       </c>
@@ -12533,7 +12533,7 @@
       </c>
       <c r="E525" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="17.25" hidden="1">
       <c r="A526" s="1" t="s">
         <v>35</v>
       </c>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="E526" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="17.25" hidden="1">
       <c r="A527" s="1" t="s">
         <v>35</v>
       </c>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="E527" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="17.25" hidden="1">
       <c r="A528" s="1" t="s">
         <v>35</v>
       </c>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="E528" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="17.25" hidden="1">
       <c r="A529" s="1" t="s">
         <v>35</v>
       </c>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="E529" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="17.25" hidden="1">
       <c r="A530" s="1" t="s">
         <v>35</v>
       </c>
@@ -12603,10 +12603,10 @@
       <c r="C530" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="D530" s="3"/>
+      <c r="D530" s="1"/>
       <c r="E530" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="17.25" hidden="1">
       <c r="A531" s="1" t="s">
         <v>35</v>
       </c>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E531" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="17.25" hidden="1">
       <c r="A532" s="1" t="s">
         <v>35</v>
       </c>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E532" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="17.25" hidden="1">
       <c r="A533" s="1" t="s">
         <v>35</v>
       </c>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="E533" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="17.25" hidden="1">
       <c r="A534" s="1" t="s">
         <v>35</v>
       </c>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="E534" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="17.25" hidden="1">
       <c r="A535" s="1" t="s">
         <v>35</v>
       </c>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="E535" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="17.25" hidden="1">
       <c r="A536" s="1" t="s">
         <v>35</v>
       </c>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="E536" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="17.25" hidden="1">
       <c r="A537" s="1" t="s">
         <v>35</v>
       </c>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="E537" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="538" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="538" customHeight="1" ht="17.25" hidden="1">
       <c r="A538" s="1" t="s">
         <v>35</v>
       </c>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="E538" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="539" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="539" customHeight="1" ht="17.25" hidden="1">
       <c r="A539" s="1" t="s">
         <v>35</v>
       </c>
@@ -12741,7 +12741,7 @@
       </c>
       <c r="E539" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="540" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="540" customHeight="1" ht="17.25" hidden="1">
       <c r="A540" s="1" t="s">
         <v>35</v>
       </c>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E540" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="541" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="541" customHeight="1" ht="17.25" hidden="1">
       <c r="A541" s="1" t="s">
         <v>35</v>
       </c>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="E541" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="542" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="542" customHeight="1" ht="17.25" hidden="1">
       <c r="A542" s="1" t="s">
         <v>35</v>
       </c>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="E542" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="543" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="543" customHeight="1" ht="17.25" hidden="1">
       <c r="A543" s="1" t="s">
         <v>35</v>
       </c>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="E543" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="544" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="544" customHeight="1" ht="17.25" hidden="1">
       <c r="A544" s="1" t="s">
         <v>35</v>
       </c>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="E544" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="545" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="545" customHeight="1" ht="17.25" hidden="1">
       <c r="A545" s="1" t="s">
         <v>35</v>
       </c>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E545" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="546" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="546" customHeight="1" ht="17.25" hidden="1">
       <c r="A546" s="1" t="s">
         <v>35</v>
       </c>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="E546" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="547" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="547" customHeight="1" ht="17.25" hidden="1">
       <c r="A547" s="1" t="s">
         <v>35</v>
       </c>
@@ -12856,10 +12856,10 @@
       <c r="C547" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="D547" s="3"/>
+      <c r="D547" s="1"/>
       <c r="E547" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="548" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="548" customHeight="1" ht="17.25" hidden="1">
       <c r="A548" s="1" t="s">
         <v>35</v>
       </c>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="E548" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="549" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="549" customHeight="1" ht="17.25" hidden="1">
       <c r="A549" s="1" t="s">
         <v>35</v>
       </c>
@@ -12889,7 +12889,7 @@
       </c>
       <c r="E549" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="550" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="550" customHeight="1" ht="17.25" hidden="1">
       <c r="A550" s="1" t="s">
         <v>35</v>
       </c>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="E550" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="551" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="551" customHeight="1" ht="17.25" hidden="1">
       <c r="A551" s="1" t="s">
         <v>35</v>
       </c>
@@ -12919,7 +12919,7 @@
       </c>
       <c r="E551" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="552" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="552" customHeight="1" ht="17.25" hidden="1">
       <c r="A552" s="1" t="s">
         <v>35</v>
       </c>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="E552" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="553" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="553" customHeight="1" ht="17.25" hidden="1">
       <c r="A553" s="1" t="s">
         <v>35</v>
       </c>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="E553" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="554" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="554" customHeight="1" ht="17.25" hidden="1">
       <c r="A554" s="1" t="s">
         <v>35</v>
       </c>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="E554" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="555" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="555" customHeight="1" ht="17.25" hidden="1">
       <c r="A555" s="1" t="s">
         <v>35</v>
       </c>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="E555" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="556" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="556" customHeight="1" ht="17.25" hidden="1">
       <c r="A556" s="1" t="s">
         <v>35</v>
       </c>
@@ -12994,7 +12994,7 @@
       </c>
       <c r="E556" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="557" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="557" customHeight="1" ht="17.25" hidden="1">
       <c r="A557" s="1" t="s">
         <v>35</v>
       </c>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="E557" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="558" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="558" customHeight="1" ht="17.25" hidden="1">
       <c r="A558" s="1" t="s">
         <v>35</v>
       </c>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="E558" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="559" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="559" customHeight="1" ht="17.25" hidden="1">
       <c r="A559" s="1" t="s">
         <v>35</v>
       </c>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="E559" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="560" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="560" customHeight="1" ht="17.25" hidden="1">
       <c r="A560" s="1" t="s">
         <v>35</v>
       </c>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="E560" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="561" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="561" customHeight="1" ht="17.25" hidden="1">
       <c r="A561" s="1" t="s">
         <v>35</v>
       </c>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="E561" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="562" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="562" customHeight="1" ht="17.25" hidden="1">
       <c r="A562" s="1" t="s">
         <v>35</v>
       </c>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="E562" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="563" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="563" customHeight="1" ht="17.25" hidden="1">
       <c r="A563" s="1" t="s">
         <v>35</v>
       </c>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="E563" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="564" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="564" customHeight="1" ht="17.25" hidden="1">
       <c r="A564" s="1" t="s">
         <v>35</v>
       </c>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="E564" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="565" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="565" customHeight="1" ht="17.25" hidden="1">
       <c r="A565" s="1" t="s">
         <v>35</v>
       </c>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="E565" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="566" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="566" customHeight="1" ht="17.25" hidden="1">
       <c r="A566" s="1" t="s">
         <v>35</v>
       </c>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="E566" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="567" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="567" customHeight="1" ht="17.25" hidden="1">
       <c r="A567" s="1" t="s">
         <v>35</v>
       </c>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="E567" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="568" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="568" customHeight="1" ht="17.25" hidden="1">
       <c r="A568" s="1" t="s">
         <v>35</v>
       </c>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="E568" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="569" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="569" customHeight="1" ht="17.25" hidden="1">
       <c r="A569" s="1" t="s">
         <v>35</v>
       </c>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E569" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="570" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="570" customHeight="1" ht="17.25" hidden="1">
       <c r="A570" s="1" t="s">
         <v>35</v>
       </c>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="E570" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="571" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="571" customHeight="1" ht="17.25" hidden="1">
       <c r="A571" s="1" t="s">
         <v>35</v>
       </c>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="E571" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="572" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="572" customHeight="1" ht="17.25" hidden="1">
       <c r="A572" s="1" t="s">
         <v>35</v>
       </c>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="E572" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="573" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="573" customHeight="1" ht="17.25" hidden="1">
       <c r="A573" s="1" t="s">
         <v>35</v>
       </c>
@@ -13244,10 +13244,10 @@
       <c r="C573" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="D573" s="3"/>
+      <c r="D573" s="1"/>
       <c r="E573" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="574" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="574" customHeight="1" ht="17.25" hidden="1">
       <c r="A574" s="1" t="s">
         <v>35</v>
       </c>
@@ -13257,10 +13257,10 @@
       <c r="C574" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D574" s="3"/>
+      <c r="D574" s="1"/>
       <c r="E574" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="575" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="575" customHeight="1" ht="17.25" hidden="1">
       <c r="A575" s="1" t="s">
         <v>35</v>
       </c>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="E575" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="576" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="576" customHeight="1" ht="17.25" hidden="1">
       <c r="A576" s="1" t="s">
         <v>35</v>
       </c>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="E576" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="577" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="577" customHeight="1" ht="17.25" hidden="1">
       <c r="A577" s="1" t="s">
         <v>35</v>
       </c>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="E577" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="578" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="578" customHeight="1" ht="17.25" hidden="1">
       <c r="A578" s="1" t="s">
         <v>35</v>
       </c>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="E578" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="579" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="579" customHeight="1" ht="17.25" hidden="1">
       <c r="A579" s="1" t="s">
         <v>35</v>
       </c>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="E579" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="580" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="580" customHeight="1" ht="17.25" hidden="1">
       <c r="A580" s="1" t="s">
         <v>35</v>
       </c>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E580" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="581" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="581" customHeight="1" ht="17.25" hidden="1">
       <c r="A581" s="1" t="s">
         <v>35</v>
       </c>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="E581" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="582" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="582" customHeight="1" ht="17.25" hidden="1">
       <c r="A582" s="1" t="s">
         <v>35</v>
       </c>
@@ -13380,7 +13380,7 @@
       </c>
       <c r="E582" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="583" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="583" customHeight="1" ht="17.25" hidden="1">
       <c r="A583" s="1" t="s">
         <v>35</v>
       </c>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="E583" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="584" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="584" customHeight="1" ht="17.25" hidden="1">
       <c r="A584" s="1" t="s">
         <v>35</v>
       </c>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="E584" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="585" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="585" customHeight="1" ht="17.25" hidden="1">
       <c r="A585" s="1" t="s">
         <v>35</v>
       </c>
@@ -13425,7 +13425,7 @@
       </c>
       <c r="E585" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="586" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="586" customHeight="1" ht="17.25" hidden="1">
       <c r="A586" s="1" t="s">
         <v>35</v>
       </c>
@@ -13435,10 +13435,10 @@
       <c r="C586" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="D586" s="3"/>
+      <c r="D586" s="1"/>
       <c r="E586" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="587" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="587" customHeight="1" ht="17.25" hidden="1">
       <c r="A587" s="1" t="s">
         <v>35</v>
       </c>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="E587" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="588" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="588" customHeight="1" ht="17.25" hidden="1">
       <c r="A588" s="1" t="s">
         <v>35</v>
       </c>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="E588" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="589" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="589" customHeight="1" ht="17.25" hidden="1">
       <c r="A589" s="1" t="s">
         <v>35</v>
       </c>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="E589" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="590" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="590" customHeight="1" ht="17.25" hidden="1">
       <c r="A590" s="1" t="s">
         <v>35</v>
       </c>
@@ -13498,7 +13498,7 @@
       </c>
       <c r="E590" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="591" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="591" customHeight="1" ht="17.25" hidden="1">
       <c r="A591" s="1" t="s">
         <v>35</v>
       </c>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="E591" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="592" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="592" customHeight="1" ht="17.25" hidden="1">
       <c r="A592" s="1" t="s">
         <v>35</v>
       </c>
@@ -13528,7 +13528,7 @@
       </c>
       <c r="E592" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="593" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="593" customHeight="1" ht="17.25" hidden="1">
       <c r="A593" s="1" t="s">
         <v>35</v>
       </c>
@@ -13543,7 +13543,7 @@
       </c>
       <c r="E593" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="594" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="594" customHeight="1" ht="17.25" hidden="1">
       <c r="A594" s="1" t="s">
         <v>35</v>
       </c>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E594" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="595" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="595" customHeight="1" ht="17.25" hidden="1">
       <c r="A595" s="1" t="s">
         <v>35</v>
       </c>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="E595" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="596" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="596" customHeight="1" ht="17.25" hidden="1">
       <c r="A596" s="1" t="s">
         <v>35</v>
       </c>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="E596" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="597" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="597" customHeight="1" ht="17.25" hidden="1">
       <c r="A597" s="1" t="s">
         <v>35</v>
       </c>
@@ -13603,7 +13603,7 @@
       </c>
       <c r="E597" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="598" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="598" customHeight="1" ht="17.25" hidden="1">
       <c r="A598" s="1" t="s">
         <v>35</v>
       </c>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="E598" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="599" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="599" customHeight="1" ht="17.25" hidden="1">
       <c r="A599" s="1" t="s">
         <v>35</v>
       </c>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="E599" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="600" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="600" customHeight="1" ht="17.25" hidden="1">
       <c r="A600" s="1" t="s">
         <v>35</v>
       </c>
@@ -13643,10 +13643,10 @@
       <c r="C600" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D600" s="3"/>
+      <c r="D600" s="1"/>
       <c r="E600" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="601" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="601" customHeight="1" ht="17.25" hidden="1">
       <c r="A601" s="1" t="s">
         <v>35</v>
       </c>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="E601" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="602" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="602" customHeight="1" ht="17.25" hidden="1">
       <c r="A602" s="1" t="s">
         <v>35</v>
       </c>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="E602" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="603" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="603" customHeight="1" ht="17.25" hidden="1">
       <c r="A603" s="1" t="s">
         <v>35</v>
       </c>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="E603" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="604" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="604" customHeight="1" ht="17.25" hidden="1">
       <c r="A604" s="1" t="s">
         <v>35</v>
       </c>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="E604" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="605" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="605" customHeight="1" ht="17.25" hidden="1">
       <c r="A605" s="1" t="s">
         <v>35</v>
       </c>
@@ -13716,10 +13716,10 @@
       <c r="C605" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="D605" s="3"/>
+      <c r="D605" s="1"/>
       <c r="E605" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="606" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="606" customHeight="1" ht="17.25" hidden="1">
       <c r="A606" s="1" t="s">
         <v>35</v>
       </c>
@@ -13729,10 +13729,10 @@
       <c r="C606" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="D606" s="3"/>
+      <c r="D606" s="1"/>
       <c r="E606" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="607" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="607" customHeight="1" ht="17.25" hidden="1">
       <c r="A607" s="1" t="s">
         <v>35</v>
       </c>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="E607" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="608" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="608" customHeight="1" ht="17.25" hidden="1">
       <c r="A608" s="1" t="s">
         <v>35</v>
       </c>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="E608" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="609" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="609" customHeight="1" ht="17.25" hidden="1">
       <c r="A609" s="1" t="s">
         <v>35</v>
       </c>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="E609" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="610" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="610" customHeight="1" ht="17.25" hidden="1">
       <c r="A610" s="1" t="s">
         <v>35</v>
       </c>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="E610" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="611" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="611" customHeight="1" ht="17.25" hidden="1">
       <c r="A611" s="1" t="s">
         <v>35</v>
       </c>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="E611" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="612" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="612" customHeight="1" ht="17.25" hidden="1">
       <c r="A612" s="1" t="s">
         <v>35</v>
       </c>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="E612" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="613" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="613" customHeight="1" ht="17.25" hidden="1">
       <c r="A613" s="1" t="s">
         <v>35</v>
       </c>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="E613" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="614" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="614" customHeight="1" ht="17.25" hidden="1">
       <c r="A614" s="1" t="s">
         <v>35</v>
       </c>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="E614" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="615" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="615" customHeight="1" ht="17.25" hidden="1">
       <c r="A615" s="1" t="s">
         <v>35</v>
       </c>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="E615" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="616" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="616" customHeight="1" ht="17.25" hidden="1">
       <c r="A616" s="1" t="s">
         <v>35</v>
       </c>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="E616" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="617" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="617" customHeight="1" ht="17.25" hidden="1">
       <c r="A617" s="1" t="s">
         <v>35</v>
       </c>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="E617" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="618" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="618" customHeight="1" ht="17.25" hidden="1">
       <c r="A618" s="1" t="s">
         <v>35</v>
       </c>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="E618" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="619" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="619" customHeight="1" ht="17.25" hidden="1">
       <c r="A619" s="1" t="s">
         <v>35</v>
       </c>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E619" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="620" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="620" customHeight="1" ht="17.25" hidden="1">
       <c r="A620" s="1" t="s">
         <v>35</v>
       </c>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="E620" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="621" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="621" customHeight="1" ht="17.25" hidden="1">
       <c r="A621" s="1" t="s">
         <v>35</v>
       </c>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="E621" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="622" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="622" customHeight="1" ht="17.25" hidden="1">
       <c r="A622" s="1" t="s">
         <v>35</v>
       </c>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="E622" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="623" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="623" customHeight="1" ht="17.25" hidden="1">
       <c r="A623" s="1" t="s">
         <v>35</v>
       </c>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="E623" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="624" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="624" customHeight="1" ht="17.25" hidden="1">
       <c r="A624" s="1" t="s">
         <v>35</v>
       </c>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="E624" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="625" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="625" customHeight="1" ht="17.25" hidden="1">
       <c r="A625" s="1" t="s">
         <v>35</v>
       </c>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="E625" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="626" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="626" customHeight="1" ht="17.25" hidden="1">
       <c r="A626" s="1" t="s">
         <v>35</v>
       </c>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="E626" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="627" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="627" customHeight="1" ht="17.25" hidden="1">
       <c r="A627" s="1" t="s">
         <v>35</v>
       </c>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="E627" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="628" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="628" customHeight="1" ht="17.25" hidden="1">
       <c r="A628" s="1" t="s">
         <v>35</v>
       </c>
@@ -14062,7 +14062,7 @@
       </c>
       <c r="E628" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="629" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="629" customHeight="1" ht="17.25" hidden="1">
       <c r="A629" s="1" t="s">
         <v>35</v>
       </c>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="E629" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="630" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="630" customHeight="1" ht="17.25" hidden="1">
       <c r="A630" s="1" t="s">
         <v>35</v>
       </c>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="E630" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="631" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="631" customHeight="1" ht="17.25" hidden="1">
       <c r="A631" s="1" t="s">
         <v>35</v>
       </c>
@@ -14102,10 +14102,10 @@
       <c r="C631" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="D631" s="3"/>
+      <c r="D631" s="1"/>
       <c r="E631" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="632" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="632" customHeight="1" ht="17.25" hidden="1">
       <c r="A632" s="1" t="s">
         <v>35</v>
       </c>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="E632" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="633" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="633" customHeight="1" ht="17.25" hidden="1">
       <c r="A633" s="1" t="s">
         <v>35</v>
       </c>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="E633" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="634" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="634" customHeight="1" ht="17.25" hidden="1">
       <c r="A634" s="1" t="s">
         <v>35</v>
       </c>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="E634" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="635" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="635" customHeight="1" ht="17.25" hidden="1">
       <c r="A635" s="1" t="s">
         <v>35</v>
       </c>
@@ -14160,10 +14160,10 @@
       <c r="C635" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="D635" s="3"/>
+      <c r="D635" s="1"/>
       <c r="E635" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="636" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="636" customHeight="1" ht="17.25" hidden="1">
       <c r="A636" s="1" t="s">
         <v>35</v>
       </c>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="E636" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="637" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="637" customHeight="1" ht="17.25" hidden="1">
       <c r="A637" s="1" t="s">
         <v>35</v>
       </c>
@@ -14188,10 +14188,10 @@
       <c r="C637" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D637" s="3"/>
+      <c r="D637" s="1"/>
       <c r="E637" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="638" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="638" customHeight="1" ht="17.25" hidden="1">
       <c r="A638" s="1" t="s">
         <v>35</v>
       </c>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="E638" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="639" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="639" customHeight="1" ht="17.25" hidden="1">
       <c r="A639" s="1" t="s">
         <v>35</v>
       </c>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="E639" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="640" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="640" customHeight="1" ht="17.25" hidden="1">
       <c r="A640" s="1" t="s">
         <v>35</v>
       </c>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="E640" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="641" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="641" customHeight="1" ht="17.25" hidden="1">
       <c r="A641" s="1" t="s">
         <v>35</v>
       </c>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="E641" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="642" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="642" customHeight="1" ht="17.25" hidden="1">
       <c r="A642" s="1" t="s">
         <v>35</v>
       </c>
@@ -14266,7 +14266,7 @@
       </c>
       <c r="E642" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="643" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="643" customHeight="1" ht="17.25" hidden="1">
       <c r="A643" s="1" t="s">
         <v>35</v>
       </c>
@@ -14281,7 +14281,7 @@
       </c>
       <c r="E643" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="644" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="644" customHeight="1" ht="17.25" hidden="1">
       <c r="A644" s="1" t="s">
         <v>35</v>
       </c>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E644" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="645" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="645" customHeight="1" ht="17.25" hidden="1">
       <c r="A645" s="1" t="s">
         <v>35</v>
       </c>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="E645" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="646" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="646" customHeight="1" ht="17.25" hidden="1">
       <c r="A646" s="1" t="s">
         <v>35</v>
       </c>
@@ -14326,7 +14326,7 @@
       </c>
       <c r="E646" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="647" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="647" customHeight="1" ht="17.25" hidden="1">
       <c r="A647" s="1" t="s">
         <v>35</v>
       </c>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="E647" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="648" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="648" customHeight="1" ht="17.25" hidden="1">
       <c r="A648" s="1" t="s">
         <v>35</v>
       </c>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="E648" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="649" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="649" customHeight="1" ht="17.25" hidden="1">
       <c r="A649" s="1" t="s">
         <v>35</v>
       </c>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="E649" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="650" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="650" customHeight="1" ht="17.25" hidden="1">
       <c r="A650" s="1" t="s">
         <v>35</v>
       </c>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="E650" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="651" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="651" customHeight="1" ht="17.25" hidden="1">
       <c r="A651" s="1" t="s">
         <v>35</v>
       </c>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E651" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="652" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="652" customHeight="1" ht="17.25" hidden="1">
       <c r="A652" s="1" t="s">
         <v>35</v>
       </c>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="E652" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="653" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="653" customHeight="1" ht="17.25" hidden="1">
       <c r="A653" s="1" t="s">
         <v>35</v>
       </c>
@@ -14426,10 +14426,10 @@
       <c r="C653" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="D653" s="3"/>
+      <c r="D653" s="1"/>
       <c r="E653" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="654" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="654" customHeight="1" ht="17.25" hidden="1">
       <c r="A654" s="1" t="s">
         <v>35</v>
       </c>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="E654" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="655" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="655" customHeight="1" ht="17.25" hidden="1">
       <c r="A655" s="1" t="s">
         <v>35</v>
       </c>
@@ -14454,10 +14454,10 @@
       <c r="C655" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="D655" s="3"/>
+      <c r="D655" s="1"/>
       <c r="E655" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="656" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="656" customHeight="1" ht="17.25" hidden="1">
       <c r="A656" s="1" t="s">
         <v>35</v>
       </c>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="E656" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="657" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="657" customHeight="1" ht="17.25" hidden="1">
       <c r="A657" s="1" t="s">
         <v>35</v>
       </c>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E657" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="658" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="658" customHeight="1" ht="17.25" hidden="1">
       <c r="A658" s="1" t="s">
         <v>35</v>
       </c>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="E658" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="659" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="659" customHeight="1" ht="17.25" hidden="1">
       <c r="A659" s="1" t="s">
         <v>35</v>
       </c>
@@ -14517,7 +14517,7 @@
       </c>
       <c r="E659" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="660" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="660" customHeight="1" ht="17.25" hidden="1">
       <c r="A660" s="1" t="s">
         <v>35</v>
       </c>
@@ -14532,7 +14532,7 @@
       </c>
       <c r="E660" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="661" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="661" customHeight="1" ht="17.25" hidden="1">
       <c r="A661" s="1" t="s">
         <v>35</v>
       </c>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="E661" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="662" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="662" customHeight="1" ht="17.25" hidden="1">
       <c r="A662" s="1" t="s">
         <v>35</v>
       </c>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="E662" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="663" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="663" customHeight="1" ht="17.25" hidden="1">
       <c r="A663" s="1" t="s">
         <v>35</v>
       </c>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="E663" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="664" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="664" customHeight="1" ht="17.25" hidden="1">
       <c r="A664" s="1" t="s">
         <v>35</v>
       </c>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E664" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="665" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="665" customHeight="1" ht="17.25" hidden="1">
       <c r="A665" s="1" t="s">
         <v>35</v>
       </c>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="E665" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="666" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="666" customHeight="1" ht="17.25" hidden="1">
       <c r="A666" s="1" t="s">
         <v>35</v>
       </c>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="E666" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="667" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="667" customHeight="1" ht="17.25" hidden="1">
       <c r="A667" s="1" t="s">
         <v>35</v>
       </c>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="E667" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="668" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="668" customHeight="1" ht="17.25" hidden="1">
       <c r="A668" s="1" t="s">
         <v>35</v>
       </c>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="E668" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="669" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="669" customHeight="1" ht="17.25" hidden="1">
       <c r="A669" s="1" t="s">
         <v>35</v>
       </c>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="E669" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="670" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="670" customHeight="1" ht="17.25" hidden="1">
       <c r="A670" s="1" t="s">
         <v>35</v>
       </c>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="E670" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="671" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="671" customHeight="1" ht="17.25" hidden="1">
       <c r="A671" s="1" t="s">
         <v>35</v>
       </c>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="E671" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="672" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="672" customHeight="1" ht="17.25" hidden="1">
       <c r="A672" s="1" t="s">
         <v>35</v>
       </c>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="E672" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="673" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="673" customHeight="1" ht="17.25" hidden="1">
       <c r="A673" s="1" t="s">
         <v>35</v>
       </c>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="E673" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="674" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="674" customHeight="1" ht="17.25" hidden="1">
       <c r="A674" s="1" t="s">
         <v>35</v>
       </c>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="E674" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="675" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="675" customHeight="1" ht="17.25" hidden="1">
       <c r="A675" s="1" t="s">
         <v>35</v>
       </c>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="E675" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="676" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="676" customHeight="1" ht="17.25" hidden="1">
       <c r="A676" s="1" t="s">
         <v>35</v>
       </c>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="E676" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="677" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="677" customHeight="1" ht="17.25" hidden="1">
       <c r="A677" s="1" t="s">
         <v>35</v>
       </c>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="E677" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="678" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="678" customHeight="1" ht="17.25" hidden="1">
       <c r="A678" s="1" t="s">
         <v>35</v>
       </c>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="E678" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="679" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="679" customHeight="1" ht="17.25" hidden="1">
       <c r="A679" s="1" t="s">
         <v>35</v>
       </c>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="E679" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="680" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="680" customHeight="1" ht="17.25" hidden="1">
       <c r="A680" s="1" t="s">
         <v>35</v>
       </c>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="E680" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="681" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="681" customHeight="1" ht="17.25" hidden="1">
       <c r="A681" s="1" t="s">
         <v>35</v>
       </c>
@@ -14842,10 +14842,10 @@
       <c r="C681" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="D681" s="3"/>
+      <c r="D681" s="1"/>
       <c r="E681" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="682" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="682" customHeight="1" ht="17.25" hidden="1">
       <c r="A682" s="1" t="s">
         <v>35</v>
       </c>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="E682" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="683" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="683" customHeight="1" ht="17.25" hidden="1">
       <c r="A683" s="1" t="s">
         <v>35</v>
       </c>
@@ -14875,7 +14875,7 @@
       </c>
       <c r="E683" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="684" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="684" customHeight="1" ht="17.25" hidden="1">
       <c r="A684" s="1" t="s">
         <v>35</v>
       </c>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="E684" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="685" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="685" customHeight="1" ht="17.25" hidden="1">
       <c r="A685" s="1" t="s">
         <v>35</v>
       </c>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="E685" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="686" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="686" customHeight="1" ht="17.25" hidden="1">
       <c r="A686" s="1" t="s">
         <v>35</v>
       </c>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="E686" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="687" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="687" customHeight="1" ht="17.25" hidden="1">
       <c r="A687" s="1" t="s">
         <v>35</v>
       </c>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="E687" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="688" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="688" customHeight="1" ht="17.25" hidden="1">
       <c r="A688" s="1" t="s">
         <v>35</v>
       </c>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="E688" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="689" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="689" customHeight="1" ht="17.25" hidden="1">
       <c r="A689" s="1" t="s">
         <v>35</v>
       </c>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="E689" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="690" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="690" customHeight="1" ht="17.25" hidden="1">
       <c r="A690" s="1" t="s">
         <v>35</v>
       </c>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="E690" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="691" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="691" customHeight="1" ht="17.25" hidden="1">
       <c r="A691" s="1" t="s">
         <v>35</v>
       </c>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="E691" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="692" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="692" customHeight="1" ht="17.25" hidden="1">
       <c r="A692" s="1" t="s">
         <v>35</v>
       </c>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="E692" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="693" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="693" customHeight="1" ht="17.25" hidden="1">
       <c r="A693" s="1" t="s">
         <v>35</v>
       </c>
@@ -15025,7 +15025,7 @@
       </c>
       <c r="E693" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="694" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="694" customHeight="1" ht="17.25" hidden="1">
       <c r="A694" s="1" t="s">
         <v>35</v>
       </c>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="E694" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="695" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="695" customHeight="1" ht="17.25" hidden="1">
       <c r="A695" s="1" t="s">
         <v>35</v>
       </c>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="E695" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="696" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="696" customHeight="1" ht="17.25" hidden="1">
       <c r="A696" s="1" t="s">
         <v>35</v>
       </c>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="E696" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="697" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="697" customHeight="1" ht="17.25" hidden="1">
       <c r="A697" s="1" t="s">
         <v>35</v>
       </c>
@@ -15085,7 +15085,7 @@
       </c>
       <c r="E697" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="698" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="698" customHeight="1" ht="17.25" hidden="1">
       <c r="A698" s="1" t="s">
         <v>35</v>
       </c>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="E698" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="699" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="699" customHeight="1" ht="17.25" hidden="1">
       <c r="A699" s="1" t="s">
         <v>35</v>
       </c>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="E699" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="700" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="700" customHeight="1" ht="17.25" hidden="1">
       <c r="A700" s="1" t="s">
         <v>35</v>
       </c>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="E700" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="701" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="701" customHeight="1" ht="17.25" hidden="1">
       <c r="A701" s="1" t="s">
         <v>35</v>
       </c>
@@ -15145,7 +15145,7 @@
       </c>
       <c r="E701" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="702" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="702" customHeight="1" ht="17.25" hidden="1">
       <c r="A702" s="1" t="s">
         <v>35</v>
       </c>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="E702" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="703" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="703" customHeight="1" ht="17.25" hidden="1">
       <c r="A703" s="1" t="s">
         <v>35</v>
       </c>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="E703" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="704" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="704" customHeight="1" ht="17.25" hidden="1">
       <c r="A704" s="1" t="s">
         <v>35</v>
       </c>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="E704" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="705" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="705" customHeight="1" ht="17.25" hidden="1">
       <c r="A705" s="1" t="s">
         <v>35</v>
       </c>
@@ -15205,7 +15205,7 @@
       </c>
       <c r="E705" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="706" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="706" customHeight="1" ht="17.25" hidden="1">
       <c r="A706" s="1" t="s">
         <v>35</v>
       </c>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="E706" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="707" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="707" customHeight="1" ht="17.25" hidden="1">
       <c r="A707" s="1" t="s">
         <v>35</v>
       </c>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="E707" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="708" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="708" customHeight="1" ht="17.25" hidden="1">
       <c r="A708" s="1" t="s">
         <v>35</v>
       </c>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E708" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="709" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="709" customHeight="1" ht="17.25" hidden="1">
       <c r="A709" s="1" t="s">
         <v>35</v>
       </c>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="E709" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="710" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="710" customHeight="1" ht="17.25" hidden="1">
       <c r="A710" s="1" t="s">
         <v>35</v>
       </c>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E710" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="711" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="711" customHeight="1" ht="17.25" hidden="1">
       <c r="A711" s="1" t="s">
         <v>35</v>
       </c>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="E711" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="712" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="712" customHeight="1" ht="17.25" hidden="1">
       <c r="A712" s="1" t="s">
         <v>35</v>
       </c>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="E712" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="713" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="713" customHeight="1" ht="17.25" hidden="1">
       <c r="A713" s="1" t="s">
         <v>35</v>
       </c>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="E713" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="714" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="714" customHeight="1" ht="17.25" hidden="1">
       <c r="A714" s="1" t="s">
         <v>35</v>
       </c>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="E714" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="715" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="715" customHeight="1" ht="17.25" hidden="1">
       <c r="A715" s="1" t="s">
         <v>35</v>
       </c>
@@ -15355,7 +15355,7 @@
       </c>
       <c r="E715" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="716" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="716" customHeight="1" ht="17.25" hidden="1">
       <c r="A716" s="1" t="s">
         <v>35</v>
       </c>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="E716" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="717" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="717" customHeight="1" ht="17.25" hidden="1">
       <c r="A717" s="1" t="s">
         <v>35</v>
       </c>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="E717" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="718" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="718" customHeight="1" ht="17.25" hidden="1">
       <c r="A718" s="1" t="s">
         <v>35</v>
       </c>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="E718" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="719" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="719" customHeight="1" ht="17.25" hidden="1">
       <c r="A719" s="1" t="s">
         <v>35</v>
       </c>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="E719" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="720" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="720" customHeight="1" ht="17.25" hidden="1">
       <c r="A720" s="1" t="s">
         <v>35</v>
       </c>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="E720" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="721" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="721" customHeight="1" ht="17.25" hidden="1">
       <c r="A721" s="1" t="s">
         <v>35</v>
       </c>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="E721" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="722" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="722" customHeight="1" ht="17.25" hidden="1">
       <c r="A722" s="1" t="s">
         <v>35</v>
       </c>
@@ -15455,10 +15455,10 @@
       <c r="C722" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="D722" s="3"/>
+      <c r="D722" s="1"/>
       <c r="E722" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="723" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="723" customHeight="1" ht="17.25" hidden="1">
       <c r="A723" s="1" t="s">
         <v>35</v>
       </c>
@@ -15468,10 +15468,10 @@
       <c r="C723" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="D723" s="3"/>
+      <c r="D723" s="1"/>
       <c r="E723" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="724" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="724" customHeight="1" ht="17.25" hidden="1">
       <c r="A724" s="1" t="s">
         <v>35</v>
       </c>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="E724" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="725" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="725" customHeight="1" ht="17.25" hidden="1">
       <c r="A725" s="1" t="s">
         <v>35</v>
       </c>
@@ -15501,7 +15501,7 @@
       </c>
       <c r="E725" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="726" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="726" customHeight="1" ht="17.25" hidden="1">
       <c r="A726" s="1" t="s">
         <v>35</v>
       </c>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="E726" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="727" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="727" customHeight="1" ht="17.25" hidden="1">
       <c r="A727" s="1" t="s">
         <v>35</v>
       </c>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="E727" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="728" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="728" customHeight="1" ht="17.25" hidden="1">
       <c r="A728" s="1" t="s">
         <v>35</v>
       </c>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="E728" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="729" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="729" customHeight="1" ht="17.25" hidden="1">
       <c r="A729" s="1" t="s">
         <v>35</v>
       </c>
@@ -15556,10 +15556,10 @@
       <c r="C729" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="D729" s="3"/>
+      <c r="D729" s="1"/>
       <c r="E729" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="730" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="730" customHeight="1" ht="17.25" hidden="1">
       <c r="A730" s="1" t="s">
         <v>35</v>
       </c>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="E730" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="731" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="731" customHeight="1" ht="17.25" hidden="1">
       <c r="A731" s="1" t="s">
         <v>35</v>
       </c>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="E731" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="732" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="732" customHeight="1" ht="17.25" hidden="1">
       <c r="A732" s="1" t="s">
         <v>35</v>
       </c>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="E732" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="733" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="733" customHeight="1" ht="17.25" hidden="1">
       <c r="A733" s="1" t="s">
         <v>35</v>
       </c>
@@ -15619,7 +15619,7 @@
       </c>
       <c r="E733" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="734" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="734" customHeight="1" ht="17.25" hidden="1">
       <c r="A734" s="1" t="s">
         <v>35</v>
       </c>
@@ -15629,10 +15629,10 @@
       <c r="C734" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="D734" s="3"/>
+      <c r="D734" s="1"/>
       <c r="E734" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="735" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="735" customHeight="1" ht="17.25" hidden="1">
       <c r="A735" s="1" t="s">
         <v>35</v>
       </c>
@@ -15642,10 +15642,10 @@
       <c r="C735" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="D735" s="3"/>
+      <c r="D735" s="1"/>
       <c r="E735" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="736" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="736" customHeight="1" ht="17.25" hidden="1">
       <c r="A736" s="1" t="s">
         <v>35</v>
       </c>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="E736" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="737" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="737" customHeight="1" ht="17.25" hidden="1">
       <c r="A737" s="1" t="s">
         <v>35</v>
       </c>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="E737" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="738" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="738" customHeight="1" ht="17.25" hidden="1">
       <c r="A738" s="1" t="s">
         <v>35</v>
       </c>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E738" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="739" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="739" customHeight="1" ht="17.25" hidden="1">
       <c r="A739" s="1" t="s">
         <v>35</v>
       </c>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="E739" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="740" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="740" customHeight="1" ht="17.25" hidden="1">
       <c r="A740" s="1" t="s">
         <v>35</v>
       </c>
@@ -15720,7 +15720,7 @@
       </c>
       <c r="E740" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="741" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="741" customHeight="1" ht="17.25" hidden="1">
       <c r="A741" s="1" t="s">
         <v>35</v>
       </c>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="E741" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="742" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="742" customHeight="1" ht="17.25" hidden="1">
       <c r="A742" s="1" t="s">
         <v>35</v>
       </c>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="E742" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="743" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="743" customHeight="1" ht="17.25" hidden="1">
       <c r="A743" s="1" t="s">
         <v>35</v>
       </c>
@@ -15765,7 +15765,7 @@
       </c>
       <c r="E743" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="744" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="744" customHeight="1" ht="17.25" hidden="1">
       <c r="A744" s="1" t="s">
         <v>35</v>
       </c>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="E744" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="745" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="745" customHeight="1" ht="17.25" hidden="1">
       <c r="A745" s="1" t="s">
         <v>35</v>
       </c>
@@ -15795,7 +15795,7 @@
       </c>
       <c r="E745" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="746" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="746" customHeight="1" ht="17.25" hidden="1">
       <c r="A746" s="1" t="s">
         <v>35</v>
       </c>
@@ -15810,7 +15810,7 @@
       </c>
       <c r="E746" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="747" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="747" customHeight="1" ht="17.25" hidden="1">
       <c r="A747" s="1" t="s">
         <v>35</v>
       </c>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="E747" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="748" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="748" customHeight="1" ht="17.25" hidden="1">
       <c r="A748" s="1" t="s">
         <v>35</v>
       </c>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="E748" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="749" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="749" customHeight="1" ht="17.25" hidden="1">
       <c r="A749" s="1" t="s">
         <v>35</v>
       </c>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="E749" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="750" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="750" customHeight="1" ht="17.25" hidden="1">
       <c r="A750" s="1" t="s">
         <v>35</v>
       </c>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="E750" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="751" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="751" customHeight="1" ht="17.25" hidden="1">
       <c r="A751" s="1" t="s">
         <v>35</v>
       </c>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E751" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="752" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="752" customHeight="1" ht="17.25" hidden="1">
       <c r="A752" s="1" t="s">
         <v>35</v>
       </c>
@@ -15900,7 +15900,7 @@
       </c>
       <c r="E752" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="753" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="753" customHeight="1" ht="17.25" hidden="1">
       <c r="A753" s="1" t="s">
         <v>35</v>
       </c>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="E753" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="754" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="754" customHeight="1" ht="17.25" hidden="1">
       <c r="A754" s="1" t="s">
         <v>35</v>
       </c>
@@ -15925,10 +15925,10 @@
       <c r="C754" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="D754" s="3"/>
+      <c r="D754" s="1"/>
       <c r="E754" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="755" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="755" customHeight="1" ht="17.25" hidden="1">
       <c r="A755" s="1" t="s">
         <v>35</v>
       </c>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="E755" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="756" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="756" customHeight="1" ht="17.25" hidden="1">
       <c r="A756" s="1" t="s">
         <v>35</v>
       </c>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="E756" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="757" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="757" customHeight="1" ht="17.25" hidden="1">
       <c r="A757" s="1" t="s">
         <v>35</v>
       </c>
@@ -15973,7 +15973,7 @@
       </c>
       <c r="E757" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="758" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="758" customHeight="1" ht="17.25" hidden="1">
       <c r="A758" s="1" t="s">
         <v>35</v>
       </c>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="E758" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="759" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="759" customHeight="1" ht="17.25" hidden="1">
       <c r="A759" s="1" t="s">
         <v>35</v>
       </c>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="E759" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="760" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="760" customHeight="1" ht="17.25" hidden="1">
       <c r="A760" s="1" t="s">
         <v>35</v>
       </c>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E760" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="761" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="761" customHeight="1" ht="17.25" hidden="1">
       <c r="A761" s="1" t="s">
         <v>35</v>
       </c>
@@ -16033,7 +16033,7 @@
       </c>
       <c r="E761" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="762" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="762" customHeight="1" ht="17.25" hidden="1">
       <c r="A762" s="1" t="s">
         <v>35</v>
       </c>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="E762" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="763" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="763" customHeight="1" ht="17.25" hidden="1">
       <c r="A763" s="1" t="s">
         <v>35</v>
       </c>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="E763" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="764" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="764" customHeight="1" ht="17.25" hidden="1">
       <c r="A764" s="1" t="s">
         <v>35</v>
       </c>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="E764" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="765" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="765" customHeight="1" ht="17.25" hidden="1">
       <c r="A765" s="1" t="s">
         <v>35</v>
       </c>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="E765" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="766" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="766" customHeight="1" ht="17.25" hidden="1">
       <c r="A766" s="1" t="s">
         <v>35</v>
       </c>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="E766" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="767" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="767" customHeight="1" ht="17.25" hidden="1">
       <c r="A767" s="1" t="s">
         <v>35</v>
       </c>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="E767" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="768" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="768" customHeight="1" ht="17.25" hidden="1">
       <c r="A768" s="1" t="s">
         <v>35</v>
       </c>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="E768" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="769" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="769" customHeight="1" ht="17.25" hidden="1">
       <c r="A769" s="1" t="s">
         <v>35</v>
       </c>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="E769" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="770" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="770" customHeight="1" ht="17.25" hidden="1">
       <c r="A770" s="1" t="s">
         <v>35</v>
       </c>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="E770" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="771" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="771" customHeight="1" ht="17.25" hidden="1">
       <c r="A771" s="1" t="s">
         <v>35</v>
       </c>
@@ -16183,7 +16183,7 @@
       </c>
       <c r="E771" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="772" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="772" customHeight="1" ht="17.25" hidden="1">
       <c r="A772" s="1" t="s">
         <v>35</v>
       </c>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="E772" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="773" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="773" customHeight="1" ht="17.25" hidden="1">
       <c r="A773" s="1" t="s">
         <v>35</v>
       </c>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="E773" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="774" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="774" customHeight="1" ht="17.25" hidden="1">
       <c r="A774" s="1" t="s">
         <v>35</v>
       </c>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="E774" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="775" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="775" customHeight="1" ht="17.25" hidden="1">
       <c r="A775" s="1" t="s">
         <v>35</v>
       </c>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="E775" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="776" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="776" customHeight="1" ht="17.25" hidden="1">
       <c r="A776" s="1" t="s">
         <v>35</v>
       </c>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="E776" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="777" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="777" customHeight="1" ht="17.25" hidden="1">
       <c r="A777" s="1" t="s">
         <v>35</v>
       </c>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="E777" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="778" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="778" customHeight="1" ht="17.25" hidden="1">
       <c r="A778" s="1" t="s">
         <v>35</v>
       </c>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="E778" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="779" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="779" customHeight="1" ht="17.25" hidden="1">
       <c r="A779" s="1" t="s">
         <v>35</v>
       </c>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="E779" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="780" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="780" customHeight="1" ht="17.25" hidden="1">
       <c r="A780" s="1" t="s">
         <v>35</v>
       </c>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="E780" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="781" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="781" customHeight="1" ht="17.25" hidden="1">
       <c r="A781" s="1" t="s">
         <v>35</v>
       </c>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="E781" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="782" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="782" customHeight="1" ht="17.25" hidden="1">
       <c r="A782" s="1" t="s">
         <v>35</v>
       </c>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="E782" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="783" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="783" customHeight="1" ht="17.25" hidden="1">
       <c r="A783" s="1" t="s">
         <v>35</v>
       </c>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="E783" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="784" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="784" customHeight="1" ht="17.25" hidden="1">
       <c r="A784" s="1" t="s">
         <v>35</v>
       </c>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="E784" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="785" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="785" customHeight="1" ht="17.25" hidden="1">
       <c r="A785" s="1" t="s">
         <v>35</v>
       </c>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="E785" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="786" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="786" customHeight="1" ht="17.25" hidden="1">
       <c r="A786" s="1" t="s">
         <v>35</v>
       </c>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="E786" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="787" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="787" customHeight="1" ht="17.25" hidden="1">
       <c r="A787" s="1" t="s">
         <v>35</v>
       </c>
@@ -16423,7 +16423,7 @@
       </c>
       <c r="E787" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="788" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="788" customHeight="1" ht="17.25" hidden="1">
       <c r="A788" s="1" t="s">
         <v>35</v>
       </c>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="E788" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="789" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="789" customHeight="1" ht="17.25" hidden="1">
       <c r="A789" s="1" t="s">
         <v>35</v>
       </c>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="E789" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="790" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="790" customHeight="1" ht="17.25" hidden="1">
       <c r="A790" s="1" t="s">
         <v>35</v>
       </c>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="E790" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="791" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="791" customHeight="1" ht="17.25" hidden="1">
       <c r="A791" s="1" t="s">
         <v>35</v>
       </c>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="E791" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="792" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="792" customHeight="1" ht="17.25" hidden="1">
       <c r="A792" s="1" t="s">
         <v>35</v>
       </c>
@@ -16498,7 +16498,7 @@
       </c>
       <c r="E792" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="793" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="793" customHeight="1" ht="17.25" hidden="1">
       <c r="A793" s="1" t="s">
         <v>35</v>
       </c>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="E793" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="794" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="794" customHeight="1" ht="17.25" hidden="1">
       <c r="A794" s="1" t="s">
         <v>35</v>
       </c>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="E794" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="795" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="795" customHeight="1" ht="17.25" hidden="1">
       <c r="A795" s="1" t="s">
         <v>35</v>
       </c>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="E795" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="796" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="796" customHeight="1" ht="17.25" hidden="1">
       <c r="A796" s="1" t="s">
         <v>35</v>
       </c>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="E796" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="797" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="797" customHeight="1" ht="17.25" hidden="1">
       <c r="A797" s="1" t="s">
         <v>35</v>
       </c>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="E797" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="798" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="798" customHeight="1" ht="17.25" hidden="1">
       <c r="A798" s="1" t="s">
         <v>35</v>
       </c>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="E798" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="799" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="799" customHeight="1" ht="17.25" hidden="1">
       <c r="A799" s="1" t="s">
         <v>35</v>
       </c>
@@ -16603,7 +16603,7 @@
       </c>
       <c r="E799" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="800" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="800" customHeight="1" ht="17.25" hidden="1">
       <c r="A800" s="1" t="s">
         <v>35</v>
       </c>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="E800" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="801" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="801" customHeight="1" ht="17.25" hidden="1">
       <c r="A801" s="1" t="s">
         <v>35</v>
       </c>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E801" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="802" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="802" customHeight="1" ht="17.25" hidden="1">
       <c r="A802" s="1" t="s">
         <v>35</v>
       </c>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="E802" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="803" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="803" customHeight="1" ht="17.25" hidden="1">
       <c r="A803" s="1" t="s">
         <v>35</v>
       </c>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="E803" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="804" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="804" customHeight="1" ht="17.25" hidden="1">
       <c r="A804" s="1" t="s">
         <v>35</v>
       </c>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="E804" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="805" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="805" customHeight="1" ht="17.25" hidden="1">
       <c r="A805" s="1" t="s">
         <v>35</v>
       </c>
@@ -16693,7 +16693,7 @@
       </c>
       <c r="E805" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="806" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="806" customHeight="1" ht="17.25" hidden="1">
       <c r="A806" s="1" t="s">
         <v>35</v>
       </c>
@@ -16708,7 +16708,7 @@
       </c>
       <c r="E806" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="807" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="807" customHeight="1" ht="17.25" hidden="1">
       <c r="A807" s="1" t="s">
         <v>35</v>
       </c>
@@ -16723,7 +16723,7 @@
       </c>
       <c r="E807" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="808" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="808" customHeight="1" ht="17.25" hidden="1">
       <c r="A808" s="1" t="s">
         <v>35</v>
       </c>
@@ -16738,7 +16738,7 @@
       </c>
       <c r="E808" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="809" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="809" customHeight="1" ht="17.25" hidden="1">
       <c r="A809" s="1" t="s">
         <v>35</v>
       </c>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="E809" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="810" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="810" customHeight="1" ht="17.25" hidden="1">
       <c r="A810" s="1" t="s">
         <v>35</v>
       </c>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="E810" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="811" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="811" customHeight="1" ht="17.25" hidden="1">
       <c r="A811" s="1" t="s">
         <v>35</v>
       </c>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="E811" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="812" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="812" customHeight="1" ht="17.25" hidden="1">
       <c r="A812" s="1" t="s">
         <v>35</v>
       </c>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="E812" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="813" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="813" customHeight="1" ht="17.25" hidden="1">
       <c r="A813" s="1" t="s">
         <v>35</v>
       </c>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="E813" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="814" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="814" customHeight="1" ht="17.25" hidden="1">
       <c r="A814" s="1" t="s">
         <v>35</v>
       </c>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="E814" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="815" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="815" customHeight="1" ht="17.25" hidden="1">
       <c r="A815" s="1" t="s">
         <v>35</v>
       </c>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="E815" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="816" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="816" customHeight="1" ht="17.25" hidden="1">
       <c r="A816" s="1" t="s">
         <v>35</v>
       </c>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="E816" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="817" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="817" customHeight="1" ht="17.25" hidden="1">
       <c r="A817" s="1" t="s">
         <v>35</v>
       </c>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="E817" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="818" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="818" customHeight="1" ht="17.25" hidden="1">
       <c r="A818" s="1" t="s">
         <v>35</v>
       </c>
@@ -16888,7 +16888,7 @@
       </c>
       <c r="E818" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="819" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="819" customHeight="1" ht="17.25" hidden="1">
       <c r="A819" s="1" t="s">
         <v>35</v>
       </c>
@@ -16903,7 +16903,7 @@
       </c>
       <c r="E819" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="820" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="820" customHeight="1" ht="17.25" hidden="1">
       <c r="A820" s="1" t="s">
         <v>35</v>
       </c>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="E820" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="821" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="821" customHeight="1" ht="17.25" hidden="1">
       <c r="A821" s="1" t="s">
         <v>35</v>
       </c>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="E821" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="822" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="822" customHeight="1" ht="17.25" hidden="1">
       <c r="A822" s="1" t="s">
         <v>35</v>
       </c>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="E822" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="823" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="823" customHeight="1" ht="17.25" hidden="1">
       <c r="A823" s="1" t="s">
         <v>35</v>
       </c>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="E823" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="824" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="824" customHeight="1" ht="17.25" hidden="1">
       <c r="A824" s="1" t="s">
         <v>35</v>
       </c>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="E824" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="825" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="825" customHeight="1" ht="17.25" hidden="1">
       <c r="A825" s="1" t="s">
         <v>35</v>
       </c>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="E825" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="826" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="826" customHeight="1" ht="17.25" hidden="1">
       <c r="A826" s="1" t="s">
         <v>35</v>
       </c>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="E826" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="827" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="827" customHeight="1" ht="17.25" hidden="1">
       <c r="A827" s="1" t="s">
         <v>35</v>
       </c>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="E827" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="828" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="828" customHeight="1" ht="17.25" hidden="1">
       <c r="A828" s="1" t="s">
         <v>35</v>
       </c>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="E828" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="829" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="829" customHeight="1" ht="17.25" hidden="1">
       <c r="A829" s="1" t="s">
         <v>35</v>
       </c>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="E829" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="830" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="830" customHeight="1" ht="17.25" hidden="1">
       <c r="A830" s="1" t="s">
         <v>35</v>
       </c>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="E830" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="831" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="831" customHeight="1" ht="17.25" hidden="1">
       <c r="A831" s="1" t="s">
         <v>35</v>
       </c>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="E831" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="832" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="832" customHeight="1" ht="17.25" hidden="1">
       <c r="A832" s="1" t="s">
         <v>35</v>
       </c>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="E832" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="833" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="833" customHeight="1" ht="17.25" hidden="1">
       <c r="A833" s="1" t="s">
         <v>35</v>
       </c>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="E833" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="834" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="834" customHeight="1" ht="17.25" hidden="1">
       <c r="A834" s="1" t="s">
         <v>35</v>
       </c>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="E834" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="835" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="835" customHeight="1" ht="17.25" hidden="1">
       <c r="A835" s="1" t="s">
         <v>35</v>
       </c>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="E835" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="836" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="836" customHeight="1" ht="17.25" hidden="1">
       <c r="A836" s="1" t="s">
         <v>35</v>
       </c>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="E836" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="837" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="837" customHeight="1" ht="17.25" hidden="1">
       <c r="A837" s="1" t="s">
         <v>35</v>
       </c>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="E837" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="838" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="838" customHeight="1" ht="17.25" hidden="1">
       <c r="A838" s="1" t="s">
         <v>35</v>
       </c>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="E838" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="839" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="839" customHeight="1" ht="17.25" hidden="1">
       <c r="A839" s="1" t="s">
         <v>35</v>
       </c>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="E839" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="840" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="840" customHeight="1" ht="17.25" hidden="1">
       <c r="A840" s="1" t="s">
         <v>35</v>
       </c>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="E840" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="841" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="841" customHeight="1" ht="17.25" hidden="1">
       <c r="A841" s="1" t="s">
         <v>35</v>
       </c>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="E841" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="842" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="842" customHeight="1" ht="17.25" hidden="1">
       <c r="A842" s="1" t="s">
         <v>35</v>
       </c>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E842" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="843" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="843" customHeight="1" ht="17.25" hidden="1">
       <c r="A843" s="1" t="s">
         <v>35</v>
       </c>
@@ -17263,7 +17263,7 @@
       </c>
       <c r="E843" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="844" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="844" customHeight="1" ht="17.25" hidden="1">
       <c r="A844" s="1" t="s">
         <v>35</v>
       </c>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="E844" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="845" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="845" customHeight="1" ht="17.25" hidden="1">
       <c r="A845" s="1" t="s">
         <v>35</v>
       </c>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="E845" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="846" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="846" customHeight="1" ht="17.25" hidden="1">
       <c r="A846" s="1" t="s">
         <v>35</v>
       </c>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="E846" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="847" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="847" customHeight="1" ht="17.25" hidden="1">
       <c r="A847" s="1" t="s">
         <v>35</v>
       </c>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="E847" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="848" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="848" customHeight="1" ht="17.25" hidden="1">
       <c r="A848" s="1" t="s">
         <v>35</v>
       </c>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="E848" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="849" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="849" customHeight="1" ht="17.25" hidden="1">
       <c r="A849" s="1" t="s">
         <v>35</v>
       </c>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="E849" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="850" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="850" customHeight="1" ht="17.25" hidden="1">
       <c r="A850" s="1" t="s">
         <v>35</v>
       </c>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="E850" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="851" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="851" customHeight="1" ht="17.25" hidden="1">
       <c r="A851" s="1" t="s">
         <v>35</v>
       </c>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="E851" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="852" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="852" customHeight="1" ht="17.25" hidden="1">
       <c r="A852" s="1" t="s">
         <v>35</v>
       </c>
@@ -17398,7 +17398,7 @@
       </c>
       <c r="E852" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="853" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="853" customHeight="1" ht="17.25" hidden="1">
       <c r="A853" s="1" t="s">
         <v>35</v>
       </c>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="E853" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="854" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="854" customHeight="1" ht="17.25" hidden="1">
       <c r="A854" s="1" t="s">
         <v>35</v>
       </c>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="E854" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="855" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="855" customHeight="1" ht="17.25" hidden="1">
       <c r="A855" s="1" t="s">
         <v>35</v>
       </c>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="E855" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="856" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="856" customHeight="1" ht="17.25" hidden="1">
       <c r="A856" s="1" t="s">
         <v>35</v>
       </c>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="E856" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="857" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="857" customHeight="1" ht="17.25" hidden="1">
       <c r="A857" s="1" t="s">
         <v>35</v>
       </c>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="E857" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="858" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="858" customHeight="1" ht="17.25" hidden="1">
       <c r="A858" s="1" t="s">
         <v>35</v>
       </c>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="E858" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="859" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="859" customHeight="1" ht="17.25" hidden="1">
       <c r="A859" s="1" t="s">
         <v>35</v>
       </c>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="E859" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="860" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="860" customHeight="1" ht="17.25" hidden="1">
       <c r="A860" s="1" t="s">
         <v>35</v>
       </c>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="E860" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="861" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="861" customHeight="1" ht="17.25" hidden="1">
       <c r="A861" s="1" t="s">
         <v>35</v>
       </c>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="E861" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="862" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="862" customHeight="1" ht="17.25" hidden="1">
       <c r="A862" s="1" t="s">
         <v>35</v>
       </c>
@@ -17548,7 +17548,7 @@
       </c>
       <c r="E862" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="863" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="863" customHeight="1" ht="17.25" hidden="1">
       <c r="A863" s="1" t="s">
         <v>35</v>
       </c>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="E863" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="864" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="864" customHeight="1" ht="17.25" hidden="1">
       <c r="A864" s="1" t="s">
         <v>35</v>
       </c>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="E864" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="865" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="865" customHeight="1" ht="17.25" hidden="1">
       <c r="A865" s="1" t="s">
         <v>35</v>
       </c>
@@ -17593,7 +17593,7 @@
       </c>
       <c r="E865" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="866" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="866" customHeight="1" ht="17.25" hidden="1">
       <c r="A866" s="1" t="s">
         <v>35</v>
       </c>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="E866" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="867" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="867" customHeight="1" ht="17.25" hidden="1">
       <c r="A867" s="1" t="s">
         <v>35</v>
       </c>
@@ -17618,10 +17618,10 @@
       <c r="C867" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="D867" s="3"/>
+      <c r="D867" s="1"/>
       <c r="E867" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="868" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="868" customHeight="1" ht="17.25" hidden="1">
       <c r="A868" s="1" t="s">
         <v>35</v>
       </c>
@@ -17636,7 +17636,7 @@
       </c>
       <c r="E868" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="869" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="869" customHeight="1" ht="17.25" hidden="1">
       <c r="A869" s="1" t="s">
         <v>35</v>
       </c>
@@ -17646,10 +17646,10 @@
       <c r="C869" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="D869" s="3"/>
+      <c r="D869" s="1"/>
       <c r="E869" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="870" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="870" customHeight="1" ht="17.25" hidden="1">
       <c r="A870" s="1" t="s">
         <v>35</v>
       </c>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="E870" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="871" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="871" customHeight="1" ht="17.25" hidden="1">
       <c r="A871" s="1" t="s">
         <v>35</v>
       </c>
@@ -17679,7 +17679,7 @@
       </c>
       <c r="E871" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="872" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="872" customHeight="1" ht="17.25" hidden="1">
       <c r="A872" s="1" t="s">
         <v>35</v>
       </c>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="E872" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="873" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="873" customHeight="1" ht="17.25" hidden="1">
       <c r="A873" s="1" t="s">
         <v>35</v>
       </c>
@@ -17704,10 +17704,10 @@
       <c r="C873" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="D873" s="3"/>
+      <c r="D873" s="1"/>
       <c r="E873" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="874" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="874" customHeight="1" ht="17.25" hidden="1">
       <c r="A874" s="1" t="s">
         <v>35</v>
       </c>
@@ -17722,7 +17722,7 @@
       </c>
       <c r="E874" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="875" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="875" customHeight="1" ht="17.25" hidden="1">
       <c r="A875" s="1" t="s">
         <v>35</v>
       </c>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="E875" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="876" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="876" customHeight="1" ht="17.25" hidden="1">
       <c r="A876" s="1" t="s">
         <v>35</v>
       </c>
@@ -17747,10 +17747,10 @@
       <c r="C876" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="D876" s="3"/>
+      <c r="D876" s="1"/>
       <c r="E876" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="877" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="877" customHeight="1" ht="17.25" hidden="1">
       <c r="A877" s="1" t="s">
         <v>35</v>
       </c>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="E877" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="878" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="878" customHeight="1" ht="17.25" hidden="1">
       <c r="A878" s="1" t="s">
         <v>35</v>
       </c>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="E878" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="879" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="879" customHeight="1" ht="17.25" hidden="1">
       <c r="A879" s="1" t="s">
         <v>35</v>
       </c>
@@ -17795,7 +17795,7 @@
       </c>
       <c r="E879" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="880" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="880" customHeight="1" ht="17.25" hidden="1">
       <c r="A880" s="1" t="s">
         <v>35</v>
       </c>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="E880" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="881" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="881" customHeight="1" ht="17.25" hidden="1">
       <c r="A881" s="1" t="s">
         <v>35</v>
       </c>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="E881" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="882" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="882" customHeight="1" ht="17.25" hidden="1">
       <c r="A882" s="1" t="s">
         <v>35</v>
       </c>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="E882" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="883" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="883" customHeight="1" ht="17.25" hidden="1">
       <c r="A883" s="1" t="s">
         <v>35</v>
       </c>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="E883" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="884" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="884" customHeight="1" ht="17.25" hidden="1">
       <c r="A884" s="1" t="s">
         <v>35</v>
       </c>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="E884" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="885" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="885" customHeight="1" ht="17.25" hidden="1">
       <c r="A885" s="1" t="s">
         <v>35</v>
       </c>
@@ -17885,7 +17885,7 @@
       </c>
       <c r="E885" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="886" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="886" customHeight="1" ht="17.25" hidden="1">
       <c r="A886" s="1" t="s">
         <v>35</v>
       </c>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="E886" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="887" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="887" customHeight="1" ht="17.25" hidden="1">
       <c r="A887" s="1" t="s">
         <v>35</v>
       </c>
@@ -17915,7 +17915,7 @@
       </c>
       <c r="E887" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="888" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="888" customHeight="1" ht="17.25" hidden="1">
       <c r="A888" s="1" t="s">
         <v>35</v>
       </c>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="E888" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="889" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="889" customHeight="1" ht="17.25" hidden="1">
       <c r="A889" s="1" t="s">
         <v>35</v>
       </c>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E889" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="890" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="890" customHeight="1" ht="17.25" hidden="1">
       <c r="A890" s="1" t="s">
         <v>35</v>
       </c>
@@ -17960,7 +17960,7 @@
       </c>
       <c r="E890" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="891" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="891" customHeight="1" ht="17.25" hidden="1">
       <c r="A891" s="1" t="s">
         <v>35</v>
       </c>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="E891" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="892" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="892" customHeight="1" ht="17.25" hidden="1">
       <c r="A892" s="1" t="s">
         <v>35</v>
       </c>
@@ -17985,10 +17985,10 @@
       <c r="C892" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="D892" s="3"/>
+      <c r="D892" s="1"/>
       <c r="E892" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="893" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="893" customHeight="1" ht="17.25" hidden="1">
       <c r="A893" s="1" t="s">
         <v>35</v>
       </c>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="E893" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="894" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="894" customHeight="1" ht="17.25" hidden="1">
       <c r="A894" s="1" t="s">
         <v>35</v>
       </c>
@@ -18018,7 +18018,7 @@
       </c>
       <c r="E894" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="895" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="895" customHeight="1" ht="17.25" hidden="1">
       <c r="A895" s="1" t="s">
         <v>35</v>
       </c>
@@ -18033,7 +18033,7 @@
       </c>
       <c r="E895" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="896" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="896" customHeight="1" ht="17.25" hidden="1">
       <c r="A896" s="1" t="s">
         <v>35</v>
       </c>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="E896" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="897" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="897" customHeight="1" ht="17.25" hidden="1">
       <c r="A897" s="1" t="s">
         <v>35</v>
       </c>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="E897" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="898" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="898" customHeight="1" ht="17.25" hidden="1">
       <c r="A898" s="1" t="s">
         <v>35</v>
       </c>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="E898" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="899" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="899" customHeight="1" ht="17.25" hidden="1">
       <c r="A899" s="1" t="s">
         <v>35</v>
       </c>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="E899" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="900" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="900" customHeight="1" ht="17.25" hidden="1">
       <c r="A900" s="1" t="s">
         <v>35</v>
       </c>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="E900" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="901" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="901" customHeight="1" ht="17.25" hidden="1">
       <c r="A901" s="1" t="s">
         <v>35</v>
       </c>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="E901" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="902" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="902" customHeight="1" ht="17.25" hidden="1">
       <c r="A902" s="1" t="s">
         <v>35</v>
       </c>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="E902" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="903" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="903" customHeight="1" ht="17.25" hidden="1">
       <c r="A903" s="1" t="s">
         <v>35</v>
       </c>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="E903" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="904" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="904" customHeight="1" ht="17.25" hidden="1">
       <c r="A904" s="1" t="s">
         <v>35</v>
       </c>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="E904" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="905" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="905" customHeight="1" ht="17.25" hidden="1">
       <c r="A905" s="1" t="s">
         <v>35</v>
       </c>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="E905" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="906" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="906" customHeight="1" ht="17.25" hidden="1">
       <c r="A906" s="1" t="s">
         <v>35</v>
       </c>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="E906" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="907" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="907" customHeight="1" ht="17.25" hidden="1">
       <c r="A907" s="1" t="s">
         <v>35</v>
       </c>
@@ -18213,7 +18213,7 @@
       </c>
       <c r="E907" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="908" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="908" customHeight="1" ht="17.25" hidden="1">
       <c r="A908" s="1" t="s">
         <v>35</v>
       </c>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="E908" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="909" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="909" customHeight="1" ht="17.25" hidden="1">
       <c r="A909" s="1" t="s">
         <v>35</v>
       </c>
@@ -18243,7 +18243,7 @@
       </c>
       <c r="E909" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="910" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="910" customHeight="1" ht="17.25" hidden="1">
       <c r="A910" s="1" t="s">
         <v>35</v>
       </c>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="E910" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="911" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="911" customHeight="1" ht="17.25" hidden="1">
       <c r="A911" s="1" t="s">
         <v>35</v>
       </c>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E911" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="912" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="912" customHeight="1" ht="17.25" hidden="1">
       <c r="A912" s="1" t="s">
         <v>35</v>
       </c>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="E912" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="913" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="913" customHeight="1" ht="17.25" hidden="1">
       <c r="A913" s="1" t="s">
         <v>35</v>
       </c>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="E913" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="914" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="914" customHeight="1" ht="17.25" hidden="1">
       <c r="A914" s="1" t="s">
         <v>35</v>
       </c>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="E914" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="915" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="915" customHeight="1" ht="17.25" hidden="1">
       <c r="A915" s="1" t="s">
         <v>35</v>
       </c>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="E915" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="916" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="916" customHeight="1" ht="17.25" hidden="1">
       <c r="A916" s="1" t="s">
         <v>35</v>
       </c>
@@ -18348,7 +18348,7 @@
       </c>
       <c r="E916" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="917" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="917" customHeight="1" ht="17.25" hidden="1">
       <c r="A917" s="1" t="s">
         <v>35</v>
       </c>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="E917" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="918" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="918" customHeight="1" ht="17.25" hidden="1">
       <c r="A918" s="1" t="s">
         <v>35</v>
       </c>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="E918" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="919" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="919" customHeight="1" ht="17.25" hidden="1">
       <c r="A919" s="1" t="s">
         <v>35</v>
       </c>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="E919" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="920" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="920" customHeight="1" ht="17.25" hidden="1">
       <c r="A920" s="1" t="s">
         <v>35</v>
       </c>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="E920" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="921" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="921" customHeight="1" ht="17.25" hidden="1">
       <c r="A921" s="1" t="s">
         <v>35</v>
       </c>
@@ -18418,10 +18418,10 @@
       <c r="C921" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="D921" s="3"/>
+      <c r="D921" s="1"/>
       <c r="E921" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="922" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="922" customHeight="1" ht="17.25" hidden="1">
       <c r="A922" s="1" t="s">
         <v>35</v>
       </c>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="E922" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="923" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="923" customHeight="1" ht="17.25" hidden="1">
       <c r="A923" s="1" t="s">
         <v>35</v>
       </c>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="E923" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="924" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="924" customHeight="1" ht="17.25" hidden="1">
       <c r="A924" s="1" t="s">
         <v>35</v>
       </c>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="E924" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="925" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="925" customHeight="1" ht="17.25" hidden="1">
       <c r="A925" s="1" t="s">
         <v>35</v>
       </c>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="E925" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="926" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="926" customHeight="1" ht="17.25" hidden="1">
       <c r="A926" s="1" t="s">
         <v>35</v>
       </c>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="E926" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="927" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="927" customHeight="1" ht="17.25" hidden="1">
       <c r="A927" s="1" t="s">
         <v>35</v>
       </c>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="E927" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="928" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="928" customHeight="1" ht="17.25" hidden="1">
       <c r="A928" s="1" t="s">
         <v>35</v>
       </c>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E928" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="929" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="929" customHeight="1" ht="17.25" hidden="1">
       <c r="A929" s="1" t="s">
         <v>35</v>
       </c>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="E929" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="930" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="930" customHeight="1" ht="17.25" hidden="1">
       <c r="A930" s="1" t="s">
         <v>35</v>
       </c>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="E930" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="931" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="931" customHeight="1" ht="17.25" hidden="1">
       <c r="A931" s="1" t="s">
         <v>35</v>
       </c>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="E931" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="932" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="932" customHeight="1" ht="17.25" hidden="1">
       <c r="A932" s="1" t="s">
         <v>35</v>
       </c>
@@ -18586,7 +18586,7 @@
       </c>
       <c r="E932" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="933" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="933" customHeight="1" ht="17.25" hidden="1">
       <c r="A933" s="1" t="s">
         <v>35</v>
       </c>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E933" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="934" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="934" customHeight="1" ht="17.25" hidden="1">
       <c r="A934" s="1" t="s">
         <v>35</v>
       </c>
@@ -18616,7 +18616,7 @@
       </c>
       <c r="E934" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="935" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="935" customHeight="1" ht="17.25" hidden="1">
       <c r="A935" s="1" t="s">
         <v>35</v>
       </c>
@@ -18631,7 +18631,7 @@
       </c>
       <c r="E935" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="936" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="936" customHeight="1" ht="17.25" hidden="1">
       <c r="A936" s="1" t="s">
         <v>35</v>
       </c>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="E936" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="937" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="937" customHeight="1" ht="17.25" hidden="1">
       <c r="A937" s="1" t="s">
         <v>35</v>
       </c>
@@ -18656,10 +18656,10 @@
       <c r="C937" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="D937" s="3"/>
+      <c r="D937" s="1"/>
       <c r="E937" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="938" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="938" customHeight="1" ht="17.25" hidden="1">
       <c r="A938" s="1" t="s">
         <v>35</v>
       </c>
@@ -18674,7 +18674,7 @@
       </c>
       <c r="E938" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="939" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="939" customHeight="1" ht="17.25" hidden="1">
       <c r="A939" s="1" t="s">
         <v>35</v>
       </c>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="E939" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="940" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="940" customHeight="1" ht="17.25" hidden="1">
       <c r="A940" s="1" t="s">
         <v>35</v>
       </c>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="E940" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="941" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="941" customHeight="1" ht="17.25" hidden="1">
       <c r="A941" s="1" t="s">
         <v>35</v>
       </c>
@@ -18719,7 +18719,7 @@
       </c>
       <c r="E941" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="942" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="942" customHeight="1" ht="17.25" hidden="1">
       <c r="A942" s="1" t="s">
         <v>35</v>
       </c>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="E942" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="943" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="943" customHeight="1" ht="17.25" hidden="1">
       <c r="A943" s="1" t="s">
         <v>35</v>
       </c>
@@ -18749,7 +18749,7 @@
       </c>
       <c r="E943" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="944" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="944" customHeight="1" ht="17.25" hidden="1">
       <c r="A944" s="1" t="s">
         <v>35</v>
       </c>
@@ -18764,7 +18764,7 @@
       </c>
       <c r="E944" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="945" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="945" customHeight="1" ht="17.25" hidden="1">
       <c r="A945" s="1" t="s">
         <v>35</v>
       </c>
@@ -18779,7 +18779,7 @@
       </c>
       <c r="E945" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="946" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="946" customHeight="1" ht="17.25" hidden="1">
       <c r="A946" s="1" t="s">
         <v>35</v>
       </c>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="E946" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="947" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="947" customHeight="1" ht="17.25" hidden="1">
       <c r="A947" s="1" t="s">
         <v>35</v>
       </c>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E947" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="948" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="948" customHeight="1" ht="17.25" hidden="1">
       <c r="A948" s="1" t="s">
         <v>35</v>
       </c>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="E948" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="949" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="949" customHeight="1" ht="17.25" hidden="1">
       <c r="A949" s="1" t="s">
         <v>35</v>
       </c>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="E949" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="950" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="950" customHeight="1" ht="17.25" hidden="1">
       <c r="A950" s="1" t="s">
         <v>35</v>
       </c>
@@ -18849,10 +18849,10 @@
       <c r="C950" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="D950" s="3"/>
+      <c r="D950" s="1"/>
       <c r="E950" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="951" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="951" customHeight="1" ht="17.25" hidden="1">
       <c r="A951" s="1" t="s">
         <v>35</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="E951" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="952" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="952" customHeight="1" ht="17.25" hidden="1">
       <c r="A952" s="1" t="s">
         <v>35</v>
       </c>
@@ -18882,7 +18882,7 @@
       </c>
       <c r="E952" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="953" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="953" customHeight="1" ht="17.25" hidden="1">
       <c r="A953" s="1" t="s">
         <v>35</v>
       </c>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="E953" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="954" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="954" customHeight="1" ht="17.25" hidden="1">
       <c r="A954" s="1" t="s">
         <v>35</v>
       </c>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="E956" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="957" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="957" customHeight="1" ht="18.75">
       <c r="A957" s="1" t="s">
         <v>35</v>
       </c>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="E957" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="958" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="958" customHeight="1" ht="18.75">
       <c r="A958" s="1" t="s">
         <v>35</v>
       </c>
@@ -18972,7 +18972,7 @@
       </c>
       <c r="E958" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="959" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="959" customHeight="1" ht="18.75">
       <c r="A959" s="1" t="s">
         <v>35</v>
       </c>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="E959" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="960" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="960" customHeight="1" ht="18.75">
       <c r="A960" s="1" t="s">
         <v>35</v>
       </c>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="E960" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="961" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="961" customHeight="1" ht="18.75">
       <c r="A961" s="1" t="s">
         <v>35</v>
       </c>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="E961" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="962" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="962" customHeight="1" ht="18.75">
       <c r="A962" s="1" t="s">
         <v>35</v>
       </c>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E962" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="963" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="963" customHeight="1" ht="18.75">
       <c r="A963" s="1" t="s">
         <v>35</v>
       </c>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="E963" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="964" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="964" customHeight="1" ht="18.75">
       <c r="A964" s="1" t="s">
         <v>35</v>
       </c>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="E964" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="965" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="965" customHeight="1" ht="18.75">
       <c r="A965" s="1" t="s">
         <v>35</v>
       </c>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="E965" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="966" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="966" customHeight="1" ht="18.75">
       <c r="A966" s="1" t="s">
         <v>35</v>
       </c>
@@ -19092,7 +19092,7 @@
       </c>
       <c r="E966" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="967" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="967" customHeight="1" ht="18.75">
       <c r="A967" s="1" t="s">
         <v>35</v>
       </c>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="E967" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="968" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="968" customHeight="1" ht="18.75">
       <c r="A968" s="1" t="s">
         <v>35</v>
       </c>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="E968" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="969" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="969" customHeight="1" ht="18.75">
       <c r="A969" s="1" t="s">
         <v>35</v>
       </c>
@@ -19132,10 +19132,10 @@
       <c r="C969" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D969" s="3"/>
+      <c r="D969" s="1"/>
       <c r="E969" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="970" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="970" customHeight="1" ht="18.75">
       <c r="A970" s="1" t="s">
         <v>35</v>
       </c>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E970" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="971" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="971" customHeight="1" ht="18.75">
       <c r="A971" s="1" t="s">
         <v>35</v>
       </c>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="E971" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="972" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="972" customHeight="1" ht="18.75">
       <c r="A972" s="1" t="s">
         <v>35</v>
       </c>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="E972" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="973" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="973" customHeight="1" ht="18.75">
       <c r="A973" s="1" t="s">
         <v>35</v>
       </c>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="E973" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="974" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="974" customHeight="1" ht="18.75">
       <c r="A974" s="1" t="s">
         <v>35</v>
       </c>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="E974" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="975" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="975" customHeight="1" ht="18.75">
       <c r="A975" s="1" t="s">
         <v>35</v>
       </c>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="E976" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="977" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="977" customHeight="1" ht="18.75">
       <c r="A977" s="1" t="s">
         <v>35</v>
       </c>
@@ -19250,10 +19250,12 @@
       <c r="C977" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="D977" s="3"/>
+      <c r="D977" s="1" t="s">
+        <v>472</v>
+      </c>
       <c r="E977" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="978" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="978" customHeight="1" ht="18.75">
       <c r="A978" s="1" t="s">
         <v>35</v>
       </c>
@@ -19263,12 +19265,10 @@
       <c r="C978" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="D978" s="1" t="s">
-        <v>1350</v>
-      </c>
+      <c r="D978" s="1"/>
       <c r="E978" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="979" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="979" customHeight="1" ht="18.75">
       <c r="A979" s="1" t="s">
         <v>35</v>
       </c>
@@ -19276,10 +19276,10 @@
         <v>1325</v>
       </c>
       <c r="C979" s="1" t="s">
-        <v>656</v>
+        <v>1350</v>
       </c>
       <c r="D979" s="1" t="s">
-        <v>654</v>
+        <v>1351</v>
       </c>
       <c r="E979" s="2"/>
     </row>
@@ -19291,10 +19291,10 @@
         <v>1325</v>
       </c>
       <c r="C980" s="1" t="s">
-        <v>1351</v>
+        <v>656</v>
       </c>
       <c r="D980" s="1" t="s">
-        <v>1352</v>
+        <v>654</v>
       </c>
       <c r="E980" s="2"/>
     </row>
@@ -19306,10 +19306,10 @@
         <v>1325</v>
       </c>
       <c r="C981" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D981" s="1" t="s">
         <v>1353</v>
-      </c>
-      <c r="D981" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="E981" s="2"/>
     </row>
@@ -19321,10 +19321,10 @@
         <v>1325</v>
       </c>
       <c r="C982" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D982" s="1" t="s">
         <v>1355</v>
-      </c>
-      <c r="D982" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="E982" s="2"/>
     </row>
@@ -19339,7 +19339,7 @@
         <v>1356</v>
       </c>
       <c r="D983" s="1" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="E983" s="2"/>
     </row>
@@ -19354,7 +19354,7 @@
         <v>1357</v>
       </c>
       <c r="D984" s="1" t="s">
-        <v>654</v>
+        <v>1353</v>
       </c>
       <c r="E984" s="2"/>
     </row>
@@ -19366,9 +19366,11 @@
         <v>1325</v>
       </c>
       <c r="C985" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="D985" s="3"/>
+        <v>1358</v>
+      </c>
+      <c r="D985" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="E985" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="986" customHeight="1" ht="17.25">
@@ -19379,11 +19381,9 @@
         <v>1325</v>
       </c>
       <c r="C986" s="1" t="s">
-        <v>1358</v>
-      </c>
-      <c r="D986" s="1" t="s">
-        <v>1359</v>
-      </c>
+        <v>722</v>
+      </c>
+      <c r="D986" s="1"/>
       <c r="E986" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="987" customHeight="1" ht="17.25">
@@ -19394,10 +19394,10 @@
         <v>1325</v>
       </c>
       <c r="C987" s="1" t="s">
-        <v>779</v>
+        <v>1359</v>
       </c>
       <c r="D987" s="1" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E987" s="2"/>
     </row>
@@ -19409,10 +19409,10 @@
         <v>1325</v>
       </c>
       <c r="C988" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D988" s="1" t="s">
         <v>1360</v>
-      </c>
-      <c r="D988" s="1" t="s">
-        <v>1359</v>
       </c>
       <c r="E988" s="2"/>
     </row>
@@ -19427,7 +19427,7 @@
         <v>1361</v>
       </c>
       <c r="D989" s="1" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="E989" s="2"/>
     </row>
@@ -19439,10 +19439,10 @@
         <v>1325</v>
       </c>
       <c r="C990" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D990" s="1" t="s">
         <v>1363</v>
-      </c>
-      <c r="D990" s="1" t="s">
-        <v>1362</v>
       </c>
       <c r="E990" s="2"/>
     </row>
@@ -19454,10 +19454,10 @@
         <v>1325</v>
       </c>
       <c r="C991" s="1" t="s">
-        <v>785</v>
+        <v>1364</v>
       </c>
       <c r="D991" s="1" t="s">
-        <v>787</v>
+        <v>1363</v>
       </c>
       <c r="E991" s="2"/>
     </row>
@@ -19484,7 +19484,7 @@
         <v>1325</v>
       </c>
       <c r="C993" s="1" t="s">
-        <v>1364</v>
+        <v>785</v>
       </c>
       <c r="D993" s="1" t="s">
         <v>787</v>
@@ -19502,7 +19502,7 @@
         <v>1365</v>
       </c>
       <c r="D994" s="1" t="s">
-        <v>1362</v>
+        <v>787</v>
       </c>
       <c r="E994" s="2"/>
     </row>
@@ -19517,7 +19517,7 @@
         <v>1366</v>
       </c>
       <c r="D995" s="1" t="s">
-        <v>811</v>
+        <v>1363</v>
       </c>
       <c r="E995" s="2"/>
     </row>
@@ -19547,7 +19547,7 @@
         <v>1368</v>
       </c>
       <c r="D997" s="1" t="s">
-        <v>1369</v>
+        <v>811</v>
       </c>
       <c r="E997" s="2"/>
     </row>
@@ -19559,10 +19559,10 @@
         <v>1325</v>
       </c>
       <c r="C998" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D998" s="1" t="s">
         <v>1370</v>
-      </c>
-      <c r="D998" s="1" t="s">
-        <v>1369</v>
       </c>
       <c r="E998" s="2"/>
     </row>
@@ -19577,7 +19577,7 @@
         <v>1371</v>
       </c>
       <c r="D999" s="1" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="E999" s="2"/>
     </row>
@@ -19589,9 +19589,11 @@
         <v>1325</v>
       </c>
       <c r="C1000" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="D1000" s="3"/>
+        <v>1372</v>
+      </c>
+      <c r="D1000" s="1" t="s">
+        <v>1370</v>
+      </c>
       <c r="E1000" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1001" customHeight="1" ht="17.25">
@@ -19602,11 +19604,9 @@
         <v>1325</v>
       </c>
       <c r="C1001" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="D1001" s="1" t="s">
-        <v>787</v>
-      </c>
+        <v>866</v>
+      </c>
+      <c r="D1001" s="1"/>
       <c r="E1001" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1002" customHeight="1" ht="17.25">
@@ -19617,10 +19617,10 @@
         <v>1325</v>
       </c>
       <c r="C1002" s="1" t="s">
-        <v>62</v>
+        <v>1373</v>
       </c>
       <c r="D1002" s="1" t="s">
-        <v>62</v>
+        <v>787</v>
       </c>
       <c r="E1002" s="2"/>
     </row>
@@ -19632,10 +19632,10 @@
         <v>1325</v>
       </c>
       <c r="C1003" s="1" t="s">
-        <v>1373</v>
+        <v>62</v>
       </c>
       <c r="D1003" s="1" t="s">
-        <v>1374</v>
+        <v>62</v>
       </c>
       <c r="E1003" s="2"/>
     </row>
@@ -19647,10 +19647,10 @@
         <v>1325</v>
       </c>
       <c r="C1004" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D1004" s="1" t="s">
         <v>1375</v>
-      </c>
-      <c r="D1004" s="1" t="s">
-        <v>1376</v>
       </c>
       <c r="E1004" s="2"/>
     </row>
@@ -19662,10 +19662,10 @@
         <v>1325</v>
       </c>
       <c r="C1005" s="1" t="s">
-        <v>972</v>
+        <v>1376</v>
       </c>
       <c r="D1005" s="1" t="s">
-        <v>62</v>
+        <v>1377</v>
       </c>
       <c r="E1005" s="2"/>
     </row>
@@ -19677,10 +19677,10 @@
         <v>1325</v>
       </c>
       <c r="C1006" s="1" t="s">
-        <v>1377</v>
+        <v>972</v>
       </c>
       <c r="D1006" s="1" t="s">
-        <v>1374</v>
+        <v>62</v>
       </c>
       <c r="E1006" s="2"/>
     </row>
@@ -19695,7 +19695,7 @@
         <v>1378</v>
       </c>
       <c r="D1007" s="1" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="E1007" s="2"/>
     </row>
@@ -19707,10 +19707,10 @@
         <v>1325</v>
       </c>
       <c r="C1008" s="1" t="s">
-        <v>975</v>
+        <v>1379</v>
       </c>
       <c r="D1008" s="1" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="E1008" s="2"/>
     </row>
@@ -19722,10 +19722,10 @@
         <v>1325</v>
       </c>
       <c r="C1009" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="D1009" s="1" t="s">
         <v>1380</v>
-      </c>
-      <c r="D1009" s="1" t="s">
-        <v>1379</v>
       </c>
       <c r="E1009" s="2"/>
     </row>
@@ -19740,7 +19740,7 @@
         <v>1381</v>
       </c>
       <c r="D1010" s="1" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="E1010" s="2"/>
     </row>
@@ -19752,10 +19752,10 @@
         <v>1325</v>
       </c>
       <c r="C1011" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D1011" s="1" t="s">
         <v>1383</v>
-      </c>
-      <c r="D1011" s="1" t="s">
-        <v>1382</v>
       </c>
       <c r="E1011" s="2"/>
     </row>
@@ -19770,7 +19770,7 @@
         <v>1384</v>
       </c>
       <c r="D1012" s="1" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="E1012" s="2"/>
     </row>
@@ -19782,10 +19782,10 @@
         <v>1325</v>
       </c>
       <c r="C1013" s="1" t="s">
-        <v>984</v>
+        <v>1385</v>
       </c>
       <c r="D1013" s="1" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
       <c r="E1013" s="2"/>
     </row>
@@ -19797,7 +19797,7 @@
         <v>1325</v>
       </c>
       <c r="C1014" s="1" t="s">
-        <v>106</v>
+        <v>984</v>
       </c>
       <c r="D1014" s="1" t="s">
         <v>1386</v>
@@ -19812,10 +19812,10 @@
         <v>1325</v>
       </c>
       <c r="C1015" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1015" s="1" t="s">
         <v>1387</v>
-      </c>
-      <c r="D1015" s="1" t="s">
-        <v>1386</v>
       </c>
       <c r="E1015" s="2"/>
     </row>
@@ -19830,7 +19830,7 @@
         <v>1388</v>
       </c>
       <c r="D1016" s="1" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="E1016" s="2"/>
     </row>
@@ -19845,7 +19845,7 @@
         <v>1389</v>
       </c>
       <c r="D1017" s="1" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="E1017" s="2"/>
     </row>
@@ -19857,9 +19857,11 @@
         <v>1325</v>
       </c>
       <c r="C1018" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D1018" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="D1018" s="3"/>
       <c r="E1018" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1019" customHeight="1" ht="17.25">
@@ -19872,9 +19874,7 @@
       <c r="C1019" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="D1019" s="1" t="s">
-        <v>1390</v>
-      </c>
+      <c r="D1019" s="1"/>
       <c r="E1019" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1020" customHeight="1" ht="17.25">
@@ -19885,10 +19885,10 @@
         <v>1325</v>
       </c>
       <c r="C1020" s="1" t="s">
-        <v>1229</v>
+        <v>1393</v>
       </c>
       <c r="D1020" s="1" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="E1020" s="2"/>
     </row>
@@ -19900,10 +19900,10 @@
         <v>1325</v>
       </c>
       <c r="C1021" s="1" t="s">
-        <v>1393</v>
+        <v>1229</v>
       </c>
       <c r="D1021" s="1" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="E1021" s="2"/>
     </row>
@@ -19915,12 +19915,27 @@
         <v>1325</v>
       </c>
       <c r="C1022" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D1022" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="D1022" s="1" t="s">
-        <v>1394</v>
-      </c>
       <c r="E1022" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="1023" customHeight="1" ht="17.25">
+      <c r="A1023" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1023" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C1023" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D1023" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E1023" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/fix_values.xlsx
+++ b/data/fix_values.xlsx
@@ -10,14 +10,14 @@
     <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">=Sheet1!$A$1:$D$1023</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">=Sheet1!$A$1:$D$1022</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4092" uniqueCount="1397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4088" uniqueCount="1396">
   <si>
     <t>lab_id</t>
   </si>
@@ -4058,9 +4058,6 @@
   </si>
   <si>
     <t>GO</t>
-  </si>
-  <si>
-    <t>GOIÁS</t>
   </si>
   <si>
     <t>GOIAS</t>
@@ -4263,7 +4260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4272,6 +4269,9 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -4582,17 +4582,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E1023"/>
+  <dimension ref="A1:E1022"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="18.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="51.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="28.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="18.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="51.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -4726,24 +4726,24 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -4760,14 +4760,14 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25" hidden="1">
-      <c r="A11" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+      <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -4777,14 +4777,14 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25" hidden="1">
-      <c r="A12" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+      <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -4794,7 +4794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -4845,14 +4845,14 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25" hidden="1">
-      <c r="A16" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+      <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -4862,14 +4862,14 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25" hidden="1">
-      <c r="A17" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+      <c r="A17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -4879,7 +4879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -4930,41 +4930,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25" hidden="1">
-      <c r="A21" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+      <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25" hidden="1">
-      <c r="A22" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+      <c r="A22" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
@@ -5015,41 +5015,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25" hidden="1">
-      <c r="A26" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+      <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25" hidden="1">
-      <c r="A27" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+      <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
@@ -5100,41 +5100,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25" hidden="1">
-      <c r="A31" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+      <c r="A31" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25" hidden="1">
-      <c r="A32" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+      <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
@@ -5185,41 +5185,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25" hidden="1">
-      <c r="A36" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
+      <c r="A36" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25" hidden="1">
-      <c r="A37" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
+      <c r="A37" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
@@ -5270,41 +5270,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25" hidden="1">
-      <c r="A41" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
+      <c r="A41" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25" hidden="1">
-      <c r="A42" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
+      <c r="A42" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="1" t="s">
         <v>4</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
@@ -5355,41 +5355,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25" hidden="1">
-      <c r="A46" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
+      <c r="A46" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25" hidden="1">
-      <c r="A47" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
+      <c r="A47" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="1" t="s">
         <v>4</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
@@ -5440,41 +5440,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25" hidden="1">
-      <c r="A51" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
+      <c r="A51" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25" hidden="1">
-      <c r="A52" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
+      <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="1" t="s">
         <v>4</v>
       </c>
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="1" t="s">
         <v>4</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="1" t="s">
         <v>4</v>
       </c>
@@ -5525,41 +5525,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25" hidden="1">
-      <c r="A56" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
+      <c r="A56" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25" hidden="1">
-      <c r="A57" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
+      <c r="A57" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="1" t="s">
         <v>4</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="1" t="s">
         <v>4</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="1" t="s">
         <v>4</v>
       </c>
@@ -5610,41 +5610,41 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25" hidden="1">
-      <c r="A61" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+      <c r="A61" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25" hidden="1">
-      <c r="A62" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+      <c r="A62" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
       <c r="A63" s="1" t="s">
         <v>4</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
       <c r="A64" s="1" t="s">
         <v>4</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
       <c r="A65" s="1" t="s">
         <v>4</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
       <c r="A66" s="1" t="s">
         <v>32</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
       <c r="A67" s="1" t="s">
         <v>32</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
       <c r="A68" s="1" t="s">
         <v>32</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
       <c r="A69" s="1" t="s">
         <v>32</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
       <c r="A70" s="1" t="s">
         <v>32</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
       <c r="A71" s="1" t="s">
         <v>32</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
       <c r="A72" s="1" t="s">
         <v>32</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
       <c r="A74" s="1" t="s">
         <v>32</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
       <c r="A75" s="1" t="s">
         <v>35</v>
       </c>
@@ -5858,10 +5858,10 @@
       <c r="C75" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D75" s="1"/>
+      <c r="D75" s="3"/>
       <c r="E75" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E76" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
       <c r="A77" s="1" t="s">
         <v>35</v>
       </c>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
       <c r="A78" s="1" t="s">
         <v>35</v>
       </c>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
       <c r="A79" s="1" t="s">
         <v>35</v>
       </c>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
       <c r="A80" s="1" t="s">
         <v>35</v>
       </c>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
       <c r="A81" s="1" t="s">
         <v>35</v>
       </c>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
       <c r="A82" s="1" t="s">
         <v>35</v>
       </c>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
       <c r="A83" s="1" t="s">
         <v>35</v>
       </c>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
       <c r="A84" s="1" t="s">
         <v>35</v>
       </c>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
       <c r="A85" s="1" t="s">
         <v>35</v>
       </c>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="E85" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
       <c r="A86" s="1" t="s">
         <v>35</v>
       </c>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
       <c r="A87" s="1" t="s">
         <v>35</v>
       </c>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
       <c r="A88" s="1" t="s">
         <v>35</v>
       </c>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
       <c r="A89" s="1" t="s">
         <v>35</v>
       </c>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
       <c r="A90" s="1" t="s">
         <v>35</v>
       </c>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E90" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
       <c r="A91" s="1" t="s">
         <v>35</v>
       </c>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E91" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
       <c r="A92" s="1" t="s">
         <v>35</v>
       </c>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E92" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
       <c r="A93" s="1" t="s">
         <v>35</v>
       </c>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="E93" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
       <c r="A94" s="1" t="s">
         <v>35</v>
       </c>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
       <c r="A95" s="1" t="s">
         <v>35</v>
       </c>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
       <c r="A96" s="1" t="s">
         <v>35</v>
       </c>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
       <c r="A97" s="1" t="s">
         <v>35</v>
       </c>
@@ -6186,10 +6186,10 @@
       <c r="C97" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D97" s="1"/>
+      <c r="D97" s="3"/>
       <c r="E97" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
       <c r="A98" s="1" t="s">
         <v>35</v>
       </c>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="E98" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
       <c r="A99" s="1" t="s">
         <v>35</v>
       </c>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="E99" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
       <c r="A100" s="1" t="s">
         <v>35</v>
       </c>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
       <c r="A101" s="1" t="s">
         <v>35</v>
       </c>
@@ -6244,10 +6244,10 @@
       <c r="C101" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D101" s="1"/>
+      <c r="D101" s="3"/>
       <c r="E101" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
       <c r="A102" s="1" t="s">
         <v>35</v>
       </c>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
       <c r="A103" s="1" t="s">
         <v>35</v>
       </c>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
       <c r="A104" s="1" t="s">
         <v>35</v>
       </c>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
       <c r="A105" s="1" t="s">
         <v>35</v>
       </c>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
       <c r="A106" s="1" t="s">
         <v>35</v>
       </c>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E106" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
       <c r="A107" s="1" t="s">
         <v>35</v>
       </c>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="E107" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
       <c r="A108" s="1" t="s">
         <v>35</v>
       </c>
@@ -6347,10 +6347,10 @@
       <c r="C108" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D108" s="1"/>
+      <c r="D108" s="3"/>
       <c r="E108" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
       <c r="A109" s="1" t="s">
         <v>35</v>
       </c>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E109" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25">
       <c r="A110" s="1" t="s">
         <v>35</v>
       </c>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="E110" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25">
       <c r="A111" s="1" t="s">
         <v>35</v>
       </c>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="E111" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
       <c r="A112" s="1" t="s">
         <v>35</v>
       </c>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="E112" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
       <c r="A113" s="1" t="s">
         <v>35</v>
       </c>
@@ -6420,10 +6420,10 @@
       <c r="C113" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D113" s="1"/>
+      <c r="D113" s="3"/>
       <c r="E113" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
       <c r="A114" s="1" t="s">
         <v>35</v>
       </c>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E114" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
       <c r="A115" s="1" t="s">
         <v>35</v>
       </c>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="E115" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
       <c r="A116" s="1" t="s">
         <v>35</v>
       </c>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="E116" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
       <c r="A117" s="1" t="s">
         <v>35</v>
       </c>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="E117" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
       <c r="A118" s="1" t="s">
         <v>35</v>
       </c>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="E118" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
       <c r="A119" s="1" t="s">
         <v>35</v>
       </c>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E119" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
       <c r="A120" s="1" t="s">
         <v>35</v>
       </c>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="E120" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
       <c r="A121" s="1" t="s">
         <v>35</v>
       </c>
@@ -6538,10 +6538,10 @@
       <c r="C121" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D121" s="1"/>
+      <c r="D121" s="3"/>
       <c r="E121" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25">
       <c r="A122" s="1" t="s">
         <v>35</v>
       </c>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="E122" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25">
       <c r="A123" s="1" t="s">
         <v>35</v>
       </c>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E123" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25">
       <c r="A124" s="1" t="s">
         <v>35</v>
       </c>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="E124" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25">
       <c r="A125" s="1" t="s">
         <v>35</v>
       </c>
@@ -6596,10 +6596,10 @@
       <c r="C125" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D125" s="1"/>
+      <c r="D125" s="3"/>
       <c r="E125" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25">
       <c r="A126" s="1" t="s">
         <v>35</v>
       </c>
@@ -6609,10 +6609,10 @@
       <c r="C126" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D126" s="1"/>
+      <c r="D126" s="3"/>
       <c r="E126" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25">
       <c r="A127" s="1" t="s">
         <v>35</v>
       </c>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E127" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
       <c r="A128" s="1" t="s">
         <v>35</v>
       </c>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="E128" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25">
       <c r="A129" s="1" t="s">
         <v>35</v>
       </c>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="E129" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25">
       <c r="A130" s="1" t="s">
         <v>35</v>
       </c>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="E130" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25">
       <c r="A131" s="1" t="s">
         <v>35</v>
       </c>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E131" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
       <c r="A132" s="1" t="s">
         <v>35</v>
       </c>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="E132" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
       <c r="A133" s="1" t="s">
         <v>35</v>
       </c>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="E133" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25">
       <c r="A134" s="1" t="s">
         <v>35</v>
       </c>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E134" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25">
       <c r="A135" s="1" t="s">
         <v>35</v>
       </c>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="E135" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25">
       <c r="A136" s="1" t="s">
         <v>35</v>
       </c>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E136" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25">
       <c r="A137" s="1" t="s">
         <v>35</v>
       </c>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="E137" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25">
       <c r="A138" s="1" t="s">
         <v>35</v>
       </c>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="E138" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25">
       <c r="A139" s="1" t="s">
         <v>35</v>
       </c>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="E139" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25">
       <c r="A140" s="1" t="s">
         <v>35</v>
       </c>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="E140" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25">
       <c r="A141" s="1" t="s">
         <v>35</v>
       </c>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="E141" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
       <c r="A142" s="1" t="s">
         <v>35</v>
       </c>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="E142" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25">
       <c r="A143" s="1" t="s">
         <v>35</v>
       </c>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="E143" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25">
       <c r="A144" s="1" t="s">
         <v>35</v>
       </c>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E144" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
       <c r="A145" s="1" t="s">
         <v>35</v>
       </c>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="E145" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25">
       <c r="A146" s="1" t="s">
         <v>35</v>
       </c>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E146" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
       <c r="A147" s="1" t="s">
         <v>35</v>
       </c>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="E147" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25">
       <c r="A148" s="1" t="s">
         <v>35</v>
       </c>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="E148" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25">
       <c r="A149" s="1" t="s">
         <v>35</v>
       </c>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="E149" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25">
       <c r="A150" s="1" t="s">
         <v>35</v>
       </c>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="E150" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25">
       <c r="A151" s="1" t="s">
         <v>35</v>
       </c>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="E151" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25">
       <c r="A152" s="1" t="s">
         <v>35</v>
       </c>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="E152" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
       <c r="A153" s="1" t="s">
         <v>35</v>
       </c>
@@ -7012,10 +7012,10 @@
       <c r="C153" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D153" s="1"/>
+      <c r="D153" s="3"/>
       <c r="E153" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25">
       <c r="A154" s="1" t="s">
         <v>35</v>
       </c>
@@ -7025,10 +7025,10 @@
       <c r="C154" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D154" s="1"/>
+      <c r="D154" s="3"/>
       <c r="E154" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
       <c r="A155" s="1" t="s">
         <v>35</v>
       </c>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="E155" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25">
       <c r="A156" s="1" t="s">
         <v>35</v>
       </c>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="E156" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25">
       <c r="A157" s="1" t="s">
         <v>35</v>
       </c>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="E157" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
       <c r="A158" s="1" t="s">
         <v>35</v>
       </c>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="E158" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25">
       <c r="A159" s="1" t="s">
         <v>35</v>
       </c>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="E159" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
       <c r="A160" s="1" t="s">
         <v>35</v>
       </c>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="E160" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
       <c r="A161" s="1" t="s">
         <v>35</v>
       </c>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="E161" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25">
       <c r="A162" s="1" t="s">
         <v>35</v>
       </c>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="E162" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25">
       <c r="A163" s="1" t="s">
         <v>35</v>
       </c>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="E163" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25">
       <c r="A164" s="1" t="s">
         <v>35</v>
       </c>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="E164" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25">
       <c r="A165" s="1" t="s">
         <v>35</v>
       </c>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E165" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25">
       <c r="A166" s="1" t="s">
         <v>35</v>
       </c>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="E166" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25">
       <c r="A167" s="1" t="s">
         <v>35</v>
       </c>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="E167" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25">
       <c r="A168" s="1" t="s">
         <v>35</v>
       </c>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="E168" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
       <c r="A169" s="1" t="s">
         <v>35</v>
       </c>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="E169" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="17.25">
       <c r="A170" s="1" t="s">
         <v>35</v>
       </c>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="E170" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="17.25">
       <c r="A171" s="1" t="s">
         <v>35</v>
       </c>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="E171" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="17.25">
       <c r="A172" s="1" t="s">
         <v>35</v>
       </c>
@@ -7293,10 +7293,10 @@
       <c r="C172" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D172" s="1"/>
+      <c r="D172" s="3"/>
       <c r="E172" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="17.25">
       <c r="A173" s="1" t="s">
         <v>35</v>
       </c>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E173" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="17.25">
       <c r="A174" s="1" t="s">
         <v>35</v>
       </c>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="E174" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="17.25">
       <c r="A175" s="1" t="s">
         <v>35</v>
       </c>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="E175" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="17.25">
       <c r="A176" s="1" t="s">
         <v>35</v>
       </c>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="E176" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="17.25">
       <c r="A177" s="1" t="s">
         <v>35</v>
       </c>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E177" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="17.25">
       <c r="A178" s="1" t="s">
         <v>35</v>
       </c>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="E178" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="17.25">
       <c r="A179" s="1" t="s">
         <v>35</v>
       </c>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="E179" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="17.25">
       <c r="A180" s="1" t="s">
         <v>35</v>
       </c>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E180" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="17.25">
       <c r="A181" s="1" t="s">
         <v>35</v>
       </c>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="E181" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="17.25">
       <c r="A182" s="1" t="s">
         <v>35</v>
       </c>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="E182" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="17.25">
       <c r="A183" s="1" t="s">
         <v>35</v>
       </c>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="E183" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="17.25">
       <c r="A184" s="1" t="s">
         <v>35</v>
       </c>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="E184" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="17.25">
       <c r="A185" s="1" t="s">
         <v>35</v>
       </c>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E185" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="17.25">
       <c r="A186" s="1" t="s">
         <v>35</v>
       </c>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="E186" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="17.25">
       <c r="A187" s="1" t="s">
         <v>35</v>
       </c>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="E187" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="17.25">
       <c r="A188" s="1" t="s">
         <v>35</v>
       </c>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E188" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="17.25">
       <c r="A189" s="1" t="s">
         <v>35</v>
       </c>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="E189" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="17.25">
       <c r="A190" s="1" t="s">
         <v>35</v>
       </c>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="E190" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="17.25">
       <c r="A191" s="1" t="s">
         <v>35</v>
       </c>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="E191" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="17.25">
       <c r="A192" s="1" t="s">
         <v>35</v>
       </c>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="E192" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="17.25">
       <c r="A193" s="1" t="s">
         <v>35</v>
       </c>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="E193" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="17.25">
       <c r="A194" s="1" t="s">
         <v>35</v>
       </c>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E194" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="17.25">
       <c r="A195" s="1" t="s">
         <v>35</v>
       </c>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="E195" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="17.25">
       <c r="A196" s="1" t="s">
         <v>35</v>
       </c>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="E196" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="17.25">
       <c r="A197" s="1" t="s">
         <v>35</v>
       </c>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="E197" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="17.25">
       <c r="A198" s="1" t="s">
         <v>35</v>
       </c>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="E198" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="17.25">
       <c r="A199" s="1" t="s">
         <v>35</v>
       </c>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="E199" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="17.25">
       <c r="A200" s="1" t="s">
         <v>35</v>
       </c>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E200" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="17.25">
       <c r="A201" s="1" t="s">
         <v>35</v>
       </c>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E201" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25">
       <c r="A202" s="1" t="s">
         <v>35</v>
       </c>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="E202" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="17.25">
       <c r="A203" s="1" t="s">
         <v>35</v>
       </c>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="E203" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="17.25">
       <c r="A204" s="1" t="s">
         <v>35</v>
       </c>
@@ -7771,10 +7771,10 @@
       <c r="C204" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D204" s="1"/>
+      <c r="D204" s="3"/>
       <c r="E204" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25">
       <c r="A205" s="1" t="s">
         <v>35</v>
       </c>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="E205" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25">
       <c r="A206" s="1" t="s">
         <v>35</v>
       </c>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="E206" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25">
       <c r="A207" s="1" t="s">
         <v>35</v>
       </c>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="E207" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25">
       <c r="A208" s="1" t="s">
         <v>35</v>
       </c>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E208" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="17.25">
       <c r="A209" s="1" t="s">
         <v>35</v>
       </c>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="E209" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="17.25">
       <c r="A210" s="1" t="s">
         <v>35</v>
       </c>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="E210" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25">
       <c r="A211" s="1" t="s">
         <v>35</v>
       </c>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="E211" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25">
       <c r="A212" s="1" t="s">
         <v>35</v>
       </c>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="E212" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25">
       <c r="A213" s="1" t="s">
         <v>35</v>
       </c>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="E213" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25">
       <c r="A214" s="1" t="s">
         <v>35</v>
       </c>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="E214" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25">
       <c r="A215" s="1" t="s">
         <v>35</v>
       </c>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="E215" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25">
       <c r="A216" s="1" t="s">
         <v>35</v>
       </c>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="E216" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="17.25">
       <c r="A217" s="1" t="s">
         <v>35</v>
       </c>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="E217" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25">
       <c r="A218" s="1" t="s">
         <v>35</v>
       </c>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E218" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25">
       <c r="A219" s="1" t="s">
         <v>35</v>
       </c>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="E219" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="17.25">
       <c r="A220" s="1" t="s">
         <v>35</v>
       </c>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="E220" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25">
       <c r="A221" s="1" t="s">
         <v>35</v>
       </c>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="E221" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="17.25">
       <c r="A222" s="1" t="s">
         <v>35</v>
       </c>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E222" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="17.25">
       <c r="A223" s="1" t="s">
         <v>35</v>
       </c>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E223" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="17.25">
       <c r="A224" s="1" t="s">
         <v>35</v>
       </c>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="E224" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="17.25">
       <c r="A225" s="1" t="s">
         <v>35</v>
       </c>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="E225" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="17.25">
       <c r="A226" s="1" t="s">
         <v>35</v>
       </c>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="E226" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="17.25">
       <c r="A227" s="1" t="s">
         <v>35</v>
       </c>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="E227" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="17.25">
       <c r="A228" s="1" t="s">
         <v>35</v>
       </c>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="E228" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="17.25">
       <c r="A229" s="1" t="s">
         <v>35</v>
       </c>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="E229" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="17.25">
       <c r="A230" s="1" t="s">
         <v>35</v>
       </c>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="E230" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="17.25">
       <c r="A231" s="1" t="s">
         <v>35</v>
       </c>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="E231" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="17.25">
       <c r="A232" s="1" t="s">
         <v>35</v>
       </c>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E232" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="17.25">
       <c r="A233" s="1" t="s">
         <v>35</v>
       </c>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E233" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="17.25">
       <c r="A234" s="1" t="s">
         <v>35</v>
       </c>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="E234" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="17.25">
       <c r="A235" s="1" t="s">
         <v>35</v>
       </c>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="E235" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="17.25">
       <c r="A236" s="1" t="s">
         <v>35</v>
       </c>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="E236" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="17.25">
       <c r="A237" s="1" t="s">
         <v>35</v>
       </c>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="E237" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="17.25">
       <c r="A238" s="1" t="s">
         <v>35</v>
       </c>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="E238" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="17.25">
       <c r="A239" s="1" t="s">
         <v>35</v>
       </c>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="E239" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="17.25">
       <c r="A240" s="1" t="s">
         <v>35</v>
       </c>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="E240" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="17.25">
       <c r="A241" s="1" t="s">
         <v>35</v>
       </c>
@@ -8324,10 +8324,10 @@
       <c r="C241" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D241" s="1"/>
+      <c r="D241" s="3"/>
       <c r="E241" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="17.25">
       <c r="A242" s="1" t="s">
         <v>35</v>
       </c>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="E242" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="17.25">
       <c r="A243" s="1" t="s">
         <v>35</v>
       </c>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="E243" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="17.25">
       <c r="A244" s="1" t="s">
         <v>35</v>
       </c>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E244" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="17.25">
       <c r="A245" s="1" t="s">
         <v>35</v>
       </c>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="E245" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="17.25">
       <c r="A246" s="1" t="s">
         <v>35</v>
       </c>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="E246" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="17.25">
       <c r="A247" s="1" t="s">
         <v>35</v>
       </c>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="E247" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="17.25">
       <c r="A248" s="1" t="s">
         <v>35</v>
       </c>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="E248" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="17.25">
       <c r="A249" s="1" t="s">
         <v>35</v>
       </c>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="E249" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="17.25">
       <c r="A250" s="1" t="s">
         <v>35</v>
       </c>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="E250" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="17.25">
       <c r="A251" s="1" t="s">
         <v>35</v>
       </c>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="E251" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="17.25">
       <c r="A252" s="1" t="s">
         <v>35</v>
       </c>
@@ -8487,10 +8487,10 @@
       <c r="C252" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D252" s="1"/>
+      <c r="D252" s="3"/>
       <c r="E252" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="17.25">
       <c r="A253" s="1" t="s">
         <v>35</v>
       </c>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="E253" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="17.25">
       <c r="A254" s="1" t="s">
         <v>35</v>
       </c>
@@ -8515,10 +8515,10 @@
       <c r="C254" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D254" s="1"/>
+      <c r="D254" s="3"/>
       <c r="E254" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="17.25">
       <c r="A255" s="1" t="s">
         <v>35</v>
       </c>
@@ -8528,10 +8528,10 @@
       <c r="C255" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D255" s="1"/>
+      <c r="D255" s="3"/>
       <c r="E255" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="17.25">
       <c r="A256" s="1" t="s">
         <v>35</v>
       </c>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="E256" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="17.25">
       <c r="A257" s="1" t="s">
         <v>35</v>
       </c>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="E257" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="17.25">
       <c r="A258" s="1" t="s">
         <v>35</v>
       </c>
@@ -8571,10 +8571,10 @@
       <c r="C258" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D258" s="1"/>
+      <c r="D258" s="3"/>
       <c r="E258" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="17.25">
       <c r="A259" s="1" t="s">
         <v>35</v>
       </c>
@@ -8584,10 +8584,10 @@
       <c r="C259" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D259" s="1"/>
+      <c r="D259" s="3"/>
       <c r="E259" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="17.25">
       <c r="A260" s="1" t="s">
         <v>35</v>
       </c>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="E260" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="17.25">
       <c r="A261" s="1" t="s">
         <v>35</v>
       </c>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="E261" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="17.25">
       <c r="A262" s="1" t="s">
         <v>35</v>
       </c>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="E262" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="17.25">
       <c r="A263" s="1" t="s">
         <v>35</v>
       </c>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="E263" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="17.25">
       <c r="A264" s="1" t="s">
         <v>35</v>
       </c>
@@ -8657,10 +8657,10 @@
       <c r="C264" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D264" s="1"/>
+      <c r="D264" s="3"/>
       <c r="E264" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="17.25">
       <c r="A265" s="1" t="s">
         <v>35</v>
       </c>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="E265" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="17.25">
       <c r="A266" s="1" t="s">
         <v>35</v>
       </c>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="E266" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="17.25">
       <c r="A267" s="1" t="s">
         <v>35</v>
       </c>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E267" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="17.25">
       <c r="A268" s="1" t="s">
         <v>35</v>
       </c>
@@ -8715,10 +8715,10 @@
       <c r="C268" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D268" s="1"/>
+      <c r="D268" s="3"/>
       <c r="E268" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="17.25">
       <c r="A269" s="1" t="s">
         <v>35</v>
       </c>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="E269" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="17.25">
       <c r="A270" s="1" t="s">
         <v>35</v>
       </c>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="E270" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="17.25">
       <c r="A271" s="1" t="s">
         <v>35</v>
       </c>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="E271" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="17.25">
       <c r="A272" s="1" t="s">
         <v>35</v>
       </c>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E272" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="17.25">
       <c r="A273" s="1" t="s">
         <v>35</v>
       </c>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="E273" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="17.25">
       <c r="A274" s="1" t="s">
         <v>35</v>
       </c>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="E274" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="17.25">
       <c r="A275" s="1" t="s">
         <v>35</v>
       </c>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E275" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="17.25">
       <c r="A276" s="1" t="s">
         <v>35</v>
       </c>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="E276" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="17.25">
       <c r="A277" s="1" t="s">
         <v>35</v>
       </c>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="E277" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="17.25">
       <c r="A278" s="1" t="s">
         <v>35</v>
       </c>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="E278" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="17.25">
       <c r="A279" s="1" t="s">
         <v>35</v>
       </c>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="E279" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="17.25">
       <c r="A280" s="1" t="s">
         <v>35</v>
       </c>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="E280" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="17.25">
       <c r="A281" s="1" t="s">
         <v>35</v>
       </c>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="E281" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="17.25">
       <c r="A282" s="1" t="s">
         <v>35</v>
       </c>
@@ -8923,10 +8923,10 @@
       <c r="C282" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D282" s="1"/>
+      <c r="D282" s="3"/>
       <c r="E282" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="17.25">
       <c r="A283" s="1" t="s">
         <v>35</v>
       </c>
@@ -8936,10 +8936,10 @@
       <c r="C283" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D283" s="1"/>
+      <c r="D283" s="3"/>
       <c r="E283" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="17.25">
       <c r="A284" s="1" t="s">
         <v>35</v>
       </c>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="E284" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="17.25">
       <c r="A285" s="1" t="s">
         <v>35</v>
       </c>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="E285" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="17.25">
       <c r="A286" s="1" t="s">
         <v>35</v>
       </c>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="E286" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="17.25">
       <c r="A287" s="1" t="s">
         <v>35</v>
       </c>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="E287" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="17.25">
       <c r="A288" s="1" t="s">
         <v>35</v>
       </c>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="E288" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="17.25">
       <c r="A289" s="1" t="s">
         <v>35</v>
       </c>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="E289" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="17.25">
       <c r="A290" s="1" t="s">
         <v>35</v>
       </c>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="E290" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="17.25">
       <c r="A291" s="1" t="s">
         <v>35</v>
       </c>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="E291" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="17.25">
       <c r="A292" s="1" t="s">
         <v>35</v>
       </c>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="E292" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="17.25">
       <c r="A293" s="1" t="s">
         <v>35</v>
       </c>
@@ -9084,10 +9084,10 @@
       <c r="C293" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D293" s="1"/>
+      <c r="D293" s="3"/>
       <c r="E293" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="17.25">
       <c r="A294" s="1" t="s">
         <v>35</v>
       </c>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="E294" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="17.25">
       <c r="A295" s="1" t="s">
         <v>35</v>
       </c>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="E295" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="17.25">
       <c r="A296" s="1" t="s">
         <v>35</v>
       </c>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="E296" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="17.25">
       <c r="A297" s="1" t="s">
         <v>35</v>
       </c>
@@ -9142,10 +9142,10 @@
       <c r="C297" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D297" s="1"/>
+      <c r="D297" s="3"/>
       <c r="E297" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="17.25">
       <c r="A298" s="1" t="s">
         <v>35</v>
       </c>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="E298" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="17.25">
       <c r="A299" s="1" t="s">
         <v>35</v>
       </c>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E299" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="17.25">
       <c r="A300" s="1" t="s">
         <v>35</v>
       </c>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="E300" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="17.25">
       <c r="A301" s="1" t="s">
         <v>35</v>
       </c>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="E301" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="17.25">
       <c r="A302" s="1" t="s">
         <v>35</v>
       </c>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="E302" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="17.25">
       <c r="A303" s="1" t="s">
         <v>35</v>
       </c>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="E303" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="17.25">
       <c r="A304" s="1" t="s">
         <v>35</v>
       </c>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="E304" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="17.25">
       <c r="A305" s="1" t="s">
         <v>35</v>
       </c>
@@ -9260,10 +9260,10 @@
       <c r="C305" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D305" s="1"/>
+      <c r="D305" s="3"/>
       <c r="E305" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="17.25">
       <c r="A306" s="1" t="s">
         <v>35</v>
       </c>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="E306" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="17.25">
       <c r="A307" s="1" t="s">
         <v>35</v>
       </c>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="E307" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="17.25">
       <c r="A308" s="1" t="s">
         <v>35</v>
       </c>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="E308" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="17.25">
       <c r="A309" s="1" t="s">
         <v>35</v>
       </c>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="E309" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="17.25">
       <c r="A310" s="1" t="s">
         <v>35</v>
       </c>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="E310" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="17.25">
       <c r="A311" s="1" t="s">
         <v>35</v>
       </c>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="E311" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="17.25">
       <c r="A312" s="1" t="s">
         <v>35</v>
       </c>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="E312" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="17.25">
       <c r="A313" s="1" t="s">
         <v>35</v>
       </c>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E313" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="17.25">
       <c r="A314" s="1" t="s">
         <v>35</v>
       </c>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="E314" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="17.25">
       <c r="A315" s="1" t="s">
         <v>35</v>
       </c>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="E315" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="17.25">
       <c r="A316" s="1" t="s">
         <v>35</v>
       </c>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="E316" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="17.25">
       <c r="A317" s="1" t="s">
         <v>35</v>
       </c>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="E317" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="17.25">
       <c r="A318" s="1" t="s">
         <v>35</v>
       </c>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="E318" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="17.25">
       <c r="A319" s="1" t="s">
         <v>35</v>
       </c>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="E319" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="17.25">
       <c r="A320" s="1" t="s">
         <v>35</v>
       </c>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="E320" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="17.25">
       <c r="A321" s="1" t="s">
         <v>35</v>
       </c>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="E321" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="17.25">
       <c r="A322" s="1" t="s">
         <v>35</v>
       </c>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="E322" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="17.25">
       <c r="A323" s="1" t="s">
         <v>35</v>
       </c>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="E323" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="17.25">
       <c r="A324" s="1" t="s">
         <v>35</v>
       </c>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E324" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="17.25">
       <c r="A325" s="1" t="s">
         <v>35</v>
       </c>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="E325" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="17.25">
       <c r="A326" s="1" t="s">
         <v>35</v>
       </c>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="E326" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="17.25">
       <c r="A327" s="1" t="s">
         <v>35</v>
       </c>
@@ -9588,10 +9588,10 @@
       <c r="C327" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D327" s="1"/>
+      <c r="D327" s="3"/>
       <c r="E327" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="17.25">
       <c r="A328" s="1" t="s">
         <v>35</v>
       </c>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="E328" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="17.25">
       <c r="A329" s="1" t="s">
         <v>35</v>
       </c>
@@ -9616,10 +9616,10 @@
       <c r="C329" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D329" s="1"/>
+      <c r="D329" s="3"/>
       <c r="E329" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="17.25">
       <c r="A330" s="1" t="s">
         <v>35</v>
       </c>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="E330" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="17.25">
       <c r="A331" s="1" t="s">
         <v>35</v>
       </c>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="E331" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="17.25">
       <c r="A332" s="1" t="s">
         <v>35</v>
       </c>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="E332" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="17.25">
       <c r="A333" s="1" t="s">
         <v>35</v>
       </c>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="E333" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="17.25">
       <c r="A334" s="1" t="s">
         <v>35</v>
       </c>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="E334" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="17.25">
       <c r="A335" s="1" t="s">
         <v>35</v>
       </c>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E335" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="17.25">
       <c r="A336" s="1" t="s">
         <v>35</v>
       </c>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="E336" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="17.25">
       <c r="A337" s="1" t="s">
         <v>35</v>
       </c>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E337" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="17.25">
       <c r="A338" s="1" t="s">
         <v>35</v>
       </c>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="E338" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="17.25">
       <c r="A339" s="1" t="s">
         <v>35</v>
       </c>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="E339" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="17.25">
       <c r="A340" s="1" t="s">
         <v>35</v>
       </c>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="E340" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="17.25">
       <c r="A341" s="1" t="s">
         <v>35</v>
       </c>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="E341" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="17.25">
       <c r="A342" s="1" t="s">
         <v>35</v>
       </c>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="E342" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="17.25">
       <c r="A343" s="1" t="s">
         <v>35</v>
       </c>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="E343" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="17.25">
       <c r="A344" s="1" t="s">
         <v>35</v>
       </c>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="E344" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="17.25">
       <c r="A345" s="1" t="s">
         <v>35</v>
       </c>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="E345" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="17.25">
       <c r="A346" s="1" t="s">
         <v>35</v>
       </c>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="E346" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="17.25">
       <c r="A347" s="1" t="s">
         <v>35</v>
       </c>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E347" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="17.25">
       <c r="A348" s="1" t="s">
         <v>35</v>
       </c>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="E348" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="17.25">
       <c r="A349" s="1" t="s">
         <v>35</v>
       </c>
@@ -9914,10 +9914,10 @@
       <c r="C349" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D349" s="1"/>
+      <c r="D349" s="3"/>
       <c r="E349" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="17.25">
       <c r="A350" s="1" t="s">
         <v>35</v>
       </c>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="E350" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="17.25">
       <c r="A351" s="1" t="s">
         <v>35</v>
       </c>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="E351" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="17.25">
       <c r="A352" s="1" t="s">
         <v>35</v>
       </c>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="E352" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="17.25">
       <c r="A353" s="1" t="s">
         <v>35</v>
       </c>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="E353" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="17.25">
       <c r="A354" s="1" t="s">
         <v>35</v>
       </c>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="E354" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="17.25">
       <c r="A355" s="1" t="s">
         <v>35</v>
       </c>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="E355" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="17.25">
       <c r="A356" s="1" t="s">
         <v>35</v>
       </c>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="E356" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="17.25">
       <c r="A357" s="1" t="s">
         <v>35</v>
       </c>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="E357" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="17.25">
       <c r="A358" s="1" t="s">
         <v>35</v>
       </c>
@@ -10047,10 +10047,10 @@
       <c r="C358" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="D358" s="1"/>
+      <c r="D358" s="3"/>
       <c r="E358" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="17.25">
       <c r="A359" s="1" t="s">
         <v>35</v>
       </c>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="E359" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="17.25">
       <c r="A360" s="1" t="s">
         <v>35</v>
       </c>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="E360" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="17.25">
       <c r="A361" s="1" t="s">
         <v>35</v>
       </c>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E361" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="17.25">
       <c r="A362" s="1" t="s">
         <v>35</v>
       </c>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="E362" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="17.25">
       <c r="A363" s="1" t="s">
         <v>35</v>
       </c>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E363" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="17.25">
       <c r="A364" s="1" t="s">
         <v>35</v>
       </c>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="E364" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="17.25">
       <c r="A365" s="1" t="s">
         <v>35</v>
       </c>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="E365" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="17.25">
       <c r="A366" s="1" t="s">
         <v>35</v>
       </c>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="E366" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="17.25">
       <c r="A367" s="1" t="s">
         <v>35</v>
       </c>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="E367" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="17.25">
       <c r="A368" s="1" t="s">
         <v>35</v>
       </c>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="E368" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="17.25">
       <c r="A369" s="1" t="s">
         <v>35</v>
       </c>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="E369" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="17.25">
       <c r="A370" s="1" t="s">
         <v>35</v>
       </c>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="E370" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="17.25">
       <c r="A371" s="1" t="s">
         <v>35</v>
       </c>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="E371" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="17.25">
       <c r="A372" s="1" t="s">
         <v>35</v>
       </c>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E372" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="17.25">
       <c r="A373" s="1" t="s">
         <v>35</v>
       </c>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="E373" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="17.25">
       <c r="A374" s="1" t="s">
         <v>35</v>
       </c>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="E374" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="17.25">
       <c r="A375" s="1" t="s">
         <v>35</v>
       </c>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="E375" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="17.25">
       <c r="A376" s="1" t="s">
         <v>35</v>
       </c>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="E376" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="17.25">
       <c r="A377" s="1" t="s">
         <v>35</v>
       </c>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="E377" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="17.25">
       <c r="A378" s="1" t="s">
         <v>35</v>
       </c>
@@ -10345,10 +10345,10 @@
       <c r="C378" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D378" s="1"/>
+      <c r="D378" s="3"/>
       <c r="E378" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="17.25">
       <c r="A379" s="1" t="s">
         <v>35</v>
       </c>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="E379" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="17.25">
       <c r="A380" s="1" t="s">
         <v>35</v>
       </c>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="E380" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="17.25">
       <c r="A381" s="1" t="s">
         <v>35</v>
       </c>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="E381" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="17.25">
       <c r="A382" s="1" t="s">
         <v>35</v>
       </c>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="E382" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="17.25">
       <c r="A383" s="1" t="s">
         <v>35</v>
       </c>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E383" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="17.25">
       <c r="A384" s="1" t="s">
         <v>35</v>
       </c>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="E384" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="17.25">
       <c r="A385" s="1" t="s">
         <v>35</v>
       </c>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="E385" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="17.25">
       <c r="A386" s="1" t="s">
         <v>35</v>
       </c>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E386" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="17.25">
       <c r="A387" s="1" t="s">
         <v>35</v>
       </c>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="E387" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="17.25">
       <c r="A388" s="1" t="s">
         <v>35</v>
       </c>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="E388" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="17.25">
       <c r="A389" s="1" t="s">
         <v>35</v>
       </c>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="E389" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="17.25">
       <c r="A390" s="1" t="s">
         <v>35</v>
       </c>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="E390" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="17.25">
       <c r="A391" s="1" t="s">
         <v>35</v>
       </c>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="E391" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="17.25">
       <c r="A392" s="1" t="s">
         <v>35</v>
       </c>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="E392" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="17.25">
       <c r="A393" s="1" t="s">
         <v>35</v>
       </c>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="E393" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="17.25">
       <c r="A394" s="1" t="s">
         <v>35</v>
       </c>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="E394" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="17.25">
       <c r="A395" s="1" t="s">
         <v>35</v>
       </c>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="E395" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="17.25">
       <c r="A396" s="1" t="s">
         <v>35</v>
       </c>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="E396" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="17.25">
       <c r="A397" s="1" t="s">
         <v>35</v>
       </c>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="E397" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="17.25">
       <c r="A398" s="1" t="s">
         <v>35</v>
       </c>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="E398" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="17.25">
       <c r="A399" s="1" t="s">
         <v>35</v>
       </c>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="E399" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="17.25">
       <c r="A400" s="1" t="s">
         <v>35</v>
       </c>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="E400" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="17.25">
       <c r="A401" s="1" t="s">
         <v>35</v>
       </c>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="E401" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="17.25">
       <c r="A402" s="1" t="s">
         <v>35</v>
       </c>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="E402" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="17.25">
       <c r="A403" s="1" t="s">
         <v>35</v>
       </c>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="E403" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="17.25">
       <c r="A404" s="1" t="s">
         <v>35</v>
       </c>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="E404" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="17.25">
       <c r="A405" s="1" t="s">
         <v>35</v>
       </c>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="E405" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="17.25">
       <c r="A406" s="1" t="s">
         <v>35</v>
       </c>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="E406" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="17.25">
       <c r="A407" s="1" t="s">
         <v>35</v>
       </c>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="E407" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="17.25">
       <c r="A408" s="1" t="s">
         <v>35</v>
       </c>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="E408" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="17.25">
       <c r="A409" s="1" t="s">
         <v>35</v>
       </c>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="E409" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="17.25">
       <c r="A410" s="1" t="s">
         <v>35</v>
       </c>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="E410" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="17.25">
       <c r="A411" s="1" t="s">
         <v>35</v>
       </c>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="E411" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="17.25">
       <c r="A412" s="1" t="s">
         <v>35</v>
       </c>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="E412" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="17.25">
       <c r="A413" s="1" t="s">
         <v>35</v>
       </c>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E413" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="17.25">
       <c r="A414" s="1" t="s">
         <v>35</v>
       </c>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="E414" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="17.25">
       <c r="A415" s="1" t="s">
         <v>35</v>
       </c>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E415" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="17.25">
       <c r="A416" s="1" t="s">
         <v>35</v>
       </c>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="E416" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="17.25">
       <c r="A417" s="1" t="s">
         <v>35</v>
       </c>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="E417" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="17.25">
       <c r="A418" s="1" t="s">
         <v>35</v>
       </c>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="E418" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="17.25">
       <c r="A419" s="1" t="s">
         <v>35</v>
       </c>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="E419" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="17.25">
       <c r="A420" s="1" t="s">
         <v>35</v>
       </c>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="E420" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="17.25">
       <c r="A421" s="1" t="s">
         <v>35</v>
       </c>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="E421" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="17.25">
       <c r="A422" s="1" t="s">
         <v>35</v>
       </c>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="E422" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="17.25">
       <c r="A423" s="1" t="s">
         <v>35</v>
       </c>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E423" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="17.25">
       <c r="A424" s="1" t="s">
         <v>35</v>
       </c>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="E424" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="17.25">
       <c r="A425" s="1" t="s">
         <v>35</v>
       </c>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="E425" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="17.25">
       <c r="A426" s="1" t="s">
         <v>35</v>
       </c>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="E426" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="17.25">
       <c r="A427" s="1" t="s">
         <v>35</v>
       </c>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="E427" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="17.25">
       <c r="A428" s="1" t="s">
         <v>35</v>
       </c>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="E428" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="17.25">
       <c r="A429" s="1" t="s">
         <v>35</v>
       </c>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="E429" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="17.25">
       <c r="A430" s="1" t="s">
         <v>35</v>
       </c>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E430" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="17.25">
       <c r="A431" s="1" t="s">
         <v>35</v>
       </c>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="E431" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="17.25">
       <c r="A432" s="1" t="s">
         <v>35</v>
       </c>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E432" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="17.25">
       <c r="A433" s="1" t="s">
         <v>35</v>
       </c>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="E433" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="17.25">
       <c r="A434" s="1" t="s">
         <v>35</v>
       </c>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="E434" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="17.25">
       <c r="A435" s="1" t="s">
         <v>35</v>
       </c>
@@ -11203,7 +11203,7 @@
       </c>
       <c r="E435" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="17.25">
       <c r="A436" s="1" t="s">
         <v>35</v>
       </c>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="E436" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="17.25">
       <c r="A437" s="1" t="s">
         <v>35</v>
       </c>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="E437" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="17.25">
       <c r="A438" s="1" t="s">
         <v>35</v>
       </c>
@@ -11248,7 +11248,7 @@
       </c>
       <c r="E438" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="17.25">
       <c r="A439" s="1" t="s">
         <v>35</v>
       </c>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="E439" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="17.25">
       <c r="A440" s="1" t="s">
         <v>35</v>
       </c>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="E440" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="17.25">
       <c r="A441" s="1" t="s">
         <v>35</v>
       </c>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="E441" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="17.25">
       <c r="A442" s="1" t="s">
         <v>35</v>
       </c>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="E442" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="17.25">
       <c r="A443" s="1" t="s">
         <v>35</v>
       </c>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="E443" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="17.25">
       <c r="A444" s="1" t="s">
         <v>35</v>
       </c>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="E444" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="17.25">
       <c r="A445" s="1" t="s">
         <v>35</v>
       </c>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="E445" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="17.25">
       <c r="A446" s="1" t="s">
         <v>35</v>
       </c>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="E446" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="17.25">
       <c r="A447" s="1" t="s">
         <v>35</v>
       </c>
@@ -11378,10 +11378,10 @@
       <c r="C447" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="D447" s="1"/>
+      <c r="D447" s="3"/>
       <c r="E447" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="17.25">
       <c r="A448" s="1" t="s">
         <v>35</v>
       </c>
@@ -11391,10 +11391,10 @@
       <c r="C448" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="D448" s="1"/>
+      <c r="D448" s="3"/>
       <c r="E448" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="17.25">
       <c r="A449" s="1" t="s">
         <v>35</v>
       </c>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="E449" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="17.25">
       <c r="A450" s="1" t="s">
         <v>35</v>
       </c>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="E450" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="17.25">
       <c r="A451" s="1" t="s">
         <v>35</v>
       </c>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="E451" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="17.25">
       <c r="A452" s="1" t="s">
         <v>35</v>
       </c>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="E452" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="17.25">
       <c r="A453" s="1" t="s">
         <v>35</v>
       </c>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E453" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="17.25">
       <c r="A454" s="1" t="s">
         <v>35</v>
       </c>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="E454" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="17.25">
       <c r="A455" s="1" t="s">
         <v>35</v>
       </c>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="E455" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="17.25">
       <c r="A456" s="1" t="s">
         <v>35</v>
       </c>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E456" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="17.25">
       <c r="A457" s="1" t="s">
         <v>35</v>
       </c>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E457" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="17.25">
       <c r="A458" s="1" t="s">
         <v>35</v>
       </c>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="E458" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="17.25">
       <c r="A459" s="1" t="s">
         <v>35</v>
       </c>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="E459" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="17.25">
       <c r="A460" s="1" t="s">
         <v>35</v>
       </c>
@@ -11574,7 +11574,7 @@
       </c>
       <c r="E460" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="17.25">
       <c r="A461" s="1" t="s">
         <v>35</v>
       </c>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="E461" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="17.25">
       <c r="A462" s="1" t="s">
         <v>35</v>
       </c>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="E462" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="17.25">
       <c r="A463" s="1" t="s">
         <v>35</v>
       </c>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="E463" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="17.25">
       <c r="A464" s="1" t="s">
         <v>35</v>
       </c>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="E464" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="17.25">
       <c r="A465" s="1" t="s">
         <v>35</v>
       </c>
@@ -11644,10 +11644,10 @@
       <c r="C465" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="D465" s="1"/>
+      <c r="D465" s="3"/>
       <c r="E465" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="17.25">
       <c r="A466" s="1" t="s">
         <v>35</v>
       </c>
@@ -11657,10 +11657,10 @@
       <c r="C466" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="D466" s="1"/>
+      <c r="D466" s="3"/>
       <c r="E466" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="17.25">
       <c r="A467" s="1" t="s">
         <v>35</v>
       </c>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E467" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="17.25">
       <c r="A468" s="1" t="s">
         <v>35</v>
       </c>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="E468" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="17.25">
       <c r="A469" s="1" t="s">
         <v>35</v>
       </c>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="E469" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="17.25">
       <c r="A470" s="1" t="s">
         <v>35</v>
       </c>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E470" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="17.25">
       <c r="A471" s="1" t="s">
         <v>35</v>
       </c>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="E471" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="17.25">
       <c r="A472" s="1" t="s">
         <v>35</v>
       </c>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="E472" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="17.25">
       <c r="A473" s="1" t="s">
         <v>35</v>
       </c>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="E473" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="17.25">
       <c r="A474" s="1" t="s">
         <v>35</v>
       </c>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="E474" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="17.25">
       <c r="A475" s="1" t="s">
         <v>35</v>
       </c>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="E475" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="17.25">
       <c r="A476" s="1" t="s">
         <v>35</v>
       </c>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="E476" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="17.25">
       <c r="A477" s="1" t="s">
         <v>35</v>
       </c>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="E477" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="17.25">
       <c r="A478" s="1" t="s">
         <v>35</v>
       </c>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="E478" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="17.25">
       <c r="A479" s="1" t="s">
         <v>35</v>
       </c>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="E479" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="17.25">
       <c r="A480" s="1" t="s">
         <v>35</v>
       </c>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="E480" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="17.25">
       <c r="A481" s="1" t="s">
         <v>35</v>
       </c>
@@ -11880,10 +11880,10 @@
       <c r="C481" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="D481" s="1"/>
+      <c r="D481" s="3"/>
       <c r="E481" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="17.25">
       <c r="A482" s="1" t="s">
         <v>35</v>
       </c>
@@ -11893,10 +11893,10 @@
       <c r="C482" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="D482" s="1"/>
+      <c r="D482" s="3"/>
       <c r="E482" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="17.25">
       <c r="A483" s="1" t="s">
         <v>35</v>
       </c>
@@ -11906,10 +11906,10 @@
       <c r="C483" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="D483" s="1"/>
+      <c r="D483" s="3"/>
       <c r="E483" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="17.25">
       <c r="A484" s="1" t="s">
         <v>35</v>
       </c>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="E484" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="17.25">
       <c r="A485" s="1" t="s">
         <v>35</v>
       </c>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E485" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="17.25">
       <c r="A486" s="1" t="s">
         <v>35</v>
       </c>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="E486" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="17.25">
       <c r="A487" s="1" t="s">
         <v>35</v>
       </c>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="E487" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="17.25">
       <c r="A488" s="1" t="s">
         <v>35</v>
       </c>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="E488" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="17.25">
       <c r="A489" s="1" t="s">
         <v>35</v>
       </c>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="E489" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="17.25">
       <c r="A490" s="1" t="s">
         <v>35</v>
       </c>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="E490" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="17.25">
       <c r="A491" s="1" t="s">
         <v>35</v>
       </c>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="E491" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="17.25">
       <c r="A492" s="1" t="s">
         <v>35</v>
       </c>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="E492" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="17.25">
       <c r="A493" s="1" t="s">
         <v>35</v>
       </c>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="E493" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="17.25">
       <c r="A494" s="1" t="s">
         <v>35</v>
       </c>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="E494" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="17.25">
       <c r="A495" s="1" t="s">
         <v>35</v>
       </c>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E495" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="17.25">
       <c r="A496" s="1" t="s">
         <v>35</v>
       </c>
@@ -12099,10 +12099,10 @@
       <c r="C496" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="D496" s="1"/>
+      <c r="D496" s="3"/>
       <c r="E496" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="17.25">
       <c r="A497" s="1" t="s">
         <v>35</v>
       </c>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E497" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="17.25">
       <c r="A498" s="1" t="s">
         <v>35</v>
       </c>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="E498" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="17.25">
       <c r="A499" s="1" t="s">
         <v>35</v>
       </c>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="E499" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="17.25">
       <c r="A500" s="1" t="s">
         <v>35</v>
       </c>
@@ -12157,10 +12157,10 @@
       <c r="C500" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="D500" s="1"/>
+      <c r="D500" s="3"/>
       <c r="E500" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="17.25">
       <c r="A501" s="1" t="s">
         <v>35</v>
       </c>
@@ -12170,10 +12170,10 @@
       <c r="C501" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="D501" s="1"/>
+      <c r="D501" s="3"/>
       <c r="E501" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="17.25">
       <c r="A502" s="1" t="s">
         <v>35</v>
       </c>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="E502" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="17.25">
       <c r="A503" s="1" t="s">
         <v>35</v>
       </c>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="E503" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="17.25">
       <c r="A504" s="1" t="s">
         <v>35</v>
       </c>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="E504" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="17.25">
       <c r="A505" s="1" t="s">
         <v>35</v>
       </c>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="E505" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="17.25">
       <c r="A506" s="1" t="s">
         <v>35</v>
       </c>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E506" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="17.25">
       <c r="A507" s="1" t="s">
         <v>35</v>
       </c>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="E507" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="17.25">
       <c r="A508" s="1" t="s">
         <v>35</v>
       </c>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="E508" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="17.25">
       <c r="A509" s="1" t="s">
         <v>35</v>
       </c>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="E509" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="17.25">
       <c r="A510" s="1" t="s">
         <v>35</v>
       </c>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E510" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="17.25">
       <c r="A511" s="1" t="s">
         <v>35</v>
       </c>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="E511" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="17.25">
       <c r="A512" s="1" t="s">
         <v>35</v>
       </c>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="E512" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="17.25">
       <c r="A513" s="1" t="s">
         <v>35</v>
       </c>
@@ -12353,7 +12353,7 @@
       </c>
       <c r="E513" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="17.25">
       <c r="A514" s="1" t="s">
         <v>35</v>
       </c>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E514" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="17.25">
       <c r="A515" s="1" t="s">
         <v>35</v>
       </c>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="E515" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="17.25">
       <c r="A516" s="1" t="s">
         <v>35</v>
       </c>
@@ -12398,7 +12398,7 @@
       </c>
       <c r="E516" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="17.25">
       <c r="A517" s="1" t="s">
         <v>35</v>
       </c>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="E517" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="17.25">
       <c r="A518" s="1" t="s">
         <v>35</v>
       </c>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="E518" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="17.25">
       <c r="A519" s="1" t="s">
         <v>35</v>
       </c>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="E519" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="17.25">
       <c r="A520" s="1" t="s">
         <v>35</v>
       </c>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E520" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="17.25">
       <c r="A521" s="1" t="s">
         <v>35</v>
       </c>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="E521" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="17.25">
       <c r="A522" s="1" t="s">
         <v>35</v>
       </c>
@@ -12488,7 +12488,7 @@
       </c>
       <c r="E522" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="17.25">
       <c r="A523" s="1" t="s">
         <v>35</v>
       </c>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="E523" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="17.25">
       <c r="A524" s="1" t="s">
         <v>35</v>
       </c>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="E524" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="17.25">
       <c r="A525" s="1" t="s">
         <v>35</v>
       </c>
@@ -12533,7 +12533,7 @@
       </c>
       <c r="E525" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="17.25">
       <c r="A526" s="1" t="s">
         <v>35</v>
       </c>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="E526" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="17.25">
       <c r="A527" s="1" t="s">
         <v>35</v>
       </c>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="E527" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="17.25">
       <c r="A528" s="1" t="s">
         <v>35</v>
       </c>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="E528" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="17.25">
       <c r="A529" s="1" t="s">
         <v>35</v>
       </c>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="E529" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="17.25">
       <c r="A530" s="1" t="s">
         <v>35</v>
       </c>
@@ -12603,10 +12603,10 @@
       <c r="C530" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="D530" s="1"/>
+      <c r="D530" s="3"/>
       <c r="E530" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="17.25">
       <c r="A531" s="1" t="s">
         <v>35</v>
       </c>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E531" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="17.25">
       <c r="A532" s="1" t="s">
         <v>35</v>
       </c>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E532" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="17.25">
       <c r="A533" s="1" t="s">
         <v>35</v>
       </c>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="E533" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="17.25">
       <c r="A534" s="1" t="s">
         <v>35</v>
       </c>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="E534" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="17.25">
       <c r="A535" s="1" t="s">
         <v>35</v>
       </c>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="E535" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="17.25">
       <c r="A536" s="1" t="s">
         <v>35</v>
       </c>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="E536" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="17.25">
       <c r="A537" s="1" t="s">
         <v>35</v>
       </c>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="E537" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="538" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="538" customHeight="1" ht="17.25">
       <c r="A538" s="1" t="s">
         <v>35</v>
       </c>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="E538" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="539" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="539" customHeight="1" ht="17.25">
       <c r="A539" s="1" t="s">
         <v>35</v>
       </c>
@@ -12741,7 +12741,7 @@
       </c>
       <c r="E539" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="540" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="540" customHeight="1" ht="17.25">
       <c r="A540" s="1" t="s">
         <v>35</v>
       </c>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E540" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="541" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="541" customHeight="1" ht="17.25">
       <c r="A541" s="1" t="s">
         <v>35</v>
       </c>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="E541" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="542" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="542" customHeight="1" ht="17.25">
       <c r="A542" s="1" t="s">
         <v>35</v>
       </c>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="E542" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="543" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="543" customHeight="1" ht="17.25">
       <c r="A543" s="1" t="s">
         <v>35</v>
       </c>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="E543" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="544" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="544" customHeight="1" ht="17.25">
       <c r="A544" s="1" t="s">
         <v>35</v>
       </c>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="E544" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="545" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="545" customHeight="1" ht="17.25">
       <c r="A545" s="1" t="s">
         <v>35</v>
       </c>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E545" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="546" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="546" customHeight="1" ht="17.25">
       <c r="A546" s="1" t="s">
         <v>35</v>
       </c>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="E546" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="547" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="547" customHeight="1" ht="17.25">
       <c r="A547" s="1" t="s">
         <v>35</v>
       </c>
@@ -12856,10 +12856,10 @@
       <c r="C547" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="D547" s="1"/>
+      <c r="D547" s="3"/>
       <c r="E547" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="548" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="548" customHeight="1" ht="17.25">
       <c r="A548" s="1" t="s">
         <v>35</v>
       </c>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="E548" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="549" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="549" customHeight="1" ht="17.25">
       <c r="A549" s="1" t="s">
         <v>35</v>
       </c>
@@ -12889,7 +12889,7 @@
       </c>
       <c r="E549" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="550" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="550" customHeight="1" ht="17.25">
       <c r="A550" s="1" t="s">
         <v>35</v>
       </c>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="E550" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="551" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="551" customHeight="1" ht="17.25">
       <c r="A551" s="1" t="s">
         <v>35</v>
       </c>
@@ -12919,7 +12919,7 @@
       </c>
       <c r="E551" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="552" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="552" customHeight="1" ht="17.25">
       <c r="A552" s="1" t="s">
         <v>35</v>
       </c>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="E552" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="553" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="553" customHeight="1" ht="17.25">
       <c r="A553" s="1" t="s">
         <v>35</v>
       </c>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="E553" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="554" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="554" customHeight="1" ht="17.25">
       <c r="A554" s="1" t="s">
         <v>35</v>
       </c>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="E554" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="555" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="555" customHeight="1" ht="17.25">
       <c r="A555" s="1" t="s">
         <v>35</v>
       </c>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="E555" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="556" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="556" customHeight="1" ht="17.25">
       <c r="A556" s="1" t="s">
         <v>35</v>
       </c>
@@ -12994,7 +12994,7 @@
       </c>
       <c r="E556" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="557" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="557" customHeight="1" ht="17.25">
       <c r="A557" s="1" t="s">
         <v>35</v>
       </c>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="E557" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="558" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="558" customHeight="1" ht="17.25">
       <c r="A558" s="1" t="s">
         <v>35</v>
       </c>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="E558" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="559" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="559" customHeight="1" ht="17.25">
       <c r="A559" s="1" t="s">
         <v>35</v>
       </c>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="E559" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="560" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="560" customHeight="1" ht="17.25">
       <c r="A560" s="1" t="s">
         <v>35</v>
       </c>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="E560" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="561" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="561" customHeight="1" ht="17.25">
       <c r="A561" s="1" t="s">
         <v>35</v>
       </c>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="E561" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="562" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="562" customHeight="1" ht="17.25">
       <c r="A562" s="1" t="s">
         <v>35</v>
       </c>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="E562" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="563" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="563" customHeight="1" ht="17.25">
       <c r="A563" s="1" t="s">
         <v>35</v>
       </c>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="E563" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="564" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="564" customHeight="1" ht="17.25">
       <c r="A564" s="1" t="s">
         <v>35</v>
       </c>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="E564" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="565" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="565" customHeight="1" ht="17.25">
       <c r="A565" s="1" t="s">
         <v>35</v>
       </c>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="E565" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="566" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="566" customHeight="1" ht="17.25">
       <c r="A566" s="1" t="s">
         <v>35</v>
       </c>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="E566" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="567" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="567" customHeight="1" ht="17.25">
       <c r="A567" s="1" t="s">
         <v>35</v>
       </c>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="E567" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="568" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="568" customHeight="1" ht="17.25">
       <c r="A568" s="1" t="s">
         <v>35</v>
       </c>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="E568" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="569" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="569" customHeight="1" ht="17.25">
       <c r="A569" s="1" t="s">
         <v>35</v>
       </c>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E569" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="570" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="570" customHeight="1" ht="17.25">
       <c r="A570" s="1" t="s">
         <v>35</v>
       </c>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="E570" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="571" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="571" customHeight="1" ht="17.25">
       <c r="A571" s="1" t="s">
         <v>35</v>
       </c>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="E571" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="572" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="572" customHeight="1" ht="17.25">
       <c r="A572" s="1" t="s">
         <v>35</v>
       </c>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="E572" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="573" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="573" customHeight="1" ht="17.25">
       <c r="A573" s="1" t="s">
         <v>35</v>
       </c>
@@ -13244,10 +13244,10 @@
       <c r="C573" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="D573" s="1"/>
+      <c r="D573" s="3"/>
       <c r="E573" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="574" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="574" customHeight="1" ht="17.25">
       <c r="A574" s="1" t="s">
         <v>35</v>
       </c>
@@ -13257,10 +13257,10 @@
       <c r="C574" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D574" s="1"/>
+      <c r="D574" s="3"/>
       <c r="E574" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="575" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="575" customHeight="1" ht="17.25">
       <c r="A575" s="1" t="s">
         <v>35</v>
       </c>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="E575" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="576" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="576" customHeight="1" ht="17.25">
       <c r="A576" s="1" t="s">
         <v>35</v>
       </c>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="E576" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="577" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="577" customHeight="1" ht="17.25">
       <c r="A577" s="1" t="s">
         <v>35</v>
       </c>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="E577" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="578" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="578" customHeight="1" ht="17.25">
       <c r="A578" s="1" t="s">
         <v>35</v>
       </c>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="E578" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="579" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="579" customHeight="1" ht="17.25">
       <c r="A579" s="1" t="s">
         <v>35</v>
       </c>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="E579" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="580" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="580" customHeight="1" ht="17.25">
       <c r="A580" s="1" t="s">
         <v>35</v>
       </c>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E580" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="581" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="581" customHeight="1" ht="17.25">
       <c r="A581" s="1" t="s">
         <v>35</v>
       </c>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="E581" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="582" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="582" customHeight="1" ht="17.25">
       <c r="A582" s="1" t="s">
         <v>35</v>
       </c>
@@ -13380,7 +13380,7 @@
       </c>
       <c r="E582" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="583" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="583" customHeight="1" ht="17.25">
       <c r="A583" s="1" t="s">
         <v>35</v>
       </c>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="E583" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="584" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="584" customHeight="1" ht="17.25">
       <c r="A584" s="1" t="s">
         <v>35</v>
       </c>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="E584" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="585" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="585" customHeight="1" ht="17.25">
       <c r="A585" s="1" t="s">
         <v>35</v>
       </c>
@@ -13425,7 +13425,7 @@
       </c>
       <c r="E585" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="586" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="586" customHeight="1" ht="17.25">
       <c r="A586" s="1" t="s">
         <v>35</v>
       </c>
@@ -13435,10 +13435,10 @@
       <c r="C586" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="D586" s="1"/>
+      <c r="D586" s="3"/>
       <c r="E586" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="587" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="587" customHeight="1" ht="17.25">
       <c r="A587" s="1" t="s">
         <v>35</v>
       </c>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="E587" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="588" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="588" customHeight="1" ht="17.25">
       <c r="A588" s="1" t="s">
         <v>35</v>
       </c>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="E588" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="589" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="589" customHeight="1" ht="17.25">
       <c r="A589" s="1" t="s">
         <v>35</v>
       </c>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="E589" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="590" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="590" customHeight="1" ht="17.25">
       <c r="A590" s="1" t="s">
         <v>35</v>
       </c>
@@ -13498,7 +13498,7 @@
       </c>
       <c r="E590" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="591" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="591" customHeight="1" ht="17.25">
       <c r="A591" s="1" t="s">
         <v>35</v>
       </c>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="E591" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="592" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="592" customHeight="1" ht="17.25">
       <c r="A592" s="1" t="s">
         <v>35</v>
       </c>
@@ -13528,7 +13528,7 @@
       </c>
       <c r="E592" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="593" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="593" customHeight="1" ht="17.25">
       <c r="A593" s="1" t="s">
         <v>35</v>
       </c>
@@ -13543,7 +13543,7 @@
       </c>
       <c r="E593" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="594" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="594" customHeight="1" ht="17.25">
       <c r="A594" s="1" t="s">
         <v>35</v>
       </c>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E594" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="595" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="595" customHeight="1" ht="17.25">
       <c r="A595" s="1" t="s">
         <v>35</v>
       </c>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="E595" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="596" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="596" customHeight="1" ht="17.25">
       <c r="A596" s="1" t="s">
         <v>35</v>
       </c>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="E596" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="597" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="597" customHeight="1" ht="17.25">
       <c r="A597" s="1" t="s">
         <v>35</v>
       </c>
@@ -13603,7 +13603,7 @@
       </c>
       <c r="E597" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="598" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="598" customHeight="1" ht="17.25">
       <c r="A598" s="1" t="s">
         <v>35</v>
       </c>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="E598" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="599" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="599" customHeight="1" ht="17.25">
       <c r="A599" s="1" t="s">
         <v>35</v>
       </c>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="E599" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="600" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="600" customHeight="1" ht="17.25">
       <c r="A600" s="1" t="s">
         <v>35</v>
       </c>
@@ -13643,10 +13643,10 @@
       <c r="C600" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D600" s="1"/>
+      <c r="D600" s="3"/>
       <c r="E600" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="601" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="601" customHeight="1" ht="17.25">
       <c r="A601" s="1" t="s">
         <v>35</v>
       </c>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="E601" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="602" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="602" customHeight="1" ht="17.25">
       <c r="A602" s="1" t="s">
         <v>35</v>
       </c>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="E602" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="603" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="603" customHeight="1" ht="17.25">
       <c r="A603" s="1" t="s">
         <v>35</v>
       </c>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="E603" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="604" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="604" customHeight="1" ht="17.25">
       <c r="A604" s="1" t="s">
         <v>35</v>
       </c>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="E604" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="605" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="605" customHeight="1" ht="17.25">
       <c r="A605" s="1" t="s">
         <v>35</v>
       </c>
@@ -13716,10 +13716,10 @@
       <c r="C605" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="D605" s="1"/>
+      <c r="D605" s="3"/>
       <c r="E605" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="606" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="606" customHeight="1" ht="17.25">
       <c r="A606" s="1" t="s">
         <v>35</v>
       </c>
@@ -13729,10 +13729,10 @@
       <c r="C606" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="D606" s="1"/>
+      <c r="D606" s="3"/>
       <c r="E606" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="607" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="607" customHeight="1" ht="17.25">
       <c r="A607" s="1" t="s">
         <v>35</v>
       </c>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="E607" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="608" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="608" customHeight="1" ht="17.25">
       <c r="A608" s="1" t="s">
         <v>35</v>
       </c>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="E608" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="609" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="609" customHeight="1" ht="17.25">
       <c r="A609" s="1" t="s">
         <v>35</v>
       </c>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="E609" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="610" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="610" customHeight="1" ht="17.25">
       <c r="A610" s="1" t="s">
         <v>35</v>
       </c>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="E610" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="611" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="611" customHeight="1" ht="17.25">
       <c r="A611" s="1" t="s">
         <v>35</v>
       </c>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="E611" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="612" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="612" customHeight="1" ht="17.25">
       <c r="A612" s="1" t="s">
         <v>35</v>
       </c>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="E612" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="613" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="613" customHeight="1" ht="17.25">
       <c r="A613" s="1" t="s">
         <v>35</v>
       </c>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="E613" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="614" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="614" customHeight="1" ht="17.25">
       <c r="A614" s="1" t="s">
         <v>35</v>
       </c>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="E614" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="615" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="615" customHeight="1" ht="17.25">
       <c r="A615" s="1" t="s">
         <v>35</v>
       </c>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="E615" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="616" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="616" customHeight="1" ht="17.25">
       <c r="A616" s="1" t="s">
         <v>35</v>
       </c>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="E616" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="617" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="617" customHeight="1" ht="17.25">
       <c r="A617" s="1" t="s">
         <v>35</v>
       </c>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="E617" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="618" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="618" customHeight="1" ht="17.25">
       <c r="A618" s="1" t="s">
         <v>35</v>
       </c>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="E618" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="619" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="619" customHeight="1" ht="17.25">
       <c r="A619" s="1" t="s">
         <v>35</v>
       </c>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E619" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="620" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="620" customHeight="1" ht="17.25">
       <c r="A620" s="1" t="s">
         <v>35</v>
       </c>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="E620" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="621" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="621" customHeight="1" ht="17.25">
       <c r="A621" s="1" t="s">
         <v>35</v>
       </c>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="E621" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="622" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="622" customHeight="1" ht="17.25">
       <c r="A622" s="1" t="s">
         <v>35</v>
       </c>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="E622" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="623" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="623" customHeight="1" ht="17.25">
       <c r="A623" s="1" t="s">
         <v>35</v>
       </c>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="E623" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="624" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="624" customHeight="1" ht="17.25">
       <c r="A624" s="1" t="s">
         <v>35</v>
       </c>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="E624" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="625" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="625" customHeight="1" ht="17.25">
       <c r="A625" s="1" t="s">
         <v>35</v>
       </c>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="E625" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="626" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="626" customHeight="1" ht="17.25">
       <c r="A626" s="1" t="s">
         <v>35</v>
       </c>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="E626" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="627" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="627" customHeight="1" ht="17.25">
       <c r="A627" s="1" t="s">
         <v>35</v>
       </c>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="E627" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="628" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="628" customHeight="1" ht="17.25">
       <c r="A628" s="1" t="s">
         <v>35</v>
       </c>
@@ -14062,7 +14062,7 @@
       </c>
       <c r="E628" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="629" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="629" customHeight="1" ht="17.25">
       <c r="A629" s="1" t="s">
         <v>35</v>
       </c>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="E629" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="630" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="630" customHeight="1" ht="17.25">
       <c r="A630" s="1" t="s">
         <v>35</v>
       </c>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="E630" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="631" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="631" customHeight="1" ht="17.25">
       <c r="A631" s="1" t="s">
         <v>35</v>
       </c>
@@ -14102,10 +14102,10 @@
       <c r="C631" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="D631" s="1"/>
+      <c r="D631" s="3"/>
       <c r="E631" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="632" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="632" customHeight="1" ht="17.25">
       <c r="A632" s="1" t="s">
         <v>35</v>
       </c>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="E632" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="633" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="633" customHeight="1" ht="17.25">
       <c r="A633" s="1" t="s">
         <v>35</v>
       </c>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="E633" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="634" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="634" customHeight="1" ht="17.25">
       <c r="A634" s="1" t="s">
         <v>35</v>
       </c>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="E634" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="635" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="635" customHeight="1" ht="17.25">
       <c r="A635" s="1" t="s">
         <v>35</v>
       </c>
@@ -14160,10 +14160,10 @@
       <c r="C635" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="D635" s="1"/>
+      <c r="D635" s="3"/>
       <c r="E635" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="636" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="636" customHeight="1" ht="17.25">
       <c r="A636" s="1" t="s">
         <v>35</v>
       </c>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="E636" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="637" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="637" customHeight="1" ht="17.25">
       <c r="A637" s="1" t="s">
         <v>35</v>
       </c>
@@ -14188,10 +14188,10 @@
       <c r="C637" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D637" s="1"/>
+      <c r="D637" s="3"/>
       <c r="E637" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="638" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="638" customHeight="1" ht="17.25">
       <c r="A638" s="1" t="s">
         <v>35</v>
       </c>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="E638" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="639" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="639" customHeight="1" ht="17.25">
       <c r="A639" s="1" t="s">
         <v>35</v>
       </c>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="E639" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="640" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="640" customHeight="1" ht="17.25">
       <c r="A640" s="1" t="s">
         <v>35</v>
       </c>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="E640" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="641" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="641" customHeight="1" ht="17.25">
       <c r="A641" s="1" t="s">
         <v>35</v>
       </c>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="E641" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="642" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="642" customHeight="1" ht="17.25">
       <c r="A642" s="1" t="s">
         <v>35</v>
       </c>
@@ -14266,7 +14266,7 @@
       </c>
       <c r="E642" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="643" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="643" customHeight="1" ht="17.25">
       <c r="A643" s="1" t="s">
         <v>35</v>
       </c>
@@ -14281,7 +14281,7 @@
       </c>
       <c r="E643" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="644" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="644" customHeight="1" ht="17.25">
       <c r="A644" s="1" t="s">
         <v>35</v>
       </c>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E644" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="645" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="645" customHeight="1" ht="17.25">
       <c r="A645" s="1" t="s">
         <v>35</v>
       </c>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="E645" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="646" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="646" customHeight="1" ht="17.25">
       <c r="A646" s="1" t="s">
         <v>35</v>
       </c>
@@ -14326,7 +14326,7 @@
       </c>
       <c r="E646" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="647" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="647" customHeight="1" ht="17.25">
       <c r="A647" s="1" t="s">
         <v>35</v>
       </c>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="E647" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="648" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="648" customHeight="1" ht="17.25">
       <c r="A648" s="1" t="s">
         <v>35</v>
       </c>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="E648" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="649" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="649" customHeight="1" ht="17.25">
       <c r="A649" s="1" t="s">
         <v>35</v>
       </c>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="E649" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="650" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="650" customHeight="1" ht="17.25">
       <c r="A650" s="1" t="s">
         <v>35</v>
       </c>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="E650" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="651" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="651" customHeight="1" ht="17.25">
       <c r="A651" s="1" t="s">
         <v>35</v>
       </c>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E651" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="652" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="652" customHeight="1" ht="17.25">
       <c r="A652" s="1" t="s">
         <v>35</v>
       </c>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="E652" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="653" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="653" customHeight="1" ht="17.25">
       <c r="A653" s="1" t="s">
         <v>35</v>
       </c>
@@ -14426,10 +14426,10 @@
       <c r="C653" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="D653" s="1"/>
+      <c r="D653" s="3"/>
       <c r="E653" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="654" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="654" customHeight="1" ht="17.25">
       <c r="A654" s="1" t="s">
         <v>35</v>
       </c>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="E654" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="655" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="655" customHeight="1" ht="17.25">
       <c r="A655" s="1" t="s">
         <v>35</v>
       </c>
@@ -14454,10 +14454,10 @@
       <c r="C655" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="D655" s="1"/>
+      <c r="D655" s="3"/>
       <c r="E655" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="656" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="656" customHeight="1" ht="17.25">
       <c r="A656" s="1" t="s">
         <v>35</v>
       </c>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="E656" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="657" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="657" customHeight="1" ht="17.25">
       <c r="A657" s="1" t="s">
         <v>35</v>
       </c>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E657" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="658" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="658" customHeight="1" ht="17.25">
       <c r="A658" s="1" t="s">
         <v>35</v>
       </c>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="E658" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="659" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="659" customHeight="1" ht="17.25">
       <c r="A659" s="1" t="s">
         <v>35</v>
       </c>
@@ -14517,7 +14517,7 @@
       </c>
       <c r="E659" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="660" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="660" customHeight="1" ht="17.25">
       <c r="A660" s="1" t="s">
         <v>35</v>
       </c>
@@ -14532,7 +14532,7 @@
       </c>
       <c r="E660" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="661" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="661" customHeight="1" ht="17.25">
       <c r="A661" s="1" t="s">
         <v>35</v>
       </c>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="E661" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="662" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="662" customHeight="1" ht="17.25">
       <c r="A662" s="1" t="s">
         <v>35</v>
       </c>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="E662" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="663" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="663" customHeight="1" ht="17.25">
       <c r="A663" s="1" t="s">
         <v>35</v>
       </c>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="E663" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="664" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="664" customHeight="1" ht="17.25">
       <c r="A664" s="1" t="s">
         <v>35</v>
       </c>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E664" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="665" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="665" customHeight="1" ht="17.25">
       <c r="A665" s="1" t="s">
         <v>35</v>
       </c>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="E665" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="666" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="666" customHeight="1" ht="17.25">
       <c r="A666" s="1" t="s">
         <v>35</v>
       </c>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="E666" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="667" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="667" customHeight="1" ht="17.25">
       <c r="A667" s="1" t="s">
         <v>35</v>
       </c>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="E667" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="668" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="668" customHeight="1" ht="17.25">
       <c r="A668" s="1" t="s">
         <v>35</v>
       </c>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="E668" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="669" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="669" customHeight="1" ht="17.25">
       <c r="A669" s="1" t="s">
         <v>35</v>
       </c>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="E669" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="670" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="670" customHeight="1" ht="17.25">
       <c r="A670" s="1" t="s">
         <v>35</v>
       </c>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="E670" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="671" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="671" customHeight="1" ht="17.25">
       <c r="A671" s="1" t="s">
         <v>35</v>
       </c>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="E671" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="672" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="672" customHeight="1" ht="17.25">
       <c r="A672" s="1" t="s">
         <v>35</v>
       </c>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="E672" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="673" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="673" customHeight="1" ht="17.25">
       <c r="A673" s="1" t="s">
         <v>35</v>
       </c>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="E673" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="674" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="674" customHeight="1" ht="17.25">
       <c r="A674" s="1" t="s">
         <v>35</v>
       </c>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="E674" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="675" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="675" customHeight="1" ht="17.25">
       <c r="A675" s="1" t="s">
         <v>35</v>
       </c>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="E675" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="676" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="676" customHeight="1" ht="17.25">
       <c r="A676" s="1" t="s">
         <v>35</v>
       </c>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="E676" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="677" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="677" customHeight="1" ht="17.25">
       <c r="A677" s="1" t="s">
         <v>35</v>
       </c>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="E677" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="678" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="678" customHeight="1" ht="17.25">
       <c r="A678" s="1" t="s">
         <v>35</v>
       </c>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="E678" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="679" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="679" customHeight="1" ht="17.25">
       <c r="A679" s="1" t="s">
         <v>35</v>
       </c>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="E679" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="680" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="680" customHeight="1" ht="17.25">
       <c r="A680" s="1" t="s">
         <v>35</v>
       </c>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="E680" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="681" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="681" customHeight="1" ht="17.25">
       <c r="A681" s="1" t="s">
         <v>35</v>
       </c>
@@ -14842,10 +14842,10 @@
       <c r="C681" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="D681" s="1"/>
+      <c r="D681" s="3"/>
       <c r="E681" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="682" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="682" customHeight="1" ht="17.25">
       <c r="A682" s="1" t="s">
         <v>35</v>
       </c>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="E682" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="683" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="683" customHeight="1" ht="17.25">
       <c r="A683" s="1" t="s">
         <v>35</v>
       </c>
@@ -14875,7 +14875,7 @@
       </c>
       <c r="E683" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="684" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="684" customHeight="1" ht="17.25">
       <c r="A684" s="1" t="s">
         <v>35</v>
       </c>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="E684" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="685" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="685" customHeight="1" ht="17.25">
       <c r="A685" s="1" t="s">
         <v>35</v>
       </c>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="E685" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="686" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="686" customHeight="1" ht="17.25">
       <c r="A686" s="1" t="s">
         <v>35</v>
       </c>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="E686" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="687" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="687" customHeight="1" ht="17.25">
       <c r="A687" s="1" t="s">
         <v>35</v>
       </c>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="E687" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="688" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="688" customHeight="1" ht="17.25">
       <c r="A688" s="1" t="s">
         <v>35</v>
       </c>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="E688" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="689" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="689" customHeight="1" ht="17.25">
       <c r="A689" s="1" t="s">
         <v>35</v>
       </c>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="E689" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="690" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="690" customHeight="1" ht="17.25">
       <c r="A690" s="1" t="s">
         <v>35</v>
       </c>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="E690" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="691" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="691" customHeight="1" ht="17.25">
       <c r="A691" s="1" t="s">
         <v>35</v>
       </c>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="E691" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="692" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="692" customHeight="1" ht="17.25">
       <c r="A692" s="1" t="s">
         <v>35</v>
       </c>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="E692" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="693" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="693" customHeight="1" ht="17.25">
       <c r="A693" s="1" t="s">
         <v>35</v>
       </c>
@@ -15025,7 +15025,7 @@
       </c>
       <c r="E693" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="694" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="694" customHeight="1" ht="17.25">
       <c r="A694" s="1" t="s">
         <v>35</v>
       </c>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="E694" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="695" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="695" customHeight="1" ht="17.25">
       <c r="A695" s="1" t="s">
         <v>35</v>
       </c>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="E695" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="696" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="696" customHeight="1" ht="17.25">
       <c r="A696" s="1" t="s">
         <v>35</v>
       </c>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="E696" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="697" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="697" customHeight="1" ht="17.25">
       <c r="A697" s="1" t="s">
         <v>35</v>
       </c>
@@ -15085,7 +15085,7 @@
       </c>
       <c r="E697" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="698" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="698" customHeight="1" ht="17.25">
       <c r="A698" s="1" t="s">
         <v>35</v>
       </c>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="E698" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="699" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="699" customHeight="1" ht="17.25">
       <c r="A699" s="1" t="s">
         <v>35</v>
       </c>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="E699" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="700" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="700" customHeight="1" ht="17.25">
       <c r="A700" s="1" t="s">
         <v>35</v>
       </c>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="E700" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="701" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="701" customHeight="1" ht="17.25">
       <c r="A701" s="1" t="s">
         <v>35</v>
       </c>
@@ -15145,7 +15145,7 @@
       </c>
       <c r="E701" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="702" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="702" customHeight="1" ht="17.25">
       <c r="A702" s="1" t="s">
         <v>35</v>
       </c>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="E702" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="703" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="703" customHeight="1" ht="17.25">
       <c r="A703" s="1" t="s">
         <v>35</v>
       </c>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="E703" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="704" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="704" customHeight="1" ht="17.25">
       <c r="A704" s="1" t="s">
         <v>35</v>
       </c>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="E704" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="705" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="705" customHeight="1" ht="17.25">
       <c r="A705" s="1" t="s">
         <v>35</v>
       </c>
@@ -15205,7 +15205,7 @@
       </c>
       <c r="E705" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="706" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="706" customHeight="1" ht="17.25">
       <c r="A706" s="1" t="s">
         <v>35</v>
       </c>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="E706" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="707" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="707" customHeight="1" ht="17.25">
       <c r="A707" s="1" t="s">
         <v>35</v>
       </c>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="E707" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="708" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="708" customHeight="1" ht="17.25">
       <c r="A708" s="1" t="s">
         <v>35</v>
       </c>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E708" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="709" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="709" customHeight="1" ht="17.25">
       <c r="A709" s="1" t="s">
         <v>35</v>
       </c>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="E709" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="710" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="710" customHeight="1" ht="17.25">
       <c r="A710" s="1" t="s">
         <v>35</v>
       </c>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E710" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="711" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="711" customHeight="1" ht="17.25">
       <c r="A711" s="1" t="s">
         <v>35</v>
       </c>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="E711" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="712" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="712" customHeight="1" ht="17.25">
       <c r="A712" s="1" t="s">
         <v>35</v>
       </c>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="E712" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="713" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="713" customHeight="1" ht="17.25">
       <c r="A713" s="1" t="s">
         <v>35</v>
       </c>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="E713" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="714" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="714" customHeight="1" ht="17.25">
       <c r="A714" s="1" t="s">
         <v>35</v>
       </c>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="E714" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="715" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="715" customHeight="1" ht="17.25">
       <c r="A715" s="1" t="s">
         <v>35</v>
       </c>
@@ -15355,7 +15355,7 @@
       </c>
       <c r="E715" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="716" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="716" customHeight="1" ht="17.25">
       <c r="A716" s="1" t="s">
         <v>35</v>
       </c>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="E716" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="717" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="717" customHeight="1" ht="17.25">
       <c r="A717" s="1" t="s">
         <v>35</v>
       </c>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="E717" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="718" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="718" customHeight="1" ht="17.25">
       <c r="A718" s="1" t="s">
         <v>35</v>
       </c>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="E718" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="719" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="719" customHeight="1" ht="17.25">
       <c r="A719" s="1" t="s">
         <v>35</v>
       </c>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="E719" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="720" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="720" customHeight="1" ht="17.25">
       <c r="A720" s="1" t="s">
         <v>35</v>
       </c>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="E720" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="721" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="721" customHeight="1" ht="17.25">
       <c r="A721" s="1" t="s">
         <v>35</v>
       </c>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="E721" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="722" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="722" customHeight="1" ht="17.25">
       <c r="A722" s="1" t="s">
         <v>35</v>
       </c>
@@ -15455,10 +15455,10 @@
       <c r="C722" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="D722" s="1"/>
+      <c r="D722" s="3"/>
       <c r="E722" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="723" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="723" customHeight="1" ht="17.25">
       <c r="A723" s="1" t="s">
         <v>35</v>
       </c>
@@ -15468,10 +15468,10 @@
       <c r="C723" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="D723" s="1"/>
+      <c r="D723" s="3"/>
       <c r="E723" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="724" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="724" customHeight="1" ht="17.25">
       <c r="A724" s="1" t="s">
         <v>35</v>
       </c>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="E724" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="725" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="725" customHeight="1" ht="17.25">
       <c r="A725" s="1" t="s">
         <v>35</v>
       </c>
@@ -15501,7 +15501,7 @@
       </c>
       <c r="E725" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="726" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="726" customHeight="1" ht="17.25">
       <c r="A726" s="1" t="s">
         <v>35</v>
       </c>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="E726" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="727" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="727" customHeight="1" ht="17.25">
       <c r="A727" s="1" t="s">
         <v>35</v>
       </c>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="E727" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="728" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="728" customHeight="1" ht="17.25">
       <c r="A728" s="1" t="s">
         <v>35</v>
       </c>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="E728" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="729" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="729" customHeight="1" ht="17.25">
       <c r="A729" s="1" t="s">
         <v>35</v>
       </c>
@@ -15556,10 +15556,10 @@
       <c r="C729" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="D729" s="1"/>
+      <c r="D729" s="3"/>
       <c r="E729" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="730" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="730" customHeight="1" ht="17.25">
       <c r="A730" s="1" t="s">
         <v>35</v>
       </c>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="E730" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="731" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="731" customHeight="1" ht="17.25">
       <c r="A731" s="1" t="s">
         <v>35</v>
       </c>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="E731" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="732" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="732" customHeight="1" ht="17.25">
       <c r="A732" s="1" t="s">
         <v>35</v>
       </c>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="E732" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="733" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="733" customHeight="1" ht="17.25">
       <c r="A733" s="1" t="s">
         <v>35</v>
       </c>
@@ -15619,7 +15619,7 @@
       </c>
       <c r="E733" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="734" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="734" customHeight="1" ht="17.25">
       <c r="A734" s="1" t="s">
         <v>35</v>
       </c>
@@ -15629,10 +15629,10 @@
       <c r="C734" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="D734" s="1"/>
+      <c r="D734" s="3"/>
       <c r="E734" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="735" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="735" customHeight="1" ht="17.25">
       <c r="A735" s="1" t="s">
         <v>35</v>
       </c>
@@ -15642,10 +15642,10 @@
       <c r="C735" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="D735" s="1"/>
+      <c r="D735" s="3"/>
       <c r="E735" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="736" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="736" customHeight="1" ht="17.25">
       <c r="A736" s="1" t="s">
         <v>35</v>
       </c>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="E736" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="737" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="737" customHeight="1" ht="17.25">
       <c r="A737" s="1" t="s">
         <v>35</v>
       </c>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="E737" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="738" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="738" customHeight="1" ht="17.25">
       <c r="A738" s="1" t="s">
         <v>35</v>
       </c>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E738" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="739" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="739" customHeight="1" ht="17.25">
       <c r="A739" s="1" t="s">
         <v>35</v>
       </c>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="E739" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="740" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="740" customHeight="1" ht="17.25">
       <c r="A740" s="1" t="s">
         <v>35</v>
       </c>
@@ -15720,7 +15720,7 @@
       </c>
       <c r="E740" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="741" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="741" customHeight="1" ht="17.25">
       <c r="A741" s="1" t="s">
         <v>35</v>
       </c>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="E741" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="742" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="742" customHeight="1" ht="17.25">
       <c r="A742" s="1" t="s">
         <v>35</v>
       </c>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="E742" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="743" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="743" customHeight="1" ht="17.25">
       <c r="A743" s="1" t="s">
         <v>35</v>
       </c>
@@ -15765,7 +15765,7 @@
       </c>
       <c r="E743" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="744" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="744" customHeight="1" ht="17.25">
       <c r="A744" s="1" t="s">
         <v>35</v>
       </c>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="E744" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="745" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="745" customHeight="1" ht="17.25">
       <c r="A745" s="1" t="s">
         <v>35</v>
       </c>
@@ -15795,7 +15795,7 @@
       </c>
       <c r="E745" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="746" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="746" customHeight="1" ht="17.25">
       <c r="A746" s="1" t="s">
         <v>35</v>
       </c>
@@ -15810,7 +15810,7 @@
       </c>
       <c r="E746" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="747" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="747" customHeight="1" ht="17.25">
       <c r="A747" s="1" t="s">
         <v>35</v>
       </c>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="E747" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="748" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="748" customHeight="1" ht="17.25">
       <c r="A748" s="1" t="s">
         <v>35</v>
       </c>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="E748" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="749" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="749" customHeight="1" ht="17.25">
       <c r="A749" s="1" t="s">
         <v>35</v>
       </c>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="E749" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="750" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="750" customHeight="1" ht="17.25">
       <c r="A750" s="1" t="s">
         <v>35</v>
       </c>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="E750" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="751" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="751" customHeight="1" ht="17.25">
       <c r="A751" s="1" t="s">
         <v>35</v>
       </c>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E751" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="752" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="752" customHeight="1" ht="17.25">
       <c r="A752" s="1" t="s">
         <v>35</v>
       </c>
@@ -15900,7 +15900,7 @@
       </c>
       <c r="E752" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="753" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="753" customHeight="1" ht="17.25">
       <c r="A753" s="1" t="s">
         <v>35</v>
       </c>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="E753" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="754" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="754" customHeight="1" ht="17.25">
       <c r="A754" s="1" t="s">
         <v>35</v>
       </c>
@@ -15925,10 +15925,10 @@
       <c r="C754" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="D754" s="1"/>
+      <c r="D754" s="3"/>
       <c r="E754" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="755" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="755" customHeight="1" ht="17.25">
       <c r="A755" s="1" t="s">
         <v>35</v>
       </c>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="E755" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="756" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="756" customHeight="1" ht="17.25">
       <c r="A756" s="1" t="s">
         <v>35</v>
       </c>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="E756" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="757" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="757" customHeight="1" ht="17.25">
       <c r="A757" s="1" t="s">
         <v>35</v>
       </c>
@@ -15973,7 +15973,7 @@
       </c>
       <c r="E757" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="758" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="758" customHeight="1" ht="17.25">
       <c r="A758" s="1" t="s">
         <v>35</v>
       </c>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="E758" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="759" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="759" customHeight="1" ht="17.25">
       <c r="A759" s="1" t="s">
         <v>35</v>
       </c>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="E759" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="760" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="760" customHeight="1" ht="17.25">
       <c r="A760" s="1" t="s">
         <v>35</v>
       </c>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E760" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="761" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="761" customHeight="1" ht="17.25">
       <c r="A761" s="1" t="s">
         <v>35</v>
       </c>
@@ -16033,7 +16033,7 @@
       </c>
       <c r="E761" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="762" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="762" customHeight="1" ht="17.25">
       <c r="A762" s="1" t="s">
         <v>35</v>
       </c>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="E762" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="763" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="763" customHeight="1" ht="17.25">
       <c r="A763" s="1" t="s">
         <v>35</v>
       </c>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="E763" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="764" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="764" customHeight="1" ht="17.25">
       <c r="A764" s="1" t="s">
         <v>35</v>
       </c>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="E764" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="765" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="765" customHeight="1" ht="17.25">
       <c r="A765" s="1" t="s">
         <v>35</v>
       </c>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="E765" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="766" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="766" customHeight="1" ht="17.25">
       <c r="A766" s="1" t="s">
         <v>35</v>
       </c>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="E766" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="767" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="767" customHeight="1" ht="17.25">
       <c r="A767" s="1" t="s">
         <v>35</v>
       </c>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="E767" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="768" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="768" customHeight="1" ht="17.25">
       <c r="A768" s="1" t="s">
         <v>35</v>
       </c>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="E768" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="769" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="769" customHeight="1" ht="17.25">
       <c r="A769" s="1" t="s">
         <v>35</v>
       </c>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="E769" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="770" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="770" customHeight="1" ht="17.25">
       <c r="A770" s="1" t="s">
         <v>35</v>
       </c>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="E770" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="771" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="771" customHeight="1" ht="17.25">
       <c r="A771" s="1" t="s">
         <v>35</v>
       </c>
@@ -16183,7 +16183,7 @@
       </c>
       <c r="E771" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="772" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="772" customHeight="1" ht="17.25">
       <c r="A772" s="1" t="s">
         <v>35</v>
       </c>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="E772" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="773" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="773" customHeight="1" ht="17.25">
       <c r="A773" s="1" t="s">
         <v>35</v>
       </c>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="E773" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="774" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="774" customHeight="1" ht="17.25">
       <c r="A774" s="1" t="s">
         <v>35</v>
       </c>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="E774" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="775" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="775" customHeight="1" ht="17.25">
       <c r="A775" s="1" t="s">
         <v>35</v>
       </c>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="E775" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="776" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="776" customHeight="1" ht="17.25">
       <c r="A776" s="1" t="s">
         <v>35</v>
       </c>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="E776" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="777" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="777" customHeight="1" ht="17.25">
       <c r="A777" s="1" t="s">
         <v>35</v>
       </c>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="E777" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="778" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="778" customHeight="1" ht="17.25">
       <c r="A778" s="1" t="s">
         <v>35</v>
       </c>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="E778" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="779" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="779" customHeight="1" ht="17.25">
       <c r="A779" s="1" t="s">
         <v>35</v>
       </c>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="E779" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="780" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="780" customHeight="1" ht="17.25">
       <c r="A780" s="1" t="s">
         <v>35</v>
       </c>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="E780" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="781" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="781" customHeight="1" ht="17.25">
       <c r="A781" s="1" t="s">
         <v>35</v>
       </c>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="E781" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="782" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="782" customHeight="1" ht="17.25">
       <c r="A782" s="1" t="s">
         <v>35</v>
       </c>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="E782" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="783" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="783" customHeight="1" ht="17.25">
       <c r="A783" s="1" t="s">
         <v>35</v>
       </c>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="E783" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="784" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="784" customHeight="1" ht="17.25">
       <c r="A784" s="1" t="s">
         <v>35</v>
       </c>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="E784" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="785" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="785" customHeight="1" ht="17.25">
       <c r="A785" s="1" t="s">
         <v>35</v>
       </c>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="E785" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="786" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="786" customHeight="1" ht="17.25">
       <c r="A786" s="1" t="s">
         <v>35</v>
       </c>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="E786" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="787" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="787" customHeight="1" ht="17.25">
       <c r="A787" s="1" t="s">
         <v>35</v>
       </c>
@@ -16423,7 +16423,7 @@
       </c>
       <c r="E787" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="788" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="788" customHeight="1" ht="17.25">
       <c r="A788" s="1" t="s">
         <v>35</v>
       </c>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="E788" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="789" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="789" customHeight="1" ht="17.25">
       <c r="A789" s="1" t="s">
         <v>35</v>
       </c>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="E789" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="790" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="790" customHeight="1" ht="17.25">
       <c r="A790" s="1" t="s">
         <v>35</v>
       </c>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="E790" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="791" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="791" customHeight="1" ht="17.25">
       <c r="A791" s="1" t="s">
         <v>35</v>
       </c>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="E791" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="792" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="792" customHeight="1" ht="17.25">
       <c r="A792" s="1" t="s">
         <v>35</v>
       </c>
@@ -16498,7 +16498,7 @@
       </c>
       <c r="E792" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="793" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="793" customHeight="1" ht="17.25">
       <c r="A793" s="1" t="s">
         <v>35</v>
       </c>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="E793" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="794" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="794" customHeight="1" ht="17.25">
       <c r="A794" s="1" t="s">
         <v>35</v>
       </c>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="E794" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="795" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="795" customHeight="1" ht="17.25">
       <c r="A795" s="1" t="s">
         <v>35</v>
       </c>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="E795" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="796" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="796" customHeight="1" ht="17.25">
       <c r="A796" s="1" t="s">
         <v>35</v>
       </c>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="E796" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="797" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="797" customHeight="1" ht="17.25">
       <c r="A797" s="1" t="s">
         <v>35</v>
       </c>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="E797" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="798" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="798" customHeight="1" ht="17.25">
       <c r="A798" s="1" t="s">
         <v>35</v>
       </c>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="E798" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="799" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="799" customHeight="1" ht="17.25">
       <c r="A799" s="1" t="s">
         <v>35</v>
       </c>
@@ -16603,7 +16603,7 @@
       </c>
       <c r="E799" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="800" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="800" customHeight="1" ht="17.25">
       <c r="A800" s="1" t="s">
         <v>35</v>
       </c>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="E800" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="801" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="801" customHeight="1" ht="17.25">
       <c r="A801" s="1" t="s">
         <v>35</v>
       </c>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E801" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="802" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="802" customHeight="1" ht="17.25">
       <c r="A802" s="1" t="s">
         <v>35</v>
       </c>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="E802" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="803" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="803" customHeight="1" ht="17.25">
       <c r="A803" s="1" t="s">
         <v>35</v>
       </c>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="E803" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="804" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="804" customHeight="1" ht="17.25">
       <c r="A804" s="1" t="s">
         <v>35</v>
       </c>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="E804" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="805" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="805" customHeight="1" ht="17.25">
       <c r="A805" s="1" t="s">
         <v>35</v>
       </c>
@@ -16693,7 +16693,7 @@
       </c>
       <c r="E805" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="806" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="806" customHeight="1" ht="17.25">
       <c r="A806" s="1" t="s">
         <v>35</v>
       </c>
@@ -16708,7 +16708,7 @@
       </c>
       <c r="E806" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="807" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="807" customHeight="1" ht="17.25">
       <c r="A807" s="1" t="s">
         <v>35</v>
       </c>
@@ -16723,7 +16723,7 @@
       </c>
       <c r="E807" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="808" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="808" customHeight="1" ht="17.25">
       <c r="A808" s="1" t="s">
         <v>35</v>
       </c>
@@ -16738,7 +16738,7 @@
       </c>
       <c r="E808" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="809" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="809" customHeight="1" ht="17.25">
       <c r="A809" s="1" t="s">
         <v>35</v>
       </c>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="E809" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="810" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="810" customHeight="1" ht="17.25">
       <c r="A810" s="1" t="s">
         <v>35</v>
       </c>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="E810" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="811" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="811" customHeight="1" ht="17.25">
       <c r="A811" s="1" t="s">
         <v>35</v>
       </c>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="E811" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="812" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="812" customHeight="1" ht="17.25">
       <c r="A812" s="1" t="s">
         <v>35</v>
       </c>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="E812" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="813" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="813" customHeight="1" ht="17.25">
       <c r="A813" s="1" t="s">
         <v>35</v>
       </c>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="E813" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="814" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="814" customHeight="1" ht="17.25">
       <c r="A814" s="1" t="s">
         <v>35</v>
       </c>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="E814" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="815" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="815" customHeight="1" ht="17.25">
       <c r="A815" s="1" t="s">
         <v>35</v>
       </c>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="E815" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="816" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="816" customHeight="1" ht="17.25">
       <c r="A816" s="1" t="s">
         <v>35</v>
       </c>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="E816" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="817" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="817" customHeight="1" ht="17.25">
       <c r="A817" s="1" t="s">
         <v>35</v>
       </c>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="E817" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="818" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="818" customHeight="1" ht="17.25">
       <c r="A818" s="1" t="s">
         <v>35</v>
       </c>
@@ -16888,7 +16888,7 @@
       </c>
       <c r="E818" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="819" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="819" customHeight="1" ht="17.25">
       <c r="A819" s="1" t="s">
         <v>35</v>
       </c>
@@ -16903,7 +16903,7 @@
       </c>
       <c r="E819" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="820" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="820" customHeight="1" ht="17.25">
       <c r="A820" s="1" t="s">
         <v>35</v>
       </c>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="E820" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="821" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="821" customHeight="1" ht="17.25">
       <c r="A821" s="1" t="s">
         <v>35</v>
       </c>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="E821" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="822" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="822" customHeight="1" ht="17.25">
       <c r="A822" s="1" t="s">
         <v>35</v>
       </c>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="E822" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="823" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="823" customHeight="1" ht="17.25">
       <c r="A823" s="1" t="s">
         <v>35</v>
       </c>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="E823" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="824" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="824" customHeight="1" ht="17.25">
       <c r="A824" s="1" t="s">
         <v>35</v>
       </c>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="E824" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="825" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="825" customHeight="1" ht="17.25">
       <c r="A825" s="1" t="s">
         <v>35</v>
       </c>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="E825" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="826" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="826" customHeight="1" ht="17.25">
       <c r="A826" s="1" t="s">
         <v>35</v>
       </c>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="E826" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="827" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="827" customHeight="1" ht="17.25">
       <c r="A827" s="1" t="s">
         <v>35</v>
       </c>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="E827" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="828" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="828" customHeight="1" ht="17.25">
       <c r="A828" s="1" t="s">
         <v>35</v>
       </c>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="E828" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="829" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="829" customHeight="1" ht="17.25">
       <c r="A829" s="1" t="s">
         <v>35</v>
       </c>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="E829" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="830" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="830" customHeight="1" ht="17.25">
       <c r="A830" s="1" t="s">
         <v>35</v>
       </c>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="E830" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="831" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="831" customHeight="1" ht="17.25">
       <c r="A831" s="1" t="s">
         <v>35</v>
       </c>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="E831" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="832" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="832" customHeight="1" ht="17.25">
       <c r="A832" s="1" t="s">
         <v>35</v>
       </c>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="E832" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="833" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="833" customHeight="1" ht="17.25">
       <c r="A833" s="1" t="s">
         <v>35</v>
       </c>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="E833" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="834" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="834" customHeight="1" ht="17.25">
       <c r="A834" s="1" t="s">
         <v>35</v>
       </c>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="E834" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="835" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="835" customHeight="1" ht="17.25">
       <c r="A835" s="1" t="s">
         <v>35</v>
       </c>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="E835" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="836" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="836" customHeight="1" ht="17.25">
       <c r="A836" s="1" t="s">
         <v>35</v>
       </c>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="E836" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="837" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="837" customHeight="1" ht="17.25">
       <c r="A837" s="1" t="s">
         <v>35</v>
       </c>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="E837" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="838" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="838" customHeight="1" ht="17.25">
       <c r="A838" s="1" t="s">
         <v>35</v>
       </c>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="E838" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="839" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="839" customHeight="1" ht="17.25">
       <c r="A839" s="1" t="s">
         <v>35</v>
       </c>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="E839" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="840" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="840" customHeight="1" ht="17.25">
       <c r="A840" s="1" t="s">
         <v>35</v>
       </c>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="E840" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="841" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="841" customHeight="1" ht="17.25">
       <c r="A841" s="1" t="s">
         <v>35</v>
       </c>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="E841" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="842" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="842" customHeight="1" ht="17.25">
       <c r="A842" s="1" t="s">
         <v>35</v>
       </c>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E842" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="843" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="843" customHeight="1" ht="17.25">
       <c r="A843" s="1" t="s">
         <v>35</v>
       </c>
@@ -17263,7 +17263,7 @@
       </c>
       <c r="E843" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="844" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="844" customHeight="1" ht="17.25">
       <c r="A844" s="1" t="s">
         <v>35</v>
       </c>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="E844" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="845" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="845" customHeight="1" ht="17.25">
       <c r="A845" s="1" t="s">
         <v>35</v>
       </c>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="E845" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="846" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="846" customHeight="1" ht="17.25">
       <c r="A846" s="1" t="s">
         <v>35</v>
       </c>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="E846" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="847" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="847" customHeight="1" ht="17.25">
       <c r="A847" s="1" t="s">
         <v>35</v>
       </c>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="E847" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="848" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="848" customHeight="1" ht="17.25">
       <c r="A848" s="1" t="s">
         <v>35</v>
       </c>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="E848" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="849" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="849" customHeight="1" ht="17.25">
       <c r="A849" s="1" t="s">
         <v>35</v>
       </c>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="E849" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="850" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="850" customHeight="1" ht="17.25">
       <c r="A850" s="1" t="s">
         <v>35</v>
       </c>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="E850" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="851" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="851" customHeight="1" ht="17.25">
       <c r="A851" s="1" t="s">
         <v>35</v>
       </c>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="E851" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="852" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="852" customHeight="1" ht="17.25">
       <c r="A852" s="1" t="s">
         <v>35</v>
       </c>
@@ -17398,7 +17398,7 @@
       </c>
       <c r="E852" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="853" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="853" customHeight="1" ht="17.25">
       <c r="A853" s="1" t="s">
         <v>35</v>
       </c>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="E853" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="854" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="854" customHeight="1" ht="17.25">
       <c r="A854" s="1" t="s">
         <v>35</v>
       </c>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="E854" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="855" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="855" customHeight="1" ht="17.25">
       <c r="A855" s="1" t="s">
         <v>35</v>
       </c>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="E855" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="856" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="856" customHeight="1" ht="17.25">
       <c r="A856" s="1" t="s">
         <v>35</v>
       </c>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="E856" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="857" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="857" customHeight="1" ht="17.25">
       <c r="A857" s="1" t="s">
         <v>35</v>
       </c>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="E857" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="858" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="858" customHeight="1" ht="17.25">
       <c r="A858" s="1" t="s">
         <v>35</v>
       </c>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="E858" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="859" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="859" customHeight="1" ht="17.25">
       <c r="A859" s="1" t="s">
         <v>35</v>
       </c>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="E859" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="860" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="860" customHeight="1" ht="17.25">
       <c r="A860" s="1" t="s">
         <v>35</v>
       </c>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="E860" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="861" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="861" customHeight="1" ht="17.25">
       <c r="A861" s="1" t="s">
         <v>35</v>
       </c>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="E861" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="862" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="862" customHeight="1" ht="17.25">
       <c r="A862" s="1" t="s">
         <v>35</v>
       </c>
@@ -17548,7 +17548,7 @@
       </c>
       <c r="E862" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="863" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="863" customHeight="1" ht="17.25">
       <c r="A863" s="1" t="s">
         <v>35</v>
       </c>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="E863" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="864" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="864" customHeight="1" ht="17.25">
       <c r="A864" s="1" t="s">
         <v>35</v>
       </c>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="E864" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="865" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="865" customHeight="1" ht="17.25">
       <c r="A865" s="1" t="s">
         <v>35</v>
       </c>
@@ -17593,7 +17593,7 @@
       </c>
       <c r="E865" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="866" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="866" customHeight="1" ht="17.25">
       <c r="A866" s="1" t="s">
         <v>35</v>
       </c>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="E866" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="867" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="867" customHeight="1" ht="17.25">
       <c r="A867" s="1" t="s">
         <v>35</v>
       </c>
@@ -17618,10 +17618,10 @@
       <c r="C867" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="D867" s="1"/>
+      <c r="D867" s="3"/>
       <c r="E867" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="868" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="868" customHeight="1" ht="17.25">
       <c r="A868" s="1" t="s">
         <v>35</v>
       </c>
@@ -17636,7 +17636,7 @@
       </c>
       <c r="E868" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="869" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="869" customHeight="1" ht="17.25">
       <c r="A869" s="1" t="s">
         <v>35</v>
       </c>
@@ -17646,10 +17646,10 @@
       <c r="C869" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="D869" s="1"/>
+      <c r="D869" s="3"/>
       <c r="E869" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="870" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="870" customHeight="1" ht="17.25">
       <c r="A870" s="1" t="s">
         <v>35</v>
       </c>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="E870" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="871" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="871" customHeight="1" ht="17.25">
       <c r="A871" s="1" t="s">
         <v>35</v>
       </c>
@@ -17679,7 +17679,7 @@
       </c>
       <c r="E871" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="872" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="872" customHeight="1" ht="17.25">
       <c r="A872" s="1" t="s">
         <v>35</v>
       </c>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="E872" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="873" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="873" customHeight="1" ht="17.25">
       <c r="A873" s="1" t="s">
         <v>35</v>
       </c>
@@ -17704,10 +17704,10 @@
       <c r="C873" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="D873" s="1"/>
+      <c r="D873" s="3"/>
       <c r="E873" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="874" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="874" customHeight="1" ht="17.25">
       <c r="A874" s="1" t="s">
         <v>35</v>
       </c>
@@ -17722,7 +17722,7 @@
       </c>
       <c r="E874" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="875" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="875" customHeight="1" ht="17.25">
       <c r="A875" s="1" t="s">
         <v>35</v>
       </c>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="E875" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="876" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="876" customHeight="1" ht="17.25">
       <c r="A876" s="1" t="s">
         <v>35</v>
       </c>
@@ -17747,10 +17747,10 @@
       <c r="C876" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="D876" s="1"/>
+      <c r="D876" s="3"/>
       <c r="E876" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="877" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="877" customHeight="1" ht="17.25">
       <c r="A877" s="1" t="s">
         <v>35</v>
       </c>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="E877" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="878" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="878" customHeight="1" ht="17.25">
       <c r="A878" s="1" t="s">
         <v>35</v>
       </c>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="E878" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="879" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="879" customHeight="1" ht="17.25">
       <c r="A879" s="1" t="s">
         <v>35</v>
       </c>
@@ -17795,7 +17795,7 @@
       </c>
       <c r="E879" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="880" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="880" customHeight="1" ht="17.25">
       <c r="A880" s="1" t="s">
         <v>35</v>
       </c>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="E880" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="881" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="881" customHeight="1" ht="17.25">
       <c r="A881" s="1" t="s">
         <v>35</v>
       </c>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="E881" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="882" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="882" customHeight="1" ht="17.25">
       <c r="A882" s="1" t="s">
         <v>35</v>
       </c>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="E882" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="883" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="883" customHeight="1" ht="17.25">
       <c r="A883" s="1" t="s">
         <v>35</v>
       </c>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="E883" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="884" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="884" customHeight="1" ht="17.25">
       <c r="A884" s="1" t="s">
         <v>35</v>
       </c>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="E884" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="885" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="885" customHeight="1" ht="17.25">
       <c r="A885" s="1" t="s">
         <v>35</v>
       </c>
@@ -17885,7 +17885,7 @@
       </c>
       <c r="E885" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="886" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="886" customHeight="1" ht="17.25">
       <c r="A886" s="1" t="s">
         <v>35</v>
       </c>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="E886" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="887" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="887" customHeight="1" ht="17.25">
       <c r="A887" s="1" t="s">
         <v>35</v>
       </c>
@@ -17915,7 +17915,7 @@
       </c>
       <c r="E887" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="888" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="888" customHeight="1" ht="17.25">
       <c r="A888" s="1" t="s">
         <v>35</v>
       </c>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="E888" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="889" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="889" customHeight="1" ht="17.25">
       <c r="A889" s="1" t="s">
         <v>35</v>
       </c>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E889" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="890" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="890" customHeight="1" ht="17.25">
       <c r="A890" s="1" t="s">
         <v>35</v>
       </c>
@@ -17960,7 +17960,7 @@
       </c>
       <c r="E890" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="891" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="891" customHeight="1" ht="17.25">
       <c r="A891" s="1" t="s">
         <v>35</v>
       </c>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="E891" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="892" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="892" customHeight="1" ht="17.25">
       <c r="A892" s="1" t="s">
         <v>35</v>
       </c>
@@ -17985,10 +17985,10 @@
       <c r="C892" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="D892" s="1"/>
+      <c r="D892" s="3"/>
       <c r="E892" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="893" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="893" customHeight="1" ht="17.25">
       <c r="A893" s="1" t="s">
         <v>35</v>
       </c>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="E893" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="894" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="894" customHeight="1" ht="17.25">
       <c r="A894" s="1" t="s">
         <v>35</v>
       </c>
@@ -18018,7 +18018,7 @@
       </c>
       <c r="E894" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="895" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="895" customHeight="1" ht="17.25">
       <c r="A895" s="1" t="s">
         <v>35</v>
       </c>
@@ -18033,7 +18033,7 @@
       </c>
       <c r="E895" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="896" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="896" customHeight="1" ht="17.25">
       <c r="A896" s="1" t="s">
         <v>35</v>
       </c>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="E896" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="897" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="897" customHeight="1" ht="17.25">
       <c r="A897" s="1" t="s">
         <v>35</v>
       </c>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="E897" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="898" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="898" customHeight="1" ht="17.25">
       <c r="A898" s="1" t="s">
         <v>35</v>
       </c>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="E898" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="899" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="899" customHeight="1" ht="17.25">
       <c r="A899" s="1" t="s">
         <v>35</v>
       </c>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="E899" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="900" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="900" customHeight="1" ht="17.25">
       <c r="A900" s="1" t="s">
         <v>35</v>
       </c>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="E900" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="901" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="901" customHeight="1" ht="17.25">
       <c r="A901" s="1" t="s">
         <v>35</v>
       </c>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="E901" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="902" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="902" customHeight="1" ht="17.25">
       <c r="A902" s="1" t="s">
         <v>35</v>
       </c>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="E902" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="903" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="903" customHeight="1" ht="17.25">
       <c r="A903" s="1" t="s">
         <v>35</v>
       </c>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="E903" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="904" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="904" customHeight="1" ht="17.25">
       <c r="A904" s="1" t="s">
         <v>35</v>
       </c>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="E904" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="905" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="905" customHeight="1" ht="17.25">
       <c r="A905" s="1" t="s">
         <v>35</v>
       </c>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="E905" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="906" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="906" customHeight="1" ht="17.25">
       <c r="A906" s="1" t="s">
         <v>35</v>
       </c>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="E906" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="907" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="907" customHeight="1" ht="17.25">
       <c r="A907" s="1" t="s">
         <v>35</v>
       </c>
@@ -18213,7 +18213,7 @@
       </c>
       <c r="E907" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="908" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="908" customHeight="1" ht="17.25">
       <c r="A908" s="1" t="s">
         <v>35</v>
       </c>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="E908" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="909" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="909" customHeight="1" ht="17.25">
       <c r="A909" s="1" t="s">
         <v>35</v>
       </c>
@@ -18243,7 +18243,7 @@
       </c>
       <c r="E909" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="910" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="910" customHeight="1" ht="17.25">
       <c r="A910" s="1" t="s">
         <v>35</v>
       </c>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="E910" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="911" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="911" customHeight="1" ht="17.25">
       <c r="A911" s="1" t="s">
         <v>35</v>
       </c>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E911" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="912" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="912" customHeight="1" ht="17.25">
       <c r="A912" s="1" t="s">
         <v>35</v>
       </c>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="E912" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="913" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="913" customHeight="1" ht="17.25">
       <c r="A913" s="1" t="s">
         <v>35</v>
       </c>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="E913" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="914" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="914" customHeight="1" ht="17.25">
       <c r="A914" s="1" t="s">
         <v>35</v>
       </c>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="E914" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="915" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="915" customHeight="1" ht="17.25">
       <c r="A915" s="1" t="s">
         <v>35</v>
       </c>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="E915" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="916" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="916" customHeight="1" ht="17.25">
       <c r="A916" s="1" t="s">
         <v>35</v>
       </c>
@@ -18348,7 +18348,7 @@
       </c>
       <c r="E916" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="917" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="917" customHeight="1" ht="17.25">
       <c r="A917" s="1" t="s">
         <v>35</v>
       </c>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="E917" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="918" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="918" customHeight="1" ht="17.25">
       <c r="A918" s="1" t="s">
         <v>35</v>
       </c>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="E918" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="919" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="919" customHeight="1" ht="17.25">
       <c r="A919" s="1" t="s">
         <v>35</v>
       </c>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="E919" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="920" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="920" customHeight="1" ht="17.25">
       <c r="A920" s="1" t="s">
         <v>35</v>
       </c>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="E920" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="921" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="921" customHeight="1" ht="17.25">
       <c r="A921" s="1" t="s">
         <v>35</v>
       </c>
@@ -18418,10 +18418,10 @@
       <c r="C921" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="D921" s="1"/>
+      <c r="D921" s="3"/>
       <c r="E921" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="922" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="922" customHeight="1" ht="17.25">
       <c r="A922" s="1" t="s">
         <v>35</v>
       </c>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="E922" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="923" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="923" customHeight="1" ht="17.25">
       <c r="A923" s="1" t="s">
         <v>35</v>
       </c>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="E923" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="924" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="924" customHeight="1" ht="17.25">
       <c r="A924" s="1" t="s">
         <v>35</v>
       </c>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="E924" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="925" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="925" customHeight="1" ht="17.25">
       <c r="A925" s="1" t="s">
         <v>35</v>
       </c>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="E925" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="926" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="926" customHeight="1" ht="17.25">
       <c r="A926" s="1" t="s">
         <v>35</v>
       </c>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="E926" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="927" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="927" customHeight="1" ht="17.25">
       <c r="A927" s="1" t="s">
         <v>35</v>
       </c>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="E927" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="928" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="928" customHeight="1" ht="17.25">
       <c r="A928" s="1" t="s">
         <v>35</v>
       </c>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E928" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="929" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="929" customHeight="1" ht="17.25">
       <c r="A929" s="1" t="s">
         <v>35</v>
       </c>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="E929" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="930" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="930" customHeight="1" ht="17.25">
       <c r="A930" s="1" t="s">
         <v>35</v>
       </c>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="E930" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="931" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="931" customHeight="1" ht="17.25">
       <c r="A931" s="1" t="s">
         <v>35</v>
       </c>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="E931" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="932" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="932" customHeight="1" ht="17.25">
       <c r="A932" s="1" t="s">
         <v>35</v>
       </c>
@@ -18586,7 +18586,7 @@
       </c>
       <c r="E932" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="933" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="933" customHeight="1" ht="17.25">
       <c r="A933" s="1" t="s">
         <v>35</v>
       </c>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E933" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="934" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="934" customHeight="1" ht="17.25">
       <c r="A934" s="1" t="s">
         <v>35</v>
       </c>
@@ -18616,7 +18616,7 @@
       </c>
       <c r="E934" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="935" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="935" customHeight="1" ht="17.25">
       <c r="A935" s="1" t="s">
         <v>35</v>
       </c>
@@ -18631,7 +18631,7 @@
       </c>
       <c r="E935" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="936" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="936" customHeight="1" ht="17.25">
       <c r="A936" s="1" t="s">
         <v>35</v>
       </c>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="E936" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="937" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="937" customHeight="1" ht="17.25">
       <c r="A937" s="1" t="s">
         <v>35</v>
       </c>
@@ -18656,10 +18656,10 @@
       <c r="C937" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="D937" s="1"/>
+      <c r="D937" s="3"/>
       <c r="E937" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="938" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="938" customHeight="1" ht="17.25">
       <c r="A938" s="1" t="s">
         <v>35</v>
       </c>
@@ -18674,7 +18674,7 @@
       </c>
       <c r="E938" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="939" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="939" customHeight="1" ht="17.25">
       <c r="A939" s="1" t="s">
         <v>35</v>
       </c>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="E939" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="940" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="940" customHeight="1" ht="17.25">
       <c r="A940" s="1" t="s">
         <v>35</v>
       </c>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="E940" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="941" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="941" customHeight="1" ht="17.25">
       <c r="A941" s="1" t="s">
         <v>35</v>
       </c>
@@ -18719,7 +18719,7 @@
       </c>
       <c r="E941" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="942" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="942" customHeight="1" ht="17.25">
       <c r="A942" s="1" t="s">
         <v>35</v>
       </c>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="E942" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="943" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="943" customHeight="1" ht="17.25">
       <c r="A943" s="1" t="s">
         <v>35</v>
       </c>
@@ -18749,7 +18749,7 @@
       </c>
       <c r="E943" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="944" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="944" customHeight="1" ht="17.25">
       <c r="A944" s="1" t="s">
         <v>35</v>
       </c>
@@ -18764,7 +18764,7 @@
       </c>
       <c r="E944" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="945" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="945" customHeight="1" ht="17.25">
       <c r="A945" s="1" t="s">
         <v>35</v>
       </c>
@@ -18779,7 +18779,7 @@
       </c>
       <c r="E945" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="946" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="946" customHeight="1" ht="17.25">
       <c r="A946" s="1" t="s">
         <v>35</v>
       </c>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="E946" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="947" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="947" customHeight="1" ht="17.25">
       <c r="A947" s="1" t="s">
         <v>35</v>
       </c>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E947" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="948" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="948" customHeight="1" ht="17.25">
       <c r="A948" s="1" t="s">
         <v>35</v>
       </c>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="E948" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="949" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="949" customHeight="1" ht="17.25">
       <c r="A949" s="1" t="s">
         <v>35</v>
       </c>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="E949" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="950" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="950" customHeight="1" ht="17.25">
       <c r="A950" s="1" t="s">
         <v>35</v>
       </c>
@@ -18849,10 +18849,10 @@
       <c r="C950" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="D950" s="1"/>
+      <c r="D950" s="3"/>
       <c r="E950" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="951" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="951" customHeight="1" ht="17.25">
       <c r="A951" s="1" t="s">
         <v>35</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="E951" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="952" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="952" customHeight="1" ht="17.25">
       <c r="A952" s="1" t="s">
         <v>35</v>
       </c>
@@ -18882,7 +18882,7 @@
       </c>
       <c r="E952" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="953" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="953" customHeight="1" ht="17.25">
       <c r="A953" s="1" t="s">
         <v>35</v>
       </c>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="E953" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="954" customHeight="1" ht="17.25" hidden="1">
+    <row x14ac:dyDescent="0.25" r="954" customHeight="1" ht="17.25">
       <c r="A954" s="1" t="s">
         <v>35</v>
       </c>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="E956" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="957" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="957" customHeight="1" ht="17.25">
       <c r="A957" s="1" t="s">
         <v>35</v>
       </c>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="E957" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="958" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="958" customHeight="1" ht="17.25">
       <c r="A958" s="1" t="s">
         <v>35</v>
       </c>
@@ -18972,7 +18972,7 @@
       </c>
       <c r="E958" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="959" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="959" customHeight="1" ht="17.25">
       <c r="A959" s="1" t="s">
         <v>35</v>
       </c>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="E959" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="960" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="960" customHeight="1" ht="17.25">
       <c r="A960" s="1" t="s">
         <v>35</v>
       </c>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="E960" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="961" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="961" customHeight="1" ht="17.25">
       <c r="A961" s="1" t="s">
         <v>35</v>
       </c>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="E961" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="962" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="962" customHeight="1" ht="17.25">
       <c r="A962" s="1" t="s">
         <v>35</v>
       </c>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E962" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="963" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="963" customHeight="1" ht="17.25">
       <c r="A963" s="1" t="s">
         <v>35</v>
       </c>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="E963" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="964" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="964" customHeight="1" ht="17.25">
       <c r="A964" s="1" t="s">
         <v>35</v>
       </c>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="E964" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="965" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="965" customHeight="1" ht="17.25">
       <c r="A965" s="1" t="s">
         <v>35</v>
       </c>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="E965" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="966" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="966" customHeight="1" ht="17.25">
       <c r="A966" s="1" t="s">
         <v>35</v>
       </c>
@@ -19092,7 +19092,7 @@
       </c>
       <c r="E966" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="967" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="967" customHeight="1" ht="17.25">
       <c r="A967" s="1" t="s">
         <v>35</v>
       </c>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="E967" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="968" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="968" customHeight="1" ht="17.25">
       <c r="A968" s="1" t="s">
         <v>35</v>
       </c>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="E968" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="969" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="969" customHeight="1" ht="17.25">
       <c r="A969" s="1" t="s">
         <v>35</v>
       </c>
@@ -19132,10 +19132,10 @@
       <c r="C969" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D969" s="1"/>
+      <c r="D969" s="3"/>
       <c r="E969" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="970" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="970" customHeight="1" ht="17.25">
       <c r="A970" s="1" t="s">
         <v>35</v>
       </c>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E970" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="971" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="971" customHeight="1" ht="17.25">
       <c r="A971" s="1" t="s">
         <v>35</v>
       </c>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="E971" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="972" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="972" customHeight="1" ht="17.25">
       <c r="A972" s="1" t="s">
         <v>35</v>
       </c>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="E972" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="973" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="973" customHeight="1" ht="17.25">
       <c r="A973" s="1" t="s">
         <v>35</v>
       </c>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="E973" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="974" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="974" customHeight="1" ht="17.25">
       <c r="A974" s="1" t="s">
         <v>35</v>
       </c>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="E974" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="975" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="975" customHeight="1" ht="17.25">
       <c r="A975" s="1" t="s">
         <v>35</v>
       </c>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="E976" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="977" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="977" customHeight="1" ht="17.25">
       <c r="A977" s="1" t="s">
         <v>35</v>
       </c>
@@ -19250,12 +19250,10 @@
       <c r="C977" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="D977" s="1" t="s">
-        <v>472</v>
-      </c>
+      <c r="D977" s="3"/>
       <c r="E977" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="978" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="978" customHeight="1" ht="17.25">
       <c r="A978" s="1" t="s">
         <v>35</v>
       </c>
@@ -19265,10 +19263,12 @@
       <c r="C978" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="D978" s="1"/>
+      <c r="D978" s="1" t="s">
+        <v>1350</v>
+      </c>
       <c r="E978" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="979" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="979" customHeight="1" ht="17.25">
       <c r="A979" s="1" t="s">
         <v>35</v>
       </c>
@@ -19276,10 +19276,10 @@
         <v>1325</v>
       </c>
       <c r="C979" s="1" t="s">
-        <v>1350</v>
+        <v>656</v>
       </c>
       <c r="D979" s="1" t="s">
-        <v>1351</v>
+        <v>654</v>
       </c>
       <c r="E979" s="2"/>
     </row>
@@ -19291,10 +19291,10 @@
         <v>1325</v>
       </c>
       <c r="C980" s="1" t="s">
-        <v>656</v>
+        <v>1351</v>
       </c>
       <c r="D980" s="1" t="s">
-        <v>654</v>
+        <v>1352</v>
       </c>
       <c r="E980" s="2"/>
     </row>
@@ -19306,10 +19306,10 @@
         <v>1325</v>
       </c>
       <c r="C981" s="1" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D981" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E981" s="2"/>
     </row>
@@ -19321,10 +19321,10 @@
         <v>1325</v>
       </c>
       <c r="C982" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D982" s="1" t="s">
         <v>1354</v>
-      </c>
-      <c r="D982" s="1" t="s">
-        <v>1355</v>
       </c>
       <c r="E982" s="2"/>
     </row>
@@ -19339,7 +19339,7 @@
         <v>1356</v>
       </c>
       <c r="D983" s="1" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="E983" s="2"/>
     </row>
@@ -19354,7 +19354,7 @@
         <v>1357</v>
       </c>
       <c r="D984" s="1" t="s">
-        <v>1353</v>
+        <v>654</v>
       </c>
       <c r="E984" s="2"/>
     </row>
@@ -19366,11 +19366,9 @@
         <v>1325</v>
       </c>
       <c r="C985" s="1" t="s">
-        <v>1358</v>
-      </c>
-      <c r="D985" s="1" t="s">
-        <v>654</v>
-      </c>
+        <v>722</v>
+      </c>
+      <c r="D985" s="3"/>
       <c r="E985" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="986" customHeight="1" ht="17.25">
@@ -19381,9 +19379,11 @@
         <v>1325</v>
       </c>
       <c r="C986" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="D986" s="1"/>
+        <v>1358</v>
+      </c>
+      <c r="D986" s="1" t="s">
+        <v>1359</v>
+      </c>
       <c r="E986" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="987" customHeight="1" ht="17.25">
@@ -19394,10 +19394,10 @@
         <v>1325</v>
       </c>
       <c r="C987" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D987" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="D987" s="1" t="s">
-        <v>1360</v>
       </c>
       <c r="E987" s="2"/>
     </row>
@@ -19409,10 +19409,10 @@
         <v>1325</v>
       </c>
       <c r="C988" s="1" t="s">
-        <v>779</v>
+        <v>1360</v>
       </c>
       <c r="D988" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E988" s="2"/>
     </row>
@@ -19427,7 +19427,7 @@
         <v>1361</v>
       </c>
       <c r="D989" s="1" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E989" s="2"/>
     </row>
@@ -19439,10 +19439,10 @@
         <v>1325</v>
       </c>
       <c r="C990" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D990" s="1" t="s">
         <v>1362</v>
-      </c>
-      <c r="D990" s="1" t="s">
-        <v>1363</v>
       </c>
       <c r="E990" s="2"/>
     </row>
@@ -19454,10 +19454,10 @@
         <v>1325</v>
       </c>
       <c r="C991" s="1" t="s">
-        <v>1364</v>
+        <v>785</v>
       </c>
       <c r="D991" s="1" t="s">
-        <v>1363</v>
+        <v>787</v>
       </c>
       <c r="E991" s="2"/>
     </row>
@@ -19484,7 +19484,7 @@
         <v>1325</v>
       </c>
       <c r="C993" s="1" t="s">
-        <v>785</v>
+        <v>1364</v>
       </c>
       <c r="D993" s="1" t="s">
         <v>787</v>
@@ -19502,7 +19502,7 @@
         <v>1365</v>
       </c>
       <c r="D994" s="1" t="s">
-        <v>787</v>
+        <v>1362</v>
       </c>
       <c r="E994" s="2"/>
     </row>
@@ -19517,7 +19517,7 @@
         <v>1366</v>
       </c>
       <c r="D995" s="1" t="s">
-        <v>1363</v>
+        <v>811</v>
       </c>
       <c r="E995" s="2"/>
     </row>
@@ -19547,7 +19547,7 @@
         <v>1368</v>
       </c>
       <c r="D997" s="1" t="s">
-        <v>811</v>
+        <v>1369</v>
       </c>
       <c r="E997" s="2"/>
     </row>
@@ -19559,10 +19559,10 @@
         <v>1325</v>
       </c>
       <c r="C998" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D998" s="1" t="s">
         <v>1369</v>
-      </c>
-      <c r="D998" s="1" t="s">
-        <v>1370</v>
       </c>
       <c r="E998" s="2"/>
     </row>
@@ -19577,7 +19577,7 @@
         <v>1371</v>
       </c>
       <c r="D999" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="E999" s="2"/>
     </row>
@@ -19589,11 +19589,9 @@
         <v>1325</v>
       </c>
       <c r="C1000" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="D1000" s="1" t="s">
-        <v>1370</v>
-      </c>
+        <v>866</v>
+      </c>
+      <c r="D1000" s="3"/>
       <c r="E1000" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1001" customHeight="1" ht="17.25">
@@ -19604,9 +19602,11 @@
         <v>1325</v>
       </c>
       <c r="C1001" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="D1001" s="1"/>
+        <v>1372</v>
+      </c>
+      <c r="D1001" s="1" t="s">
+        <v>787</v>
+      </c>
       <c r="E1001" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1002" customHeight="1" ht="17.25">
@@ -19617,10 +19617,10 @@
         <v>1325</v>
       </c>
       <c r="C1002" s="1" t="s">
-        <v>1373</v>
+        <v>62</v>
       </c>
       <c r="D1002" s="1" t="s">
-        <v>787</v>
+        <v>62</v>
       </c>
       <c r="E1002" s="2"/>
     </row>
@@ -19632,10 +19632,10 @@
         <v>1325</v>
       </c>
       <c r="C1003" s="1" t="s">
-        <v>62</v>
+        <v>1373</v>
       </c>
       <c r="D1003" s="1" t="s">
-        <v>62</v>
+        <v>1374</v>
       </c>
       <c r="E1003" s="2"/>
     </row>
@@ -19647,10 +19647,10 @@
         <v>1325</v>
       </c>
       <c r="C1004" s="1" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D1004" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E1004" s="2"/>
     </row>
@@ -19662,10 +19662,10 @@
         <v>1325</v>
       </c>
       <c r="C1005" s="1" t="s">
-        <v>1376</v>
+        <v>972</v>
       </c>
       <c r="D1005" s="1" t="s">
-        <v>1377</v>
+        <v>62</v>
       </c>
       <c r="E1005" s="2"/>
     </row>
@@ -19677,10 +19677,10 @@
         <v>1325</v>
       </c>
       <c r="C1006" s="1" t="s">
-        <v>972</v>
+        <v>1377</v>
       </c>
       <c r="D1006" s="1" t="s">
-        <v>62</v>
+        <v>1374</v>
       </c>
       <c r="E1006" s="2"/>
     </row>
@@ -19695,7 +19695,7 @@
         <v>1378</v>
       </c>
       <c r="D1007" s="1" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="E1007" s="2"/>
     </row>
@@ -19707,10 +19707,10 @@
         <v>1325</v>
       </c>
       <c r="C1008" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="D1008" s="1" t="s">
         <v>1379</v>
-      </c>
-      <c r="D1008" s="1" t="s">
-        <v>1380</v>
       </c>
       <c r="E1008" s="2"/>
     </row>
@@ -19722,10 +19722,10 @@
         <v>1325</v>
       </c>
       <c r="C1009" s="1" t="s">
-        <v>975</v>
+        <v>1380</v>
       </c>
       <c r="D1009" s="1" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="E1009" s="2"/>
     </row>
@@ -19740,7 +19740,7 @@
         <v>1381</v>
       </c>
       <c r="D1010" s="1" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="E1010" s="2"/>
     </row>
@@ -19752,10 +19752,10 @@
         <v>1325</v>
       </c>
       <c r="C1011" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D1011" s="1" t="s">
         <v>1382</v>
-      </c>
-      <c r="D1011" s="1" t="s">
-        <v>1383</v>
       </c>
       <c r="E1011" s="2"/>
     </row>
@@ -19770,7 +19770,7 @@
         <v>1384</v>
       </c>
       <c r="D1012" s="1" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="E1012" s="2"/>
     </row>
@@ -19782,10 +19782,10 @@
         <v>1325</v>
       </c>
       <c r="C1013" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="D1013" s="1" t="s">
         <v>1385</v>
-      </c>
-      <c r="D1013" s="1" t="s">
-        <v>1377</v>
       </c>
       <c r="E1013" s="2"/>
     </row>
@@ -19797,7 +19797,7 @@
         <v>1325</v>
       </c>
       <c r="C1014" s="1" t="s">
-        <v>984</v>
+        <v>106</v>
       </c>
       <c r="D1014" s="1" t="s">
         <v>1386</v>
@@ -19812,10 +19812,10 @@
         <v>1325</v>
       </c>
       <c r="C1015" s="1" t="s">
-        <v>106</v>
+        <v>1387</v>
       </c>
       <c r="D1015" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="E1015" s="2"/>
     </row>
@@ -19830,7 +19830,7 @@
         <v>1388</v>
       </c>
       <c r="D1016" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="E1016" s="2"/>
     </row>
@@ -19845,7 +19845,7 @@
         <v>1389</v>
       </c>
       <c r="D1017" s="1" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="E1017" s="2"/>
     </row>
@@ -19857,11 +19857,9 @@
         <v>1325</v>
       </c>
       <c r="C1018" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D1018" s="1" t="s">
         <v>1391</v>
       </c>
+      <c r="D1018" s="3"/>
       <c r="E1018" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1019" customHeight="1" ht="17.25">
@@ -19874,7 +19872,9 @@
       <c r="C1019" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="D1019" s="1"/>
+      <c r="D1019" s="1" t="s">
+        <v>1390</v>
+      </c>
       <c r="E1019" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="1020" customHeight="1" ht="17.25">
@@ -19885,10 +19885,10 @@
         <v>1325</v>
       </c>
       <c r="C1020" s="1" t="s">
-        <v>1393</v>
+        <v>1229</v>
       </c>
       <c r="D1020" s="1" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="E1020" s="2"/>
     </row>
@@ -19900,10 +19900,10 @@
         <v>1325</v>
       </c>
       <c r="C1021" s="1" t="s">
-        <v>1229</v>
+        <v>1393</v>
       </c>
       <c r="D1021" s="1" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="E1021" s="2"/>
     </row>
@@ -19915,27 +19915,12 @@
         <v>1325</v>
       </c>
       <c r="C1022" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D1022" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="D1022" s="1" t="s">
-        <v>1395</v>
-      </c>
       <c r="E1022" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1023" customHeight="1" ht="17.25">
-      <c r="A1023" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1023" s="1" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C1023" s="1" t="s">
-        <v>1396</v>
-      </c>
-      <c r="D1023" s="1" t="s">
-        <v>1395</v>
-      </c>
-      <c r="E1023" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
